--- a/stock_simulation_results.xlsx
+++ b/stock_simulation_results.xlsx
@@ -508,22 +508,22 @@
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.633957571680109</v>
+        <v>-1.323612281931698</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2450936357520163</v>
+        <v>0.2313540128857879</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3328432090459479</v>
+        <v>-0.330738078676345</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1221685869566377</v>
+        <v>-0.1151532774526489</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.843875731930678</v>
+        <v>-1.538149625174904</v>
       </c>
       <c r="M2" t="n">
-        <v>96.75220750921105</v>
+        <v>96.96355846756651</v>
       </c>
     </row>
     <row r="3">
@@ -539,34 +539,34 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5088472871343004</v>
+        <v>-0.4996677928691061</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3308389593380819</v>
+        <v>0.3241083583519422</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06382646764375421</v>
+        <v>0.06076920657619647</v>
       </c>
       <c r="G3" t="n">
         <v>9984.870763225184</v>
       </c>
       <c r="H3" t="n">
-        <v>-12.77683093291343</v>
+        <v>-10.61068364663351</v>
       </c>
       <c r="I3" t="n">
-        <v>4.740627083532379</v>
+        <v>4.49806641696779</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.621533978450301</v>
+        <v>-2.563531835249902</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7315061448555239</v>
+        <v>-0.6516053978288181</v>
       </c>
       <c r="L3" t="n">
-        <v>-11.38924397268688</v>
+        <v>-9.327754462744442</v>
       </c>
       <c r="M3" t="n">
-        <v>92.07093584105503</v>
+        <v>92.36547590833906</v>
       </c>
     </row>
     <row r="4">
@@ -582,34 +582,34 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3179227736900518</v>
+        <v>-0.3655084686694272</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2516289923392796</v>
+        <v>0.2712007086309213</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1521883203131214</v>
+        <v>0.1297390685731623</v>
       </c>
       <c r="G4" t="n">
-        <v>9820.964207233625</v>
+        <v>9824.329507726694</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.40873784942057</v>
+        <v>-9.446253346670838</v>
       </c>
       <c r="I4" t="n">
-        <v>3.325782071392874</v>
+        <v>3.558841632318601</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.132073368351972</v>
+        <v>-2.253051790735644</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.638418762812905</v>
+        <v>-0.5310809765041553</v>
       </c>
       <c r="L4" t="n">
-        <v>-9.853447909192569</v>
+        <v>-8.671544481592036</v>
       </c>
       <c r="M4" t="n">
-        <v>87.39959274077121</v>
+        <v>87.74588274777875</v>
       </c>
     </row>
     <row r="5">
@@ -625,34 +625,34 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2672479559314082</v>
+        <v>-0.3039294042915368</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2362877620707643</v>
+        <v>0.2481811969588492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1898474712797985</v>
+        <v>0.1645588859598177</v>
       </c>
       <c r="G5" t="n">
-        <v>9713.053290340622</v>
+        <v>9706.296202638565</v>
       </c>
       <c r="H5" t="n">
-        <v>-10.08705959250719</v>
+        <v>-8.59377103554869</v>
       </c>
       <c r="I5" t="n">
-        <v>2.996285094295394</v>
+        <v>3.138068389946481</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.064669470915592</v>
+        <v>-2.152564577326629</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6366548916921637</v>
+        <v>-0.6265123143423998</v>
       </c>
       <c r="L5" t="n">
-        <v>-9.792098860819548</v>
+        <v>-8.234779537271237</v>
       </c>
       <c r="M5" t="n">
-        <v>82.68496765362354</v>
+        <v>83.10354799314058</v>
       </c>
     </row>
     <row r="6">
@@ -668,34 +668,34 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2546545096417543</v>
+        <v>-0.2921673766612473</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2375244943354824</v>
+        <v>0.2477336767761896</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2118294713760746</v>
+        <v>0.181083126948603</v>
       </c>
       <c r="G6" t="n">
-        <v>9623.604080271176</v>
+        <v>9611.575983895284</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.2797775976985</v>
+        <v>-8.737470017729372</v>
       </c>
       <c r="I6" t="n">
-        <v>2.955299168166513</v>
+        <v>3.065213381506956</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.103460418406799</v>
+        <v>-2.102395876264768</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6566029156799269</v>
+        <v>-0.6066782408477053</v>
       </c>
       <c r="L6" t="n">
-        <v>-10.08454176361872</v>
+        <v>-8.38133075333489</v>
       </c>
       <c r="M6" t="n">
-        <v>77.91829025316343</v>
+        <v>78.41449166601456</v>
       </c>
     </row>
     <row r="7">
@@ -711,34 +711,34 @@
         <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.252908105674773</v>
+        <v>-0.2931691165949571</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2429221035895965</v>
+        <v>0.2528867434379786</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2279431004618319</v>
+        <v>0.1924631837025107</v>
       </c>
       <c r="G7" t="n">
-        <v>9542.481425076317</v>
+        <v>9526.55154711766</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.188712537090484</v>
+        <v>-1.943646354128244</v>
       </c>
       <c r="I7" t="n">
-        <v>1.101946867058562</v>
+        <v>1.26609056884986</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.466326928136017</v>
+        <v>-1.491832241492128</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6495303822457966</v>
+        <v>0.6139496040295962</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.903562215922142</v>
+        <v>-1.555438422740915</v>
       </c>
       <c r="M7" t="n">
-        <v>74.45461275393299</v>
+        <v>75.19149336852901</v>
       </c>
     </row>
     <row r="8">
@@ -747,41 +747,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0.6759237913802965</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2329787384984682</v>
+        <v>-0.2475546994073098</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2161078360736091</v>
+        <v>0.2149457374239521</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1908014824363206</v>
+        <v>0.1660322944489156</v>
       </c>
       <c r="G8" t="n">
-        <v>9466.772230773888</v>
+        <v>9447.453020686906</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.228950266426655</v>
+        <v>-0.8705009730669263</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8690431263882298</v>
+        <v>0.8691521761509813</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.235304928432468</v>
+        <v>-1.207064514798142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6883820674422974</v>
+        <v>0.606335942487909</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9068300010285956</v>
+        <v>-0.6020773692261783</v>
       </c>
       <c r="M8" t="n">
-        <v>71.92817963393543</v>
+        <v>73.19440101387931</v>
       </c>
     </row>
     <row r="9">
@@ -790,41 +790,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0.6526756739341637</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2156563268807941</v>
+        <v>-0.1904817903043689</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1923319477449137</v>
+        <v>0.1700636101548717</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1573453790410931</v>
+        <v>0.1394363399306259</v>
       </c>
       <c r="G9" t="n">
-        <v>9412.041089659693</v>
+        <v>9395.234849906239</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3972538222074338</v>
+        <v>0.4703965659117559</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6690725809787751</v>
+        <v>0.3702403370928034</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.031663097498298</v>
+        <v>-0.8400318087630936</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7196354296257648</v>
+        <v>0.7422817772560196</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.04020890910119224</v>
+        <v>0.7428868714974852</v>
       </c>
       <c r="M9" t="n">
-        <v>71.72252853299823</v>
+        <v>75.47189861496528</v>
       </c>
     </row>
     <row r="10">
@@ -833,41 +833,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0.6302271658103858</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.02243446110497926</v>
+        <v>0.2514921958582466</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06443791674793795</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.127443100212376</v>
+        <v>0.1237244563700586</v>
       </c>
       <c r="G10" t="n">
-        <v>9374.671006821267</v>
+        <v>9370.679559838178</v>
       </c>
       <c r="H10" t="n">
-        <v>4.30742309638577</v>
+        <v>6.797921361480688</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.088806654554579</v>
+        <v>-2.54558935994816</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.03372099620697309</v>
+        <v>1.144660901826034</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9639044487320967</v>
+        <v>1.125971014020567</v>
       </c>
       <c r="L10" t="n">
-        <v>4.148799894356316</v>
+        <v>6.522963917379129</v>
       </c>
       <c r="M10" t="n">
-        <v>76.00313336158331</v>
+        <v>80.06784668697443</v>
       </c>
     </row>
     <row r="11">
@@ -876,41 +876,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0.608550764779164</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3993092833889774</v>
+        <v>0.3561685105039341</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.149465217361508</v>
+        <v>0.1709756712863457</v>
       </c>
       <c r="G11" t="n">
-        <v>9404.984947765171</v>
+        <v>9433.611603854361</v>
       </c>
       <c r="H11" t="n">
-        <v>8.703500836123691</v>
+        <v>7.055545905817059</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.260289662629103</v>
+        <v>-2.87627337012655</v>
       </c>
       <c r="J11" t="n">
-        <v>1.607927028889043</v>
+        <v>1.349029795991075</v>
       </c>
       <c r="K11" t="n">
-        <v>1.322602337559792</v>
+        <v>1.01393244630856</v>
       </c>
       <c r="L11" t="n">
-        <v>8.373740539943423</v>
+        <v>6.542234777990145</v>
       </c>
       <c r="M11" t="n">
-        <v>80.72404927401698</v>
+        <v>84.63957873199975</v>
       </c>
     </row>
     <row r="12">
@@ -919,41 +919,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5876199145384451</v>
+        <v>0.7</v>
       </c>
       <c r="D12" t="n">
-        <v>0.304716995235879</v>
+        <v>0.2877423004851905</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2038440740552973</v>
+        <v>0.1984352887906671</v>
       </c>
       <c r="G12" t="n">
-        <v>9464.486452988654</v>
+        <v>9490.250443468925</v>
       </c>
       <c r="H12" t="n">
-        <v>7.04304604768481</v>
+        <v>6.6631917764983</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.820677599959112</v>
+        <v>-2.787179536142272</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9911115992607719</v>
+        <v>1.038858220818036</v>
       </c>
       <c r="K12" t="n">
-        <v>1.115481177568332</v>
+        <v>1.109393435944511</v>
       </c>
       <c r="L12" t="n">
-        <v>6.328961224554802</v>
+        <v>6.024263897118574</v>
       </c>
       <c r="M12" t="n">
-        <v>85.26368654411684</v>
+        <v>89.13717398784054</v>
       </c>
     </row>
     <row r="13">
@@ -962,41 +962,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5674089721791309</v>
+        <v>0.6759237913802965</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2615929950009435</v>
+        <v>0.247957346579736</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2149770524056486</v>
+        <v>0.214303812245586</v>
       </c>
       <c r="G13" t="n">
-        <v>9518.037807689789</v>
+        <v>9541.225399122033</v>
       </c>
       <c r="H13" t="n">
-        <v>6.321926997289339</v>
+        <v>6.341972055243524</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.591455854637474</v>
+        <v>-2.660042539654189</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7538727425603103</v>
+        <v>0.8039860267218379</v>
       </c>
       <c r="K13" t="n">
-        <v>1.020248092713196</v>
+        <v>1.122949622979076</v>
       </c>
       <c r="L13" t="n">
-        <v>5.504591977925371</v>
+        <v>5.608865165290249</v>
       </c>
       <c r="M13" t="n">
-        <v>89.68702186631711</v>
+        <v>93.56294579945063</v>
       </c>
     </row>
     <row r="14">
@@ -1005,41 +1005,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5478931767693077</v>
+        <v>0.6526756739341637</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2442451388734742</v>
+        <v>0.2272710177409026</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2124025998315994</v>
+        <v>0.2184671285692689</v>
       </c>
       <c r="G14" t="n">
-        <v>9566.234026920811</v>
+        <v>9587.10285920983</v>
       </c>
       <c r="H14" t="n">
-        <v>5.979848034240297</v>
+        <v>5.856237381709867</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.468504389714702</v>
+        <v>-2.582548919381228</v>
       </c>
       <c r="J14" t="n">
-        <v>0.675263332936807</v>
+        <v>0.6884022818251666</v>
       </c>
       <c r="K14" t="n">
-        <v>0.970356213031456</v>
+        <v>0.9887376306701525</v>
       </c>
       <c r="L14" t="n">
-        <v>5.156963190493858</v>
+        <v>4.950828374823959</v>
       </c>
       <c r="M14" t="n">
-        <v>94.04902692770305</v>
+        <v>97.88495899714702</v>
       </c>
     </row>
     <row r="15">
@@ -1048,41 +1048,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5290486190190078</v>
+        <v>0.6302271658103858</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2356321569125126</v>
+        <v>0.2166454075067645</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2064058506423636</v>
+        <v>0.2132223445865091</v>
       </c>
       <c r="G15" t="n">
-        <v>9609.61062422873</v>
+        <v>9628.392573288847</v>
       </c>
       <c r="H15" t="n">
-        <v>5.756770475819828</v>
+        <v>5.538893117401846</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.382741506846997</v>
+        <v>-2.465053233625696</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6459538440996034</v>
+        <v>0.6403004509277628</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9349145880376336</v>
+        <v>0.9269306489995326</v>
       </c>
       <c r="L15" t="n">
-        <v>4.954897401110068</v>
+        <v>4.641070983703445</v>
       </c>
       <c r="M15" t="n">
-        <v>98.36366768447941</v>
+        <v>102.1443563084671</v>
       </c>
     </row>
     <row r="16">
@@ -1091,41 +1091,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5108522119883397</v>
+        <v>0.608550764779164</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2295605370395932</v>
+        <v>0.2113828588885911</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1998449153474692</v>
+        <v>0.2058554748794592</v>
       </c>
       <c r="G16" t="n">
-        <v>9648.649561805856</v>
+        <v>9665.553315959962</v>
       </c>
       <c r="H16" t="n">
-        <v>5.568571856007188</v>
+        <v>5.602909215055477</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.30902114737887</v>
+        <v>-2.408954383828822</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6297146987568361</v>
+        <v>0.6465396623397448</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9039227085953152</v>
+        <v>0.9455691178472176</v>
       </c>
       <c r="L16" t="n">
-        <v>4.79318811598047</v>
+        <v>4.786063611413617</v>
       </c>
       <c r="M16" t="n">
-        <v>102.639534724446</v>
+        <v>106.4053469904343</v>
       </c>
     </row>
     <row r="17">
@@ -1134,41 +1134,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4932816628030994</v>
+        <v>0.5876199145384451</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2247888089698651</v>
+        <v>0.2067149592304304</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1933814409677032</v>
+        <v>0.2018014592807699</v>
       </c>
       <c r="G17" t="n">
-        <v>9683.784605625271</v>
+        <v>9698.997984363965</v>
       </c>
       <c r="H17" t="n">
-        <v>5.397113133783678</v>
+        <v>5.308762302249243</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.242255165896323</v>
+        <v>-2.349497760429776</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6189111348117473</v>
+        <v>0.6124264856005166</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8752159744682837</v>
+        <v>0.998676766005733</v>
       </c>
       <c r="L17" t="n">
-        <v>4.648985077167387</v>
+        <v>4.570367793425716</v>
       </c>
       <c r="M17" t="n">
-        <v>106.8749592877851</v>
+        <v>110.6257335948738</v>
       </c>
     </row>
     <row r="18">
@@ -1177,41 +1177,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.4763154453432114</v>
+        <v>0.5674089721791309</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2204531660554759</v>
+        <v>0.2021929669372726</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1871827984924508</v>
+        <v>0.1961655492296414</v>
       </c>
       <c r="G18" t="n">
-        <v>9715.406145062743</v>
+        <v>9729.098185927569</v>
       </c>
       <c r="H18" t="n">
-        <v>5.233217090652933</v>
+        <v>5.228471825253448</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.178887024951348</v>
+        <v>-2.238639226578286</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6093969155953118</v>
+        <v>0.5802811037032868</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8476943660530614</v>
+        <v>0.9267548644227052</v>
       </c>
       <c r="L18" t="n">
-        <v>4.511421347349958</v>
+        <v>4.496868566801154</v>
       </c>
       <c r="M18" t="n">
-        <v>111.0738048146189</v>
+        <v>114.8185822702993</v>
       </c>
     </row>
     <row r="19">
@@ -1220,41 +1220,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4599327738705397</v>
+        <v>0.5478931767693077</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2167707522927806</v>
+        <v>0.198395678333039</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1812396648361306</v>
+        <v>0.1910384638147529</v>
       </c>
       <c r="G19" t="n">
-        <v>9743.865530556468</v>
+        <v>9756.188367334813</v>
       </c>
       <c r="H19" t="n">
-        <v>5.072175574462235</v>
+        <v>5.075894802543464</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.119740036236218</v>
+        <v>-2.14257339269232</v>
       </c>
       <c r="J19" t="n">
-        <v>0.60205712369714</v>
+        <v>0.5890482383605603</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8215379626406809</v>
+        <v>0.9323568260001603</v>
       </c>
       <c r="L19" t="n">
-        <v>4.376030624563837</v>
+        <v>4.454726474211865</v>
       </c>
       <c r="M19" t="n">
-        <v>115.2394506451821</v>
+        <v>118.9902304888847</v>
       </c>
     </row>
     <row r="20">
@@ -1263,41 +1263,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4441135775637596</v>
+        <v>0.5290486190190078</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2136937067755508</v>
+        <v>0.1947445541030108</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1755007438408437</v>
+        <v>0.1865650018694358</v>
       </c>
       <c r="G20" t="n">
-        <v>9769.478977500821</v>
+        <v>9780.569530601331</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4.935888701250783</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.064566171863131</v>
+        <v>-2.125721888165964</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5968854293025879</v>
+        <v>0.5643825443951642</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7967362588347144</v>
+        <v>0.736446343891608</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.670944483725829</v>
+        <v>4.110995701371591</v>
       </c>
       <c r="M20" t="n">
-        <v>113.1873053199267</v>
+        <v>123.0929377087893</v>
       </c>
     </row>
     <row r="21">
@@ -1306,41 +1306,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4288384759290912</v>
+        <v>0.5108522119883397</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1326795632161536</v>
+        <v>0.1920840951601563</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1332939659376731</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1342155700199525</v>
+        <v>0.1795013890863278</v>
       </c>
       <c r="G21" t="n">
-        <v>9792.531079750739</v>
+        <v>9802.512577541198</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7250168173237203</v>
+        <v>4.633172944953363</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4591694701120282</v>
+        <v>-2.08572728500243</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7720360229530064</v>
+        <v>0.5652386805191422</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4341756981111003</v>
+        <v>0.8940650839564499</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6037076720535981</v>
+        <v>4.006749424426524</v>
       </c>
       <c r="M21" t="n">
-        <v>111.2545662390888</v>
+        <v>127.1704210334471</v>
       </c>
     </row>
     <row r="22">
@@ -1349,41 +1349,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4140887550567706</v>
+        <v>0.4932816628030994</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1580950259299172</v>
+        <v>0.1911318588378861</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1380603525695351</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.108008342528962</v>
+        <v>0.1733109382954789</v>
       </c>
       <c r="G22" t="n">
-        <v>9746.63098880683</v>
+        <v>9822.261319787078</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9052437187744787</v>
+        <v>4.439622089877267</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6405340721761185</v>
+        <v>-1.972412766507279</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7883850713482818</v>
+        <v>0.5683641381023755</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4170878044001426</v>
+        <v>0.8331144649401494</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6360069135464995</v>
+        <v>3.868687926412513</v>
       </c>
       <c r="M22" t="n">
-        <v>109.2534154126051</v>
+        <v>131.2044314894984</v>
       </c>
     </row>
     <row r="23">
@@ -1392,41 +1392,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3998463446941704</v>
+        <v>0.4763154453432114</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1957900270442705</v>
+        <v>0.1895647437536645</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1542218211888346</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09186951240568073</v>
+        <v>0.1673375253815674</v>
       </c>
       <c r="G23" t="n">
-        <v>9702.937713641379</v>
+        <v>9840.035187808369</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.571921937424317</v>
+        <v>4.385082341645519</v>
       </c>
       <c r="I23" t="n">
-        <v>0.962561230484595</v>
+        <v>-1.879506252980812</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9050136342944688</v>
+        <v>0.5614494071366158</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3695381089840754</v>
+        <v>0.7904335542264644</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.144836232250115</v>
+        <v>3.857459050027787</v>
       </c>
       <c r="M23" t="n">
-        <v>106.4917627627758</v>
+        <v>135.2333317660302</v>
       </c>
     </row>
     <row r="24">
@@ -1435,41 +1435,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3860937961074808</v>
+        <v>0.4599327738705397</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2920147626014799</v>
+        <v>0.1886264594280179</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2098338123611352</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08656238700061811</v>
+        <v>0.1627928779963789</v>
       </c>
       <c r="G24" t="n">
-        <v>9655.533031682822</v>
+        <v>9856.031669027532</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.777752688196733</v>
+        <v>4.259557153956444</v>
       </c>
       <c r="I24" t="n">
-        <v>1.83986041917099</v>
+        <v>-1.939900134079144</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.338048614662046</v>
+        <v>0.5587473510947716</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2331417257853876</v>
+        <v>0.6812569004244646</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.042799157902402</v>
+        <v>3.559661271396536</v>
       </c>
       <c r="M24" t="n">
-        <v>102.5649194123629</v>
+        <v>139.1883819038421</v>
       </c>
     </row>
     <row r="25">
@@ -1478,41 +1478,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.372814260704828</v>
+        <v>0.4441135775637596</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3626888897240949</v>
+        <v>0.1871524311155532</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2582813792683645</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1016701135847689</v>
+        <v>0.1562689782053197</v>
       </c>
       <c r="G25" t="n">
-        <v>9585.062822333972</v>
+        <v>9870.42850212478</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.846534454792796</v>
+        <v>4.120341712526934</v>
       </c>
       <c r="I25" t="n">
-        <v>2.554370671553302</v>
+        <v>-1.890111818247764</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.742903131798991</v>
+        <v>0.5671744043439525</v>
       </c>
       <c r="K25" t="n">
-        <v>0.09622908309051412</v>
+        <v>0.7457778435996361</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.938837831947971</v>
+        <v>3.543182142222759</v>
       </c>
       <c r="M25" t="n">
-        <v>98.18922160204158</v>
+        <v>143.1325222353879</v>
       </c>
     </row>
     <row r="26">
@@ -1521,41 +1521,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.3599914693946423</v>
+        <v>0.4288384759290912</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3306388475211057</v>
+        <v>0.1871658838312215</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2499957723148964</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1290311595055825</v>
+        <v>0.1513988872236074</v>
       </c>
       <c r="G26" t="n">
-        <v>9497.415850466394</v>
+        <v>9883.385651912302</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.873485597057645</v>
+        <v>4.074810966276239</v>
       </c>
       <c r="I26" t="n">
-        <v>2.392076120845604</v>
+        <v>-1.789102987776878</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.728684331027007</v>
+        <v>0.5769325547498985</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06725949255973915</v>
+        <v>0.7130252091207017</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.142834314679309</v>
+        <v>3.57566574236996</v>
       </c>
       <c r="M26" t="n">
-        <v>93.74805682690277</v>
+        <v>147.081368512084</v>
       </c>
     </row>
     <row r="27">
@@ -1564,41 +1564,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.3476097126539866</v>
+        <v>0.4140887550567706</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3080130643110532</v>
+        <v>0.1863626802046272</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2435464835145818</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1468466123198747</v>
+        <v>0.1480379135543186</v>
       </c>
       <c r="G27" t="n">
-        <v>9422.676379262306</v>
+        <v>9895.047086721072</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.900062914829051</v>
+        <v>3.968816437231742</v>
       </c>
       <c r="I27" t="n">
-        <v>2.281633202762114</v>
+        <v>-1.772381397834797</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.715375477384307</v>
+        <v>0.5653657782170058</v>
       </c>
       <c r="K27" t="n">
-        <v>0.04290504072182617</v>
+        <v>0.6288910938281878</v>
       </c>
       <c r="L27" t="n">
-        <v>-5.290900148729417</v>
+        <v>3.390691911442139</v>
       </c>
       <c r="M27" t="n">
-        <v>89.25608088826208</v>
+        <v>150.9775109509027</v>
       </c>
     </row>
     <row r="28">
@@ -1607,41 +1607,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.3356538212824258</v>
+        <v>0.3998463446941704</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3025010932845137</v>
+        <v>0.1846820709482549</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2448596377754756</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1583974545119183</v>
+        <v>0.1434341049998511</v>
       </c>
       <c r="G28" t="n">
-        <v>9358.635499578784</v>
+        <v>9905.542378048964</v>
       </c>
       <c r="H28" t="n">
-        <v>-6.169563651641439</v>
+        <v>3.839219278375527</v>
       </c>
       <c r="I28" t="n">
-        <v>2.302227176321083</v>
+        <v>-1.804786662174259</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.752800007678778</v>
+        <v>0.5730141455686858</v>
       </c>
       <c r="K28" t="n">
-        <v>0.008341521193486436</v>
+        <v>0.7007780406851756</v>
       </c>
       <c r="L28" t="n">
-        <v>-5.611794961805647</v>
+        <v>3.308224802455129</v>
       </c>
       <c r="M28" t="n">
-        <v>84.68968652197252</v>
+        <v>154.8477476370996</v>
       </c>
     </row>
     <row r="29">
@@ -1650,41 +1650,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3241091478178597</v>
+        <v>0.3860937961074808</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3046377688179535</v>
+        <v>0.184242061159274</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2499583066465036</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1679391133893288</v>
+        <v>0.1391350282591705</v>
       </c>
       <c r="G29" t="n">
-        <v>9300.342130733168</v>
+        <v>9914.988140244068</v>
       </c>
       <c r="H29" t="n">
-        <v>-6.562061096917348</v>
+        <v>3.751225666718328</v>
       </c>
       <c r="I29" t="n">
-        <v>2.383350548441169</v>
+        <v>-1.733323097625014</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.816156687657772</v>
+        <v>0.5641883927056239</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0316419317600052</v>
+        <v>0.6934771305250688</v>
       </c>
       <c r="L29" t="n">
-        <v>-6.026509167893956</v>
+        <v>3.275568092324006</v>
       </c>
       <c r="M29" t="n">
-        <v>80.0500528620483</v>
+        <v>158.7061555948783</v>
       </c>
     </row>
     <row r="30">
@@ -1693,41 +1693,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.3129615485915495</v>
+        <v>0.372814260704828</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3091050383827527</v>
+        <v>0.1838363227554643</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2563566298710235</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1772340171034298</v>
+        <v>0.1355413876841164</v>
       </c>
       <c r="G30" t="n">
-        <v>9245.3287643366</v>
+        <v>9923.48932621966</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.996669046109148</v>
+        <v>3.599023251030427</v>
       </c>
       <c r="I30" t="n">
-        <v>2.483367926208256</v>
+        <v>-1.663598857480747</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.888751303224205</v>
+        <v>0.5743391165824226</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.07335071770079475</v>
+        <v>0.6293038682734385</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.475403140825892</v>
+        <v>3.139067378405542</v>
       </c>
       <c r="M30" t="n">
-        <v>75.33741032072567</v>
+        <v>162.5258826453052</v>
       </c>
     </row>
     <row r="31">
@@ -1736,41 +1736,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.3021973664003558</v>
+        <v>0.3599914693946423</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3152533159061113</v>
+        <v>0.1832263448740044</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2638489971836245</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1867425190998943</v>
+        <v>0.1313562194297666</v>
       </c>
       <c r="G31" t="n">
-        <v>9192.617572967429</v>
+        <v>9931.140393597694</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.46894429205035</v>
+        <v>3.543901529783929</v>
       </c>
       <c r="I31" t="n">
-        <v>2.598019917326149</v>
+        <v>-1.646598870449128</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.969634970807292</v>
+        <v>0.5437821335122358</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1167520173297008</v>
+        <v>0.5649646495606189</v>
       </c>
       <c r="L31" t="n">
-        <v>-6.957311362861194</v>
+        <v>3.006049442407656</v>
       </c>
       <c r="M31" t="n">
-        <v>70.55740953653695</v>
+        <v>166.2990932780192</v>
       </c>
     </row>
     <row r="32">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.5081965862250442</v>
+        <v>-0.4523902873460134</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3225150713434416</v>
+        <v>0.1829854549833314</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7803970263945357</v>
+        <v>0.3933485341766821</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1967284934085663</v>
+        <v>0.1268737995516686</v>
       </c>
       <c r="G32" t="n">
-        <v>9141.431317078874</v>
+        <v>9938.026354237925</v>
       </c>
       <c r="H32" t="n">
-        <v>-29.76875015981974</v>
+        <v>-12.80244618278454</v>
       </c>
       <c r="I32" t="n">
-        <v>8.999532735544296</v>
+        <v>3.411842118116737</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.36556787162761</v>
+        <v>-0.626753402872955</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.922989522248465</v>
+        <v>-0.9912828764460441</v>
       </c>
       <c r="L32" t="n">
-        <v>-26.05777481815151</v>
+        <v>-11.00864034398681</v>
       </c>
       <c r="M32" t="n">
-        <v>65.10443702958577</v>
+        <v>161.5991090602387</v>
       </c>
     </row>
     <row r="33">
@@ -1822,41 +1822,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.4907173761825081</v>
+        <v>-0.4368305117236274</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2041235173362581</v>
+        <v>-0.151775588277352</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7646374242749249</v>
+        <v>0.6023801379583863</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3786148442266549</v>
+        <v>0.1862106831708693</v>
       </c>
       <c r="G33" t="n">
-        <v>8837.089672173717</v>
+        <v>9747.549451725792</v>
       </c>
       <c r="H33" t="n">
-        <v>-30.41627296619822</v>
+        <v>-18.85087121720436</v>
       </c>
       <c r="I33" t="n">
-        <v>8.345200297531511</v>
+        <v>6.497836298066606</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.586308246709083</v>
+        <v>-2.350760297048842</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.029009285769783</v>
+        <v>-1.388649993581946</v>
       </c>
       <c r="L33" t="n">
-        <v>-27.68639020114557</v>
+        <v>-16.09244520976854</v>
       </c>
       <c r="M33" t="n">
-        <v>59.46881561626945</v>
+        <v>156.6277258392016</v>
       </c>
     </row>
     <row r="34">
@@ -1865,41 +1865,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.4738393562935316</v>
+        <v>-0.4218059081068991</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1717403787310549</v>
+        <v>-0.112831771053524</v>
       </c>
       <c r="E34" t="n">
-        <v>0.778496706951144</v>
+        <v>0.5985653155390963</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5040328085474487</v>
+        <v>0.2726508620002069</v>
       </c>
       <c r="G34" t="n">
-        <v>8571.061992818883</v>
+        <v>9471.60443757402</v>
       </c>
       <c r="H34" t="n">
-        <v>-31.79230997476768</v>
+        <v>-19.66386466045723</v>
       </c>
       <c r="I34" t="n">
-        <v>8.280738122157574</v>
+        <v>6.077629648261476</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.955428812358688</v>
+        <v>-2.543049054039896</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.15148082473412</v>
+        <v>-1.413175247251687</v>
       </c>
       <c r="L34" t="n">
-        <v>-29.61848148970292</v>
+        <v>-17.54245931348733</v>
       </c>
       <c r="M34" t="n">
-        <v>53.66404410276373</v>
+        <v>151.4968747599034</v>
       </c>
     </row>
     <row r="35">
@@ -1908,41 +1908,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.4575418488730328</v>
+        <v>-0.4072980694774631</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1630631633896677</v>
+        <v>-0.09662771544827389</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7948215469170328</v>
+        <v>0.6008807428804264</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5986045000254984</v>
+        <v>0.3390151103349975</v>
       </c>
       <c r="G35" t="n">
-        <v>8324.707440061422</v>
+        <v>9225.161336047069</v>
       </c>
       <c r="H35" t="n">
-        <v>-33.05397861990848</v>
+        <v>-20.80967902707849</v>
       </c>
       <c r="I35" t="n">
-        <v>8.333823333713308</v>
+        <v>6.041497442574101</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.299034049450731</v>
+        <v>-2.7858348007561</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.254791165400873</v>
+        <v>-1.327770539129056</v>
       </c>
       <c r="L35" t="n">
-        <v>-31.27398050104678</v>
+        <v>-18.88178692438954</v>
       </c>
       <c r="M35" t="n">
-        <v>47.67197469721556</v>
+        <v>146.2163504903455</v>
       </c>
     </row>
     <row r="36">
@@ -1951,41 +1951,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.4418048874363016</v>
+        <v>-0.393289221918689</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.166183222801184</v>
+        <v>-0.0888660659149634</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8102758231273186</v>
+        <v>0.6034996356456246</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6719025050257668</v>
+        <v>0.392226935444894</v>
       </c>
       <c r="G36" t="n">
-        <v>8094.825922596764</v>
+        <v>9002.204831002149</v>
       </c>
       <c r="H36" t="n">
-        <v>-34.14057424700994</v>
+        <v>-20.71348096951827</v>
       </c>
       <c r="I36" t="n">
-        <v>8.429149415754088</v>
+        <v>5.912986369683222</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.604423621871425</v>
+        <v>-2.915261649881848</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.339645433437292</v>
+        <v>-1.56160734041288</v>
       </c>
       <c r="L36" t="n">
-        <v>-32.65549388656457</v>
+        <v>-19.27736359012977</v>
       </c>
       <c r="M36" t="n">
-        <v>41.52342622436827</v>
+        <v>140.8124624884782</v>
       </c>
     </row>
     <row r="37">
@@ -1994,41 +1994,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.4266091922375572</v>
+        <v>-0.3797622028404101</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1767531778480879</v>
+        <v>-0.08632870634715389</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8245396756988523</v>
+        <v>0.6028033455159961</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7296964418811058</v>
+        <v>0.4281097971682341</v>
       </c>
       <c r="G37" t="n">
-        <v>7880.205418773428</v>
+        <v>8800.234530079122</v>
       </c>
       <c r="H37" t="n">
-        <v>-35.07864524898108</v>
+        <v>-21.06943007847561</v>
       </c>
       <c r="I37" t="n">
-        <v>8.546466562486865</v>
+        <v>5.707721789017106</v>
       </c>
       <c r="J37" t="n">
-        <v>-4.876947346853185</v>
+        <v>-3.054887001931874</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.409946759844573</v>
+        <v>-1.597924479471877</v>
       </c>
       <c r="L37" t="n">
-        <v>-33.81907279319197</v>
+        <v>-20.01451977086226</v>
       </c>
       <c r="M37" t="n">
-        <v>35.20573666643941</v>
+        <v>135.2824800952994</v>
       </c>
     </row>
     <row r="38">
@@ -2037,41 +2037,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.4119361466498507</v>
+        <v>-0.3667004399526046</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1960643210554641</v>
+        <v>-0.08593219979751958</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8399781765073625</v>
+        <v>0.6010641902349415</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7760085930605832</v>
+        <v>0.457011076009563</v>
       </c>
       <c r="G38" t="n">
-        <v>7679.915039046659</v>
+        <v>8618.809404313211</v>
       </c>
       <c r="H38" t="n">
-        <v>-35.98332768114561</v>
+        <v>-20.83481608489528</v>
       </c>
       <c r="I38" t="n">
-        <v>8.710111325938865</v>
+        <v>5.743750556414533</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.140205979621401</v>
+        <v>-3.135836621247416</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.473741662589735</v>
+        <v>-1.36516062020394</v>
       </c>
       <c r="L38" t="n">
-        <v>-34.88716399741788</v>
+        <v>-19.59206276993211</v>
       </c>
       <c r="M38" t="n">
-        <v>28.7277978208684</v>
+        <v>129.6507285041121</v>
       </c>
     </row>
     <row r="39">
@@ -2080,41 +2080,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.397767774357367</v>
+        <v>-0.3540879309622675</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2259148044587549</v>
+        <v>-0.0885495763028616</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8591073753568315</v>
+        <v>0.595268586066008</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8144767958105288</v>
+        <v>0.4701272733050589</v>
       </c>
       <c r="G39" t="n">
-        <v>7491.934446888312</v>
+        <v>8456.396368764419</v>
       </c>
       <c r="H39" t="n">
-        <v>-36.97283028624874</v>
+        <v>-20.19253922219737</v>
       </c>
       <c r="I39" t="n">
-        <v>8.947697689213182</v>
+        <v>5.679930555880334</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.418441550791334</v>
+        <v>-3.246316784146357</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.539083272839313</v>
+        <v>-1.436804304930771</v>
       </c>
       <c r="L39" t="n">
-        <v>-35.98265742066621</v>
+        <v>-19.19572975539417</v>
       </c>
       <c r="M39" t="n">
-        <v>22.08554070327521</v>
+        <v>123.9289093289177</v>
       </c>
     </row>
     <row r="40">
@@ -2123,41 +2123,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.3840867173321911</v>
+        <v>-0.3419092239686008</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2724927958815838</v>
+        <v>-0.09310006517765554</v>
       </c>
       <c r="E40" t="n">
-        <v>0.886987455538333</v>
+        <v>0.5873827276899849</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8485126516929793</v>
+        <v>0.474033661536977</v>
       </c>
       <c r="G40" t="n">
-        <v>7313.187314521066</v>
+        <v>8313.122438854973</v>
       </c>
       <c r="H40" t="n">
-        <v>-38.25883372827474</v>
+        <v>-21.14336309637715</v>
       </c>
       <c r="I40" t="n">
-        <v>9.325228349977827</v>
+        <v>5.740753069230189</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.755095963168779</v>
+        <v>-3.252077605312701</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.619082489061871</v>
+        <v>-1.578925979374565</v>
       </c>
       <c r="L40" t="n">
-        <v>-37.30778383052756</v>
+        <v>-20.23361361183422</v>
       </c>
       <c r="M40" t="n">
-        <v>15.25469605143623</v>
+        <v>118.1072007491779</v>
       </c>
     </row>
     <row r="41">
@@ -2166,41 +2166,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.3708762145685527</v>
+        <v>-0.3301493985325023</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3505956247189698</v>
+        <v>-0.09650864623815968</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9341077611283599</v>
+        <v>0.5827571194916095</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8821854293210631</v>
+        <v>0.4867563330405284</v>
       </c>
       <c r="G41" t="n">
-        <v>7138.374855299792</v>
+        <v>8188.118831124483</v>
       </c>
       <c r="H41" t="n">
-        <v>-40.26009099150776</v>
+        <v>-20.27509822055644</v>
       </c>
       <c r="I41" t="n">
-        <v>9.987550924586634</v>
+        <v>5.693436422007673</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.236108191857047</v>
+        <v>-3.144408424864499</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.738546074481757</v>
+        <v>-1.544021238676996</v>
       </c>
       <c r="L41" t="n">
-        <v>-39.24719433325993</v>
+        <v>-19.27009146209026</v>
       </c>
       <c r="M41" t="n">
-        <v>8.236474827461887</v>
+        <v>112.2181272116428</v>
       </c>
     </row>
     <row r="42">
@@ -2209,41 +2209,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.3581200815484978</v>
+        <v>-0.318794047397162</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4991082008585165</v>
+        <v>-0.1028604830529064</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.5744122230069937</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9217832009252371</v>
+        <v>0.4847547144452196</v>
       </c>
       <c r="G42" t="n">
-        <v>6957.483489205633</v>
+        <v>8077.92838826623</v>
       </c>
       <c r="H42" t="n">
-        <v>-43.35170499655295</v>
+        <v>-20.39365661208092</v>
       </c>
       <c r="I42" t="n">
-        <v>11.08831243365794</v>
+        <v>5.68635669506325</v>
       </c>
       <c r="J42" t="n">
-        <v>-7.04168568868351</v>
+        <v>-3.172062928196368</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.943122007076199</v>
+        <v>-1.417675970740699</v>
       </c>
       <c r="L42" t="n">
-        <v>-42.24820025865473</v>
+        <v>-19.29703881595474</v>
       </c>
       <c r="M42" t="n">
-        <v>1.004024786944092</v>
+        <v>106.2593061001598</v>
       </c>
     </row>
     <row r="43">
@@ -2252,41 +2252,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.3458026904138309</v>
+        <v>-0.3078292588373711</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.9001060431760373</v>
+        <v>-0.1097515409326269</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.5672094701276188</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9755519231416896</v>
+        <v>0.4838232168266791</v>
       </c>
       <c r="G43" t="n">
-        <v>6761.73514028507</v>
+        <v>7982.929437936111</v>
       </c>
       <c r="H43" t="n">
-        <v>-47.05710370807453</v>
+        <v>-19.85829532860398</v>
       </c>
       <c r="I43" t="n">
-        <v>12.6790967389803</v>
+        <v>5.585341080942801</v>
       </c>
       <c r="J43" t="n">
-        <v>-8.848434555684738</v>
+        <v>-3.230570712204374</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.377287343280422</v>
+        <v>-1.545106222844742</v>
       </c>
       <c r="L43" t="n">
-        <v>-46.60372886805939</v>
+        <v>-19.0486311827103</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01</v>
+        <v>100.2499038134538</v>
       </c>
     </row>
     <row r="44">
@@ -2295,41 +2295,41 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.3339089508200336</v>
+        <v>-0.2972415996159179</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.9416680646355987</v>
+        <v>-0.1176298899531141</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.5601316303570306</v>
       </c>
       <c r="F44" t="n">
-        <v>1.051368442565608</v>
+        <v>0.4807802419231104</v>
       </c>
       <c r="G44" t="n">
-        <v>6585.561626256563</v>
+        <v>7901.031759078691</v>
       </c>
       <c r="H44" t="n">
-        <v>-22.4506341488974</v>
+        <v>-19.97525458237191</v>
       </c>
       <c r="I44" t="n">
-        <v>12.81530982898827</v>
+        <v>5.331261656532018</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.306054979624863</v>
+        <v>-3.229037543514802</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.502211698617874</v>
+        <v>-1.36300923529851</v>
       </c>
       <c r="L44" t="n">
-        <v>-22.44359099815188</v>
+        <v>-19.2360397046532</v>
       </c>
       <c r="M44" t="n">
-        <v>0.01</v>
+        <v>94.18580122585136</v>
       </c>
     </row>
     <row r="45">
@@ -2338,41 +2338,41 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.3224242914487058</v>
+        <v>-0.2870180985261932</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>-0.1258033874898242</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6645270816570592</v>
+        <v>0.554831547900247</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8552569755208834</v>
+        <v>0.4808285422003983</v>
       </c>
       <c r="G45" t="n">
-        <v>6427.005463630907</v>
+        <v>7830.862767992307</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-19.72758626008873</v>
       </c>
       <c r="I45" t="n">
-        <v>6.253214948333686</v>
+        <v>5.396593245844348</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.407979275189299</v>
+        <v>-3.178274804499448</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.146997707656903</v>
+        <v>-1.454782358039411</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.3017620345125156</v>
+        <v>-18.96405017678324</v>
       </c>
       <c r="M45" t="n">
-        <v>0.01</v>
+        <v>88.07933851345904</v>
       </c>
     </row>
     <row r="46">
@@ -2381,41 +2381,41 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.3113346421558785</v>
+        <v>-0.27714623050084</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-0.1355973964900053</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5178033644189406</v>
+        <v>0.5497597192300717</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5161718056576552</v>
+        <v>0.4781376270880714</v>
       </c>
       <c r="G46" t="n">
-        <v>6452.041376439287</v>
+        <v>7770.360717242953</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>-19.79167003467731</v>
       </c>
       <c r="I46" t="n">
-        <v>5.034810785614291</v>
+        <v>5.52077669554891</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.893825229205439</v>
+        <v>-3.221167964455383</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.573037241257325</v>
+        <v>-1.516136653698422</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5679483151515279</v>
+        <v>-19.0081979572822</v>
       </c>
       <c r="M46" t="n">
-        <v>2.777482766840421</v>
+        <v>81.91986433892284</v>
       </c>
     </row>
     <row r="47">
@@ -2424,41 +2424,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.3006264167343276</v>
+        <v>-0.2676139012669791</v>
       </c>
       <c r="D47" t="n">
-        <v>877.500236347344</v>
+        <v>-0.14661671586473</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.546369753116083</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3153825665461084</v>
+        <v>0.4769645558256648</v>
       </c>
       <c r="G47" t="n">
-        <v>6547.935556585889</v>
+        <v>7718.444785903622</v>
       </c>
       <c r="H47" t="n">
-        <v>7012.609782979382</v>
+        <v>-19.18509258432118</v>
       </c>
       <c r="I47" t="n">
-        <v>-648.049618660777</v>
+        <v>5.348257409559563</v>
       </c>
       <c r="J47" t="n">
-        <v>3508.438788706459</v>
+        <v>-3.23848714602016</v>
       </c>
       <c r="K47" t="n">
-        <v>832.6046141808534</v>
+        <v>-1.360984812066302</v>
       </c>
       <c r="L47" t="n">
-        <v>10705.60356720592</v>
+        <v>-18.43630713284808</v>
       </c>
       <c r="M47" t="n">
-        <v>11.10153995727066</v>
+        <v>75.7420568773959</v>
       </c>
     </row>
     <row r="48">
@@ -2467,41 +2467,41 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.290286496268771</v>
+        <v>-0.2584094325292127</v>
       </c>
       <c r="D48" t="n">
-        <v>0.02794509271424102</v>
+        <v>-0.1602680417579939</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0.5427869795135608</v>
       </c>
       <c r="F48" t="n">
-        <v>107.2452652119868</v>
+        <v>0.4705418048238796</v>
       </c>
       <c r="G48" t="n">
-        <v>6893.1420009273</v>
+        <v>7673.415430755218</v>
       </c>
       <c r="H48" t="n">
-        <v>-1314.203059757354</v>
+        <v>-20.17739640906662</v>
       </c>
       <c r="I48" t="n">
-        <v>8.770595914433006</v>
+        <v>5.342300808897448</v>
       </c>
       <c r="J48" t="n">
-        <v>-430.1595669733591</v>
+        <v>-3.329142273264792</v>
       </c>
       <c r="K48" t="n">
-        <v>-153.8244994319134</v>
+        <v>-1.525177386989814</v>
       </c>
       <c r="L48" t="n">
-        <v>-1889.416530248193</v>
+        <v>-19.68941526042378</v>
       </c>
       <c r="M48" t="n">
-        <v>2.812647504027556</v>
+        <v>69.50482733683812</v>
       </c>
     </row>
     <row r="49">
@@ -2510,41 +2510,41 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.2803022130635571</v>
+        <v>-0.2495215476622519</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.008969625212891744</v>
+        <v>-0.1718384672818029</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0.5443123222307599</v>
       </c>
       <c r="F49" t="n">
-        <v>83.24132442967404</v>
+        <v>0.4792192354985656</v>
       </c>
       <c r="G49" t="n">
-        <v>6703.82780083457</v>
+        <v>7634.680397922915</v>
       </c>
       <c r="H49" t="n">
-        <v>-1026.331276714553</v>
+        <v>-19.72858244207124</v>
       </c>
       <c r="I49" t="n">
-        <v>8.893142957383814</v>
+        <v>5.61572141137388</v>
       </c>
       <c r="J49" t="n">
-        <v>-334.2814784326113</v>
+        <v>-3.359458608248911</v>
       </c>
       <c r="K49" t="n">
-        <v>-119.6349826610585</v>
+        <v>-1.571452025319822</v>
       </c>
       <c r="L49" t="n">
-        <v>-1471.354594850839</v>
+        <v>-19.04377166426609</v>
       </c>
       <c r="M49" t="n">
-        <v>0.01</v>
+        <v>63.25929282710329</v>
       </c>
     </row>
     <row r="50">
@@ -2553,41 +2553,41 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.2706613351231533</v>
+        <v>-0.240939357895641</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.01541092180165858</v>
+        <v>-0.1879986276693534</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.5449262376739731</v>
       </c>
       <c r="F50" t="n">
-        <v>64.65834060631282</v>
+        <v>0.4779692579418002</v>
       </c>
       <c r="G50" t="n">
-        <v>6533.445020751113</v>
+        <v>7599.056197015244</v>
       </c>
       <c r="H50" t="n">
-        <v>-803.2713106716454</v>
+        <v>-19.80384179843477</v>
       </c>
       <c r="I50" t="n">
-        <v>8.893199838129231</v>
+        <v>5.371496275488852</v>
       </c>
       <c r="J50" t="n">
-        <v>-259.965667447581</v>
+        <v>-3.481043475626199</v>
       </c>
       <c r="K50" t="n">
-        <v>-93.14203227644134</v>
+        <v>-1.314837595841458</v>
       </c>
       <c r="L50" t="n">
-        <v>-1147.485810557539</v>
+        <v>-19.22822659441358</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01</v>
+        <v>56.98300706144302</v>
       </c>
     </row>
     <row r="51">
@@ -2596,41 +2596,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.261352051166421</v>
+        <v>-0.2326523489736513</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>-0.2071023384988598</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0.5485392803566536</v>
       </c>
       <c r="F51" t="n">
-        <v>50.26986246936308</v>
+        <v>0.4790638207092159</v>
       </c>
       <c r="G51" t="n">
-        <v>6380.100518676001</v>
+        <v>7566.687458476733</v>
       </c>
       <c r="H51" t="n">
-        <v>-630.3745742463543</v>
+        <v>-19.74652274783305</v>
       </c>
       <c r="I51" t="n">
-        <v>8.805650538149335</v>
+        <v>5.715197822364983</v>
       </c>
       <c r="J51" t="n">
-        <v>-202.3408019286187</v>
+        <v>-3.46272520705438</v>
       </c>
       <c r="K51" t="n">
-        <v>-72.60612291605858</v>
+        <v>-1.509488913930533</v>
       </c>
       <c r="L51" t="n">
-        <v>-896.5158485528823</v>
+        <v>-19.00353904645298</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01</v>
+        <v>50.67642535992832</v>
       </c>
     </row>
     <row r="52">
@@ -2639,41 +2639,41 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.2523629561563208</v>
+        <v>-0.2246503682740031</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>-0.2317924165445613</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0.5547152913567637</v>
       </c>
       <c r="F52" t="n">
-        <v>39.12707596714667</v>
+        <v>0.4774736828900593</v>
       </c>
       <c r="G52" t="n">
-        <v>6242.090466808401</v>
+        <v>7535.749072450732</v>
       </c>
       <c r="H52" t="n">
-        <v>-496.5532670796362</v>
+        <v>-20.00759849442262</v>
       </c>
       <c r="I52" t="n">
-        <v>8.781379981622063</v>
+        <v>5.560036631685492</v>
       </c>
       <c r="J52" t="n">
-        <v>-157.7606668247429</v>
+        <v>-3.640468685004988</v>
       </c>
       <c r="K52" t="n">
-        <v>-56.71057286988101</v>
+        <v>-1.374691633065545</v>
       </c>
       <c r="L52" t="n">
-        <v>-702.2431267926381</v>
+        <v>-19.46272218080767</v>
       </c>
       <c r="M52" t="n">
-        <v>0.01</v>
+        <v>44.34439708808146</v>
       </c>
     </row>
     <row r="53">
@@ -2682,41 +2682,41 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.2436830373273141</v>
+        <v>-0.2169236123696343</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>-0.2597115094103403</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0.5651950906326835</v>
       </c>
       <c r="F53" t="n">
-        <v>30.49867684821438</v>
+        <v>0.4811114315421123</v>
       </c>
       <c r="G53" t="n">
-        <v>6117.881420127561</v>
+        <v>7504.816519527277</v>
       </c>
       <c r="H53" t="n">
-        <v>-392.9083186264999</v>
+        <v>-20.32928203548345</v>
       </c>
       <c r="I53" t="n">
-        <v>8.757944200783749</v>
+        <v>5.956907784878978</v>
       </c>
       <c r="J53" t="n">
-        <v>-123.2383904301848</v>
+        <v>-3.836561556690926</v>
       </c>
       <c r="K53" t="n">
-        <v>-44.39861227962738</v>
+        <v>-1.48283296895041</v>
       </c>
       <c r="L53" t="n">
-        <v>-551.7873771355283</v>
+        <v>-19.69176877624581</v>
       </c>
       <c r="M53" t="n">
-        <v>0.01</v>
+        <v>37.97877815031804</v>
       </c>
     </row>
     <row r="54">
@@ -2725,41 +2725,41 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.2353016606933493</v>
+        <v>-0.2094626150182758</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>-0.2956221868180877</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0.5810697457842185</v>
       </c>
       <c r="F54" t="n">
-        <v>23.81707988028391</v>
+        <v>0.4855845466877254</v>
       </c>
       <c r="G54" t="n">
-        <v>6006.093278114805</v>
+        <v>7471.737322258207</v>
       </c>
       <c r="H54" t="n">
-        <v>-312.6285784917269</v>
+        <v>-20.71008044600415</v>
       </c>
       <c r="I54" t="n">
-        <v>8.735314483872044</v>
+        <v>6.061624418631421</v>
       </c>
       <c r="J54" t="n">
-        <v>-96.50362118182903</v>
+        <v>-3.837269597543254</v>
       </c>
       <c r="K54" t="n">
-        <v>-34.86141198472193</v>
+        <v>-1.420885401147645</v>
       </c>
       <c r="L54" t="n">
-        <v>-435.2582971744058</v>
+        <v>-19.90661102606363</v>
       </c>
       <c r="M54" t="n">
-        <v>0.01</v>
+        <v>31.57964671183564</v>
       </c>
     </row>
     <row r="55">
@@ -2768,41 +2768,41 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.2272085580198982</v>
+        <v>-0.2022582355651206</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>-0.3435695523592577</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0.6045667022899838</v>
       </c>
       <c r="F55" t="n">
-        <v>18.6428308999144</v>
+        <v>0.4904168382732715</v>
       </c>
       <c r="G55" t="n">
-        <v>5905.483950303324</v>
+        <v>7434.028717140278</v>
       </c>
       <c r="H55" t="n">
-        <v>-250.4404734952118</v>
+        <v>-20.89507868022617</v>
       </c>
       <c r="I55" t="n">
-        <v>8.713463106653727</v>
+        <v>6.527852628327554</v>
       </c>
       <c r="J55" t="n">
-        <v>-75.79853215767754</v>
+        <v>-4.160612400917737</v>
       </c>
       <c r="K55" t="n">
-        <v>-27.47273029261583</v>
+        <v>-1.619223681743943</v>
       </c>
       <c r="L55" t="n">
-        <v>-344.9982728388514</v>
+        <v>-20.14706213456029</v>
       </c>
       <c r="M55" t="n">
-        <v>0.01</v>
+        <v>25.13680564131991</v>
       </c>
     </row>
     <row r="56">
@@ -2811,41 +2811,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.2193938142440852</v>
+        <v>-0.1953016477443792</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>-0.4115599215184635</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0.6405258903792836</v>
       </c>
       <c r="F56" t="n">
-        <v>14.63568126833716</v>
+        <v>0.4957207243095659</v>
       </c>
       <c r="G56" t="n">
-        <v>5814.935555272992</v>
+        <v>7388.342494281258</v>
       </c>
       <c r="H56" t="n">
-        <v>-202.2609009909748</v>
+        <v>-22.47463246923616</v>
       </c>
       <c r="I56" t="n">
-        <v>8.692363298459028</v>
+        <v>7.074346480319852</v>
       </c>
       <c r="J56" t="n">
-        <v>-59.7621188875927</v>
+        <v>-4.464514053449682</v>
       </c>
       <c r="K56" t="n">
-        <v>-21.7476940544442</v>
+        <v>-1.761503522647113</v>
       </c>
       <c r="L56" t="n">
-        <v>-275.0783506345526</v>
+        <v>-21.6263035650131</v>
       </c>
       <c r="M56" t="n">
-        <v>0.01</v>
+        <v>18.61073358629342</v>
       </c>
     </row>
     <row r="57">
@@ -2854,41 +2854,41 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.2118478553274951</v>
+        <v>-0.1885843288659999</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>-0.505400935260617</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.6973030781167183</v>
       </c>
       <c r="F57" t="n">
-        <v>11.53219226734782</v>
+        <v>0.5136954702358706</v>
       </c>
       <c r="G57" t="n">
-        <v>5733.441999745693</v>
+        <v>7329.24529966349</v>
       </c>
       <c r="H57" t="n">
-        <v>-164.9284814721038</v>
+        <v>-24.81507082722591</v>
       </c>
       <c r="I57" t="n">
-        <v>8.67198920938424</v>
+        <v>7.752183819094636</v>
       </c>
       <c r="J57" t="n">
-        <v>-47.34061692471877</v>
+        <v>-4.95669770351566</v>
       </c>
       <c r="K57" t="n">
-        <v>-17.31088490609288</v>
+        <v>-1.783867273605719</v>
       </c>
       <c r="L57" t="n">
-        <v>-220.9079940935312</v>
+        <v>-23.80345198525265</v>
       </c>
       <c r="M57" t="n">
-        <v>0.01</v>
+        <v>11.99749491118305</v>
       </c>
     </row>
     <row r="58">
@@ -2897,41 +2897,41 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.2045614365267787</v>
+        <v>-0.1820980493743076</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>-0.6505157590748637</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0.7909082256168454</v>
       </c>
       <c r="F58" t="n">
-        <v>9.128395301344005</v>
+        <v>0.5462518019940488</v>
       </c>
       <c r="G58" t="n">
-        <v>5660.097799771123</v>
+        <v>7247.669230638782</v>
       </c>
       <c r="H58" t="n">
-        <v>-135.9954808544494</v>
+        <v>-27.76303411661754</v>
       </c>
       <c r="I58" t="n">
-        <v>8.652315878622304</v>
+        <v>9.040387331365361</v>
       </c>
       <c r="J58" t="n">
-        <v>-37.71814264190282</v>
+        <v>-5.61679079765811</v>
       </c>
       <c r="K58" t="n">
-        <v>-13.87163003381609</v>
+        <v>-1.684925583811379</v>
       </c>
       <c r="L58" t="n">
-        <v>-178.932937651546</v>
+        <v>-26.02436316672167</v>
       </c>
       <c r="M58" t="n">
-        <v>0.01</v>
+        <v>5.235607692289728</v>
       </c>
     </row>
     <row r="59">
@@ -2940,38 +2940,38 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-0.1975256310676859</v>
+        <v>-0.1758348627657692</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>-0.9585260660340319</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.9861483875316468</v>
       </c>
       <c r="F59" t="n">
-        <v>7.266366557321863</v>
+        <v>0.587994712863646</v>
       </c>
       <c r="G59" t="n">
-        <v>5594.088019794011</v>
+        <v>7127.448194766481</v>
       </c>
       <c r="H59" t="n">
-        <v>-113.5667062606745</v>
+        <v>-33.9200229261997</v>
       </c>
       <c r="I59" t="n">
-        <v>8.633319203882753</v>
+        <v>11.65571604268671</v>
       </c>
       <c r="J59" t="n">
-        <v>-30.26299186035513</v>
+        <v>-7.004391470640032</v>
       </c>
       <c r="K59" t="n">
-        <v>-11.20487104321226</v>
+        <v>-2.240622049478463</v>
       </c>
       <c r="L59" t="n">
-        <v>-146.4012499603591</v>
+        <v>-31.50932040363148</v>
       </c>
       <c r="M59" t="n">
         <v>0.01</v>
@@ -2983,38 +2983,38 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.1907318192086513</v>
+        <v>-0.1697870958535327</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>-1.494392721239313</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>5.823832433996708</v>
+        <v>0.6678900317545025</v>
       </c>
       <c r="G60" t="n">
-        <v>5534.679217814611</v>
+        <v>6921.629181524009</v>
       </c>
       <c r="H60" t="n">
-        <v>-96.17477103846427</v>
+        <v>-38.98456132034288</v>
       </c>
       <c r="I60" t="n">
-        <v>8.614975911863358</v>
+        <v>13.5609686622817</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.4860615551955</v>
+        <v>-9.79556761566856</v>
       </c>
       <c r="K60" t="n">
-        <v>-9.136351674941746</v>
+        <v>-3.166995123189411</v>
       </c>
       <c r="L60" t="n">
-        <v>-121.1822083567382</v>
+        <v>-38.38615539691915</v>
       </c>
       <c r="M60" t="n">
         <v>0.01</v>
@@ -3026,38 +3026,38 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.1841716776805327</v>
+        <v>-0.1639473393668137</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0.4777855685755709</v>
       </c>
       <c r="F61" t="n">
-        <v>4.706121543965406</v>
+        <v>0.784595573021893</v>
       </c>
       <c r="G61" t="n">
-        <v>5481.21129603315</v>
+        <v>6729.466263371608</v>
       </c>
       <c r="H61" t="n">
-        <v>-82.68351865975133</v>
+        <v>-19.83739109770651</v>
       </c>
       <c r="I61" t="n">
-        <v>8.597263529737438</v>
+        <v>4.005190670118395</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.00865785354217</v>
+        <v>-3.922063204480237</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.531149387743715</v>
+        <v>-1.336182184576543</v>
       </c>
       <c r="L61" t="n">
-        <v>-101.6260623712998</v>
+        <v>-21.09044581664489</v>
       </c>
       <c r="M61" t="n">
         <v>0.01</v>
@@ -3069,38 +3069,38 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.1778371694895652</v>
+        <v>-0.6783582395846885</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0.9510229603765225</v>
       </c>
       <c r="F62" t="n">
-        <v>3.839933550092241</v>
+        <v>0.6816618019795847</v>
       </c>
       <c r="G62" t="n">
-        <v>5433.090166429834</v>
+        <v>6817.626852746662</v>
       </c>
       <c r="H62" t="n">
-        <v>-72.2132486349817</v>
+        <v>-33.7179099592189</v>
       </c>
       <c r="I62" t="n">
-        <v>8.580160357621825</v>
+        <v>8.96577585542645</v>
       </c>
       <c r="J62" t="n">
-        <v>-16.53757136985853</v>
+        <v>-4.403538551208298</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.284795930911617</v>
+        <v>-2.399122663503443</v>
       </c>
       <c r="L62" t="n">
-        <v>-86.45545557813001</v>
+        <v>-31.55479531850419</v>
       </c>
       <c r="M62" t="n">
         <v>0.01</v>
@@ -3112,38 +3112,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.1717205340710389</v>
+        <v>-0.6550263903059231</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.9448444040550402</v>
       </c>
       <c r="F63" t="n">
-        <v>3.168514685836645</v>
+        <v>0.7245450343727927</v>
       </c>
       <c r="G63" t="n">
-        <v>5389.781149786851</v>
+        <v>6660.352687283735</v>
       </c>
       <c r="H63" t="n">
-        <v>-64.08282263889224</v>
+        <v>-33.03879445433884</v>
       </c>
       <c r="I63" t="n">
-        <v>8.563645441991806</v>
+        <v>8.775843456344807</v>
       </c>
       <c r="J63" t="n">
-        <v>-13.84577927741763</v>
+        <v>-4.51164723869297</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.316402442052192</v>
+        <v>-2.375902246462719</v>
       </c>
       <c r="L63" t="n">
-        <v>-74.68135891637024</v>
+        <v>-31.15050048314972</v>
       </c>
       <c r="M63" t="n">
         <v>0.01</v>
@@ -3155,38 +3155,38 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-0.1658142777816372</v>
+        <v>-0.6324970302710422</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0.9309898404531114</v>
       </c>
       <c r="F64" t="n">
-        <v>2.647922400665689</v>
+        <v>0.7462320254551729</v>
       </c>
       <c r="G64" t="n">
-        <v>5350.803034808166</v>
+        <v>6521.895216527841</v>
       </c>
       <c r="H64" t="n">
-        <v>-57.76484014136791</v>
+        <v>-32.5501318938768</v>
       </c>
       <c r="I64" t="n">
-        <v>8.54769855001042</v>
+        <v>8.828646481545986</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.7575038804444</v>
+        <v>-4.528000016328138</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.563336548733718</v>
+        <v>-2.635842742245273</v>
       </c>
       <c r="L64" t="n">
-        <v>-65.53798202053559</v>
+        <v>-30.88532817090422</v>
       </c>
       <c r="M64" t="n">
         <v>0.01</v>
@@ -3198,38 +3198,38 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.1601111647187855</v>
+        <v>-0.6107425581965442</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0.9133795569894027</v>
       </c>
       <c r="F65" t="n">
-        <v>2.244133260604769</v>
+        <v>0.756592496982146</v>
       </c>
       <c r="G65" t="n">
-        <v>5315.722731327349</v>
+        <v>6404.210774648501</v>
       </c>
       <c r="H65" t="n">
-        <v>-52.85093310388263</v>
+        <v>-31.74711588245246</v>
       </c>
       <c r="I65" t="n">
-        <v>8.53230014474072</v>
+        <v>8.633207300053595</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.13664420713787</v>
+        <v>-4.611230059910187</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.977101109327488</v>
+        <v>-2.376580520106641</v>
       </c>
       <c r="L65" t="n">
-        <v>-58.43237827560726</v>
+        <v>-30.10171916241569</v>
       </c>
       <c r="M65" t="n">
         <v>0.01</v>
@@ -3241,38 +3241,38 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-0.1546042078557667</v>
+        <v>-0.5897363221335852</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9269257035033404</v>
+        <v>0.891725398058963</v>
       </c>
       <c r="F66" t="n">
-        <v>1.930803739118934</v>
+        <v>0.7549726898134446</v>
       </c>
       <c r="G66" t="n">
-        <v>5284.150458194614</v>
+        <v>6307.099918688949</v>
       </c>
       <c r="H66" t="n">
-        <v>-47.27111224777654</v>
+        <v>-32.70323019488668</v>
       </c>
       <c r="I66" t="n">
-        <v>7.925529559587631</v>
+        <v>8.318103676895714</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.804744867834843</v>
+        <v>-4.548802158779874</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.485433032334524</v>
+        <v>-2.158675091389358</v>
       </c>
       <c r="L66" t="n">
-        <v>-51.63576058835828</v>
+        <v>-31.0926037681602</v>
       </c>
       <c r="M66" t="n">
         <v>0.01</v>
@@ -3284,38 +3284,38 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.1492866604817389</v>
+        <v>-0.5694525868160069</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8192226002237162</v>
+        <v>0.8750164474438744</v>
       </c>
       <c r="F67" t="n">
-        <v>1.674839849354943</v>
+        <v>0.7639096515696687</v>
       </c>
       <c r="G67" t="n">
-        <v>5292.272560623482</v>
+        <v>6230.527227790573</v>
       </c>
       <c r="H67" t="n">
-        <v>-41.55086052340938</v>
+        <v>-31.35808416851622</v>
       </c>
       <c r="I67" t="n">
-        <v>7.038777045112798</v>
+        <v>8.253797219734132</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.66786865812523</v>
+        <v>-4.509548900920925</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.059422175352363</v>
+        <v>-2.580640259450209</v>
       </c>
       <c r="L67" t="n">
-        <v>-45.23937431177417</v>
+        <v>-30.19447610915322</v>
       </c>
       <c r="M67" t="n">
         <v>0.01</v>
@@ -3327,38 +3327,38 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.1441520079361714</v>
+        <v>-0.5498665021314183</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7270710690284545</v>
+        <v>0.8539827229447516</v>
       </c>
       <c r="F68" t="n">
-        <v>1.457297652730708</v>
+        <v>0.7602905520333334</v>
       </c>
       <c r="G68" t="n">
-        <v>5353.434004449276</v>
+        <v>6169.966281289579</v>
       </c>
       <c r="H68" t="n">
-        <v>-36.66710158468546</v>
+        <v>-29.85635991158985</v>
       </c>
       <c r="I68" t="n">
-        <v>6.278486080558142</v>
+        <v>7.820406968547336</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.700413687887454</v>
+        <v>-4.399816264960658</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.6958967280085</v>
+        <v>-2.002046170236864</v>
       </c>
       <c r="L68" t="n">
-        <v>-39.78492592002328</v>
+        <v>-28.43781537824004</v>
       </c>
       <c r="M68" t="n">
         <v>0.01</v>
@@ -3370,38 +3370,38 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.1391939596275709</v>
+        <v>-0.5309540726767001</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6480850999630339</v>
+        <v>0.8271750666776603</v>
       </c>
       <c r="F69" t="n">
-        <v>1.272227850838658</v>
+        <v>0.7405524850024003</v>
       </c>
       <c r="G69" t="n">
-        <v>5454.555069490121</v>
+        <v>6125.978291688245</v>
       </c>
       <c r="H69" t="n">
-        <v>-32.49110412470754</v>
+        <v>-29.87242368842933</v>
       </c>
       <c r="I69" t="n">
-        <v>5.625313000695016</v>
+        <v>7.810495365425036</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.876190462945232</v>
+        <v>-4.461051935118359</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.385233633219913</v>
+        <v>-2.043411990138225</v>
       </c>
       <c r="L69" t="n">
-        <v>-35.12721522017767</v>
+        <v>-28.56639224826087</v>
       </c>
       <c r="M69" t="n">
         <v>0.01</v>
@@ -3413,38 +3413,38 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1344064413267195</v>
+        <v>-0.5126921283606354</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5802499864087081</v>
+        <v>0.804690293754255</v>
       </c>
       <c r="F70" t="n">
-        <v>1.114608862704971</v>
+        <v>0.7299954134840489</v>
       </c>
       <c r="G70" t="n">
-        <v>5585.057012559591</v>
+        <v>6099.79292918059</v>
       </c>
       <c r="H70" t="n">
-        <v>-28.91418332218926</v>
+        <v>-30.25674198286794</v>
       </c>
       <c r="I70" t="n">
-        <v>5.062922281492677</v>
+        <v>7.415589703511766</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.173091878555311</v>
+        <v>-4.216692203883072</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.119308611419487</v>
+        <v>-2.03630938984347</v>
       </c>
       <c r="L70" t="n">
-        <v>-31.14366153067138</v>
+        <v>-29.09415387308272</v>
       </c>
       <c r="M70" t="n">
         <v>0.01</v>
@@ -3456,38 +3456,38 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-0.1297835877249852</v>
+        <v>-0.4950582960176489</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5218643608968638</v>
+        <v>0.7866338107461515</v>
       </c>
       <c r="F71" t="n">
-        <v>0.9802019329296966</v>
+        <v>0.7289387868212565</v>
       </c>
       <c r="G71" t="n">
-        <v>5736.426318099278</v>
+        <v>6087.468489385404</v>
       </c>
       <c r="H71" t="n">
-        <v>-25.84457090938093</v>
+        <v>-28.98576109625762</v>
       </c>
       <c r="I71" t="n">
-        <v>4.577517010122056</v>
+        <v>7.403786940720227</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.572455680340636</v>
+        <v>-4.161198820202999</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.8912621425283</v>
+        <v>-2.341554356752769</v>
       </c>
       <c r="L71" t="n">
-        <v>-27.73077172212781</v>
+        <v>-28.08472733249316</v>
       </c>
       <c r="M71" t="n">
         <v>0.01</v>
@@ -3499,38 +3499,38 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.1253197352485847</v>
+        <v>-0.4780309719978834</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4714912860402232</v>
+        <v>0.7653151901649576</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8654288769790961</v>
+        <v>0.7182105454176855</v>
       </c>
       <c r="G72" t="n">
-        <v>5901.851505840919</v>
+        <v>6085.404735073788</v>
       </c>
       <c r="H72" t="n">
-        <v>-23.20477421169754</v>
+        <v>-27.93506141350417</v>
       </c>
       <c r="I72" t="n">
-        <v>4.157442702096985</v>
+        <v>7.174361753483435</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.058526529205195</v>
+        <v>-4.054416168344997</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.695302007536629</v>
+        <v>-1.859217176682098</v>
       </c>
       <c r="L72" t="n">
-        <v>-24.80116004634238</v>
+        <v>-26.67433300504782</v>
       </c>
       <c r="M72" t="n">
         <v>0.01</v>
@@ -3542,38 +3542,38 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.1210094151199977</v>
+        <v>-0.4615892957000254</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4279169857803503</v>
+        <v>0.7406571586204611</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7672689266508814</v>
+        <v>0.6976696573010894</v>
       </c>
       <c r="G73" t="n">
-        <v>6075.920712236715</v>
+        <v>6094.20666648393</v>
       </c>
       <c r="H73" t="n">
-        <v>-20.92934775997896</v>
+        <v>-26.37548155573994</v>
       </c>
       <c r="I73" t="n">
-        <v>3.792853005644833</v>
+        <v>6.710226104774095</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.618002107503873</v>
+        <v>-3.917055068221644</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.526536677451168</v>
+        <v>-2.038303683619717</v>
       </c>
       <c r="L73" t="n">
-        <v>-22.28103353928917</v>
+        <v>-25.6206142028072</v>
       </c>
       <c r="M73" t="n">
         <v>0.01</v>
@@ -3585,38 +3585,38 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-0.11684734665803</v>
+        <v>-0.4457131240144599</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3901160232113982</v>
+        <v>0.7156362985779502</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6831716913834206</v>
+        <v>0.6748079364087256</v>
       </c>
       <c r="G74" t="n">
-        <v>6254.370148122869</v>
+        <v>6114.457420525307</v>
       </c>
       <c r="H74" t="n">
-        <v>-18.96301301357095</v>
+        <v>-25.20870234739602</v>
       </c>
       <c r="I74" t="n">
-        <v>3.475427623989007</v>
+        <v>6.639072091829056</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.239650135403108</v>
+        <v>-3.868472913693005</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.380834729897046</v>
+        <v>-1.838752926283129</v>
       </c>
       <c r="L74" t="n">
-        <v>-20.1080702548821</v>
+        <v>-24.2768560955431</v>
       </c>
       <c r="M74" t="n">
         <v>0.01</v>
@@ -3628,38 +3628,38 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-0.1128284308083192</v>
+        <v>-0.4303830066454429</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3572219177598686</v>
+        <v>0.6894443357657094</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6109837173788734</v>
+        <v>0.6476533228006663</v>
       </c>
       <c r="G75" t="n">
-        <v>6433.875121704883</v>
+        <v>6145.193529183801</v>
       </c>
       <c r="H75" t="n">
-        <v>-17.25907180448314</v>
+        <v>-24.66138913696641</v>
       </c>
       <c r="I75" t="n">
-        <v>3.198134297037398</v>
+        <v>6.450573510312288</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.913985218083681</v>
+        <v>-3.701131388021401</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.254706226736639</v>
+        <v>-1.938867296994072</v>
       </c>
       <c r="L75" t="n">
-        <v>-18.22962895226606</v>
+        <v>-23.8508143116696</v>
       </c>
       <c r="M75" t="n">
         <v>0.01</v>
@@ -3671,38 +3671,38 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-0.1089477438963551</v>
+        <v>-0.4155801622820559</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.328502351876349</v>
+        <v>0.6664202170008942</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5488865199499846</v>
+        <v>0.6271001367970959</v>
       </c>
       <c r="G76" t="n">
-        <v>6611.87665065446</v>
+        <v>6185.952008382566</v>
       </c>
       <c r="H76" t="n">
-        <v>-15.77806761118845</v>
+        <v>-23.45574329359362</v>
       </c>
       <c r="I76" t="n">
-        <v>2.955027958718586</v>
+        <v>6.08875265334787</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.632996175572643</v>
+        <v>-3.681196667774822</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.145202621473068</v>
+        <v>-1.673092953876485</v>
       </c>
       <c r="L76" t="n">
-        <v>-16.60123844951558</v>
+        <v>-22.72128026189706</v>
       </c>
       <c r="M76" t="n">
         <v>0.01</v>
@@ -3714,38 +3714,38 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.1052005315953627</v>
+        <v>-0.4012864555887516</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3033382501814214</v>
+        <v>0.6426756094676429</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4953442964651465</v>
+        <v>0.6034728846972282</v>
       </c>
       <c r="G77" t="n">
-        <v>6786.43780965084</v>
+        <v>6234.146699043863</v>
       </c>
       <c r="H77" t="n">
-        <v>-14.48665594108023</v>
+        <v>-23.76719277788225</v>
       </c>
       <c r="I77" t="n">
-        <v>2.741081261776992</v>
+        <v>6.139216618612207</v>
       </c>
       <c r="J77" t="n">
-        <v>-2.38991596763737</v>
+        <v>-3.475559473345021</v>
       </c>
       <c r="K77" t="n">
-        <v>-1.049832301330198</v>
+        <v>-1.741336395139849</v>
       </c>
       <c r="L77" t="n">
-        <v>-15.18532294827081</v>
+        <v>-22.84487202775492</v>
       </c>
       <c r="M77" t="n">
         <v>0.01</v>
@@ -3757,38 +3757,38 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.1015822031016575</v>
+        <v>-0.3874843749872999</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.281206126046376</v>
+        <v>0.6236973554256544</v>
       </c>
       <c r="F78" t="n">
-        <v>0.449059807361796</v>
+        <v>0.590532451095886</v>
       </c>
       <c r="G78" t="n">
-        <v>6956.124903595045</v>
+        <v>6289.394224405656</v>
       </c>
       <c r="H78" t="n">
-        <v>-13.35665115067446</v>
+        <v>-22.49101823241928</v>
       </c>
       <c r="I78" t="n">
-        <v>2.55204156935012</v>
+        <v>5.754958780333</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.179027558595219</v>
+        <v>-3.396455106240725</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.9664893212557369</v>
+        <v>-1.516947446613637</v>
       </c>
       <c r="L78" t="n">
-        <v>-13.9501264611753</v>
+        <v>-21.64946200494063</v>
       </c>
       <c r="M78" t="n">
         <v>0.01</v>
@@ -3800,38 +3800,38 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.09808832551033667</v>
+        <v>-0.3741570112029147</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2616631851218689</v>
+        <v>0.6024826474856899</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4089371490288305</v>
+        <v>0.5708140907069379</v>
       </c>
       <c r="G79" t="n">
-        <v>7119.909350212352</v>
+        <v>6348.606124252263</v>
       </c>
       <c r="H79" t="n">
-        <v>-12.36422213739487</v>
+        <v>-21.81167497562931</v>
       </c>
       <c r="I79" t="n">
-        <v>2.384310278365048</v>
+        <v>5.501881731791387</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.995500106747528</v>
+        <v>-3.260575814962352</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.8933932687686109</v>
+        <v>-1.596531669513306</v>
       </c>
       <c r="L79" t="n">
-        <v>-12.86880523454596</v>
+        <v>-21.16690072831359</v>
       </c>
       <c r="M79" t="n">
         <v>0.01</v>
@@ -3843,38 +3843,38 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.0947146183844163</v>
+        <v>-0.3612880365482775</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2443347550895195</v>
+        <v>0.582951021231197</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3740503417627579</v>
+        <v>0.5541574617072986</v>
       </c>
       <c r="G80" t="n">
-        <v>7277.086822630183</v>
+        <v>6412.504188084192</v>
       </c>
       <c r="H80" t="n">
-        <v>-11.48921364391455</v>
+        <v>-20.96918507030432</v>
       </c>
       <c r="I80" t="n">
-        <v>2.234840985863032</v>
+        <v>5.452054916068389</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.835250740524968</v>
+        <v>-3.135031314712217</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.8290385206098427</v>
+        <v>-1.454925416658829</v>
       </c>
       <c r="L80" t="n">
-        <v>-11.91866191918633</v>
+        <v>-20.10708688560698</v>
       </c>
       <c r="M80" t="n">
         <v>0.01</v>
@@ -3886,38 +3886,38 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-0.09145694851076089</v>
+        <v>-0.3488616849200784</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2289036782105681</v>
+        <v>0.5622878232722579</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3436168242495181</v>
+        <v>0.533565345880449</v>
       </c>
       <c r="G81" t="n">
-        <v>7427.210762822405</v>
+        <v>6479.778258660174</v>
       </c>
       <c r="H81" t="n">
-        <v>-10.71457355017698</v>
+        <v>-20.37469298476505</v>
       </c>
       <c r="I81" t="n">
-        <v>2.101053554484656</v>
+        <v>5.145353868815303</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.694827923719401</v>
+        <v>-3.004409098455757</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.7721514238760286</v>
+        <v>-1.392090705996787</v>
       </c>
       <c r="L81" t="n">
-        <v>-11.08049934328775</v>
+        <v>-19.62583892040229</v>
       </c>
       <c r="M81" t="n">
         <v>0.01</v>
@@ -3929,38 +3929,38 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.08831132483638007</v>
+        <v>-0.3368627324835682</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2151013600294154</v>
+        <v>0.5434217711764852</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3169750879825883</v>
+        <v>0.5163975967322924</v>
       </c>
       <c r="G82" t="n">
-        <v>7570.03784743488</v>
+        <v>6550.656521158028</v>
       </c>
       <c r="H82" t="n">
-        <v>-10.02586959453359</v>
+        <v>-19.45450918729392</v>
       </c>
       <c r="I82" t="n">
-        <v>1.98076159329649</v>
+        <v>4.943060019834414</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.57131303679615</v>
+        <v>-2.990331068630997</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.7216541635782829</v>
+        <v>-1.312783283460255</v>
       </c>
       <c r="L82" t="n">
-        <v>-10.33807520161153</v>
+        <v>-18.81456351955076</v>
       </c>
       <c r="M82" t="n">
         <v>0.01</v>
@@ -3972,38 +3972,38 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.08527389357888994</v>
+        <v>-0.3252764790214572</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2027002155011573</v>
+        <v>0.5244701563154104</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2935658048056684</v>
+        <v>0.497984193234883</v>
       </c>
       <c r="G83" t="n">
-        <v>7705.483382676684</v>
+        <v>6623.879983453983</v>
       </c>
       <c r="H83" t="n">
-        <v>-9.410881552642476</v>
+        <v>-18.2982372966642</v>
       </c>
       <c r="I83" t="n">
-        <v>1.872111258222376</v>
+        <v>4.902971158900785</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.46223732830272</v>
+        <v>-2.834085599090726</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.676634272011018</v>
+        <v>-1.467405004072265</v>
       </c>
       <c r="L83" t="n">
-        <v>-9.677641894733837</v>
+        <v>-17.69675674092641</v>
       </c>
       <c r="M83" t="n">
         <v>0.01</v>
@@ -4015,38 +4015,38 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-0.08234093350514743</v>
+        <v>-0.3140887299243098</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1915072942374432</v>
+        <v>0.5043919632643874</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2729159018307394</v>
+        <v>0.4757580833501939</v>
       </c>
       <c r="G84" t="n">
-        <v>7833.584936658437</v>
+        <v>6699.25690695088</v>
       </c>
       <c r="H84" t="n">
-        <v>-8.859257085729276</v>
+        <v>-18.54021490235323</v>
       </c>
       <c r="I84" t="n">
-        <v>1.773529603787189</v>
+        <v>4.7823774700829</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.365511835065548</v>
+        <v>-2.672352121201712</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.6363188985313692</v>
+        <v>-1.382546937700945</v>
       </c>
       <c r="L84" t="n">
-        <v>-9.087558215539003</v>
+        <v>-17.81273649117299</v>
       </c>
       <c r="M84" t="n">
         <v>0.01</v>
@@ -4058,38 +4058,38 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-0.07950885137227452</v>
+        <v>-0.3032857788003735</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0.181358900673808</v>
+        <v>0.488718664769112</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2546251232538336</v>
+        <v>0.4635822149218463</v>
       </c>
       <c r="G85" t="n">
-        <v>7954.472795873872</v>
+        <v>6777.135234623599</v>
       </c>
       <c r="H85" t="n">
-        <v>-8.36222131168469</v>
+        <v>-17.61291429150478</v>
       </c>
       <c r="I85" t="n">
-        <v>1.683680994162986</v>
+        <v>4.494595615829653</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.279368245061418</v>
+        <v>-2.635553668388734</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.6000530960640933</v>
+        <v>-1.407916492876251</v>
       </c>
       <c r="L85" t="n">
-        <v>-8.557961658647216</v>
+        <v>-17.16178883694011</v>
       </c>
       <c r="M85" t="n">
         <v>0.01</v>
@@ -4101,38 +4101,38 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-0.07677417752548613</v>
+        <v>-0.2928543906835349</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1721160537409951</v>
+        <v>0.4727612776125384</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2383546905387723</v>
+        <v>0.4497672173225088</v>
       </c>
       <c r="G86" t="n">
-        <v>8068.346065949581</v>
+        <v>6855.062378776683</v>
       </c>
       <c r="H86" t="n">
-        <v>-7.912331706554986</v>
+        <v>-16.85594425894774</v>
       </c>
       <c r="I86" t="n">
-        <v>1.601430314620873</v>
+        <v>4.463289356298301</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.20230899342157</v>
+        <v>-2.554023316256315</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.5672814968431469</v>
+        <v>-1.377343208790723</v>
       </c>
       <c r="L86" t="n">
-        <v>-8.08049188219883</v>
+        <v>-16.32402142769648</v>
       </c>
       <c r="M86" t="n">
         <v>0.01</v>
@@ -4144,38 +4144,38 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-0.07413356164732932</v>
+        <v>-0.2827817858188307</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0.16366065490543</v>
+        <v>0.4560220036870187</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2238177331452517</v>
+        <v>0.43310054467047</v>
       </c>
       <c r="G87" t="n">
-        <v>8175.453432484126</v>
+        <v>6933.175502092745</v>
       </c>
       <c r="H87" t="n">
-        <v>-7.503271255241287</v>
+        <v>-16.18680624275287</v>
       </c>
       <c r="I87" t="n">
-        <v>1.525811921181772</v>
+        <v>4.236611713061921</v>
       </c>
       <c r="J87" t="n">
-        <v>-1.133065149133766</v>
+        <v>-2.382087712780686</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.5375328479419886</v>
+        <v>-1.139843584007507</v>
       </c>
       <c r="L87" t="n">
-        <v>-7.648057331135268</v>
+        <v>-15.47212582647914</v>
       </c>
       <c r="M87" t="n">
         <v>0.01</v>
@@ -4187,38 +4187,38 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-0.07158376865312541</v>
+        <v>-0.27305562400565</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1558922539325269</v>
+        <v>0.4388882580324794</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2107712131985037</v>
+        <v>0.4145815850670734</v>
       </c>
       <c r="G88" t="n">
-        <v>8276.077761782999</v>
+        <v>7011.846950039961</v>
       </c>
       <c r="H88" t="n">
-        <v>-7.129673876600195</v>
+        <v>-15.68347373135643</v>
       </c>
       <c r="I88" t="n">
-        <v>1.456003432216907</v>
+        <v>4.087169245734005</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.070560875379667</v>
+        <v>-2.412425403509401</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.5104069598667563</v>
+        <v>-1.158225542434353</v>
       </c>
       <c r="L88" t="n">
-        <v>-7.254638279629712</v>
+        <v>-15.16695543156618</v>
       </c>
       <c r="M88" t="n">
         <v>0.01</v>
@@ -4230,38 +4230,38 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.0691216747275865</v>
+        <v>-0.2636639894794452</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1487253190137462</v>
+        <v>0.4238313916218076</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1990091107153993</v>
+        <v>0.4004185053559058</v>
       </c>
       <c r="G89" t="n">
-        <v>8370.523858638435</v>
+        <v>7091.218126019725</v>
       </c>
       <c r="H89" t="n">
-        <v>-6.786977081645732</v>
+        <v>-15.30671842214072</v>
       </c>
       <c r="I89" t="n">
-        <v>1.391303605775828</v>
+        <v>3.932042820659372</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.01388343660293</v>
+        <v>-2.328468670397693</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.4855636912833878</v>
+        <v>-1.149135652774204</v>
       </c>
       <c r="L89" t="n">
-        <v>-6.895120603756222</v>
+        <v>-14.85227992465325</v>
       </c>
       <c r="M89" t="n">
         <v>0.01</v>
@@ -4273,38 +4273,38 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-0.06674426349775124</v>
+        <v>-0.2545953763134304</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0.142086932484472</v>
+        <v>0.4101049372974608</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1883566724668018</v>
+        <v>0.3887739024600759</v>
       </c>
       <c r="G90" t="n">
-        <v>8459.108813267718</v>
+        <v>7170.180617606849</v>
       </c>
       <c r="H90" t="n">
-        <v>-6.471297611201965</v>
+        <v>-14.33543252725649</v>
       </c>
       <c r="I90" t="n">
-        <v>1.331113664568151</v>
+        <v>3.827321090409245</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.9622578858494303</v>
+        <v>-2.232392220069968</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.4627136518410441</v>
+        <v>-1.142237993663569</v>
       </c>
       <c r="L90" t="n">
-        <v>-6.565155484324289</v>
+        <v>-13.88274165058078</v>
       </c>
       <c r="M90" t="n">
         <v>0.01</v>
@@ -4316,38 +4316,38 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-0.0644486223375508</v>
+        <v>-0.2458386743223817</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1359148456668804</v>
+        <v>0.394675377515123</v>
       </c>
       <c r="F91" t="n">
-        <v>0.178665558323324</v>
+        <v>0.3720917579818534</v>
       </c>
       <c r="G91" t="n">
-        <v>8542.15446569871</v>
+        <v>7248.110087197434</v>
       </c>
       <c r="H91" t="n">
-        <v>-6.17932646393563</v>
+        <v>-14.28962579311549</v>
       </c>
       <c r="I91" t="n">
-        <v>1.274921530213118</v>
+        <v>3.671353977603379</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.9150257012977275</v>
+        <v>-2.115051140067537</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.4416103547438514</v>
+        <v>-0.9638123124655853</v>
       </c>
       <c r="L91" t="n">
-        <v>-6.261040989764091</v>
+        <v>-13.69713526804523</v>
       </c>
       <c r="M91" t="n">
         <v>0.01</v>
@@ -4359,38 +4359,38 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.06223193879947746</v>
+        <v>-0.2373831554512717</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1301558367561316</v>
+        <v>0.3814737184390975</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1698097448916353</v>
+        <v>0.3602264074695644</v>
       </c>
       <c r="G92" t="n">
-        <v>8619.981596295398</v>
+        <v>7325.961389720129</v>
       </c>
       <c r="H92" t="n">
-        <v>-5.908240286440506</v>
+        <v>-13.33151973329908</v>
       </c>
       <c r="I92" t="n">
-        <v>1.222288512483256</v>
+        <v>3.501272192174293</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.8716267551221506</v>
+        <v>-2.024066872132321</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.4220435926487499</v>
+        <v>-1.053380472059468</v>
       </c>
       <c r="L92" t="n">
-        <v>-5.979622121728151</v>
+        <v>-12.90769488531658</v>
       </c>
       <c r="M92" t="n">
         <v>0.01</v>
@@ -4402,38 +4402,38 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-0.06009149716898483</v>
+        <v>-0.2292184606320598</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1247643244298899</v>
+        <v>0.3673035779660216</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1616820681522627</v>
+        <v>0.3452127933349044</v>
       </c>
       <c r="G93" t="n">
-        <v>8692.905518287793</v>
+        <v>7402.628391528567</v>
       </c>
       <c r="H93" t="n">
-        <v>-5.655626570172331</v>
+        <v>-12.8368609170425</v>
       </c>
       <c r="I93" t="n">
-        <v>1.172838070238368</v>
+        <v>3.387020505244534</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.8315840942079259</v>
+        <v>-1.978839860445702</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.4038338458422431</v>
+        <v>-1.062411420607097</v>
       </c>
       <c r="L93" t="n">
-        <v>-5.718206439984132</v>
+        <v>-12.49109169285076</v>
       </c>
       <c r="M93" t="n">
         <v>0.01</v>
@@ -4445,38 +4445,38 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.05802467513739796</v>
+        <v>-0.2213345870925387</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1197011972538775</v>
+        <v>0.3541500242643189</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1541913052911989</v>
+        <v>0.3320385929294503</v>
       </c>
       <c r="G94" t="n">
-        <v>8761.232804244069</v>
+        <v>7478.713763392699</v>
       </c>
       <c r="H94" t="n">
-        <v>-5.419420499236221</v>
+        <v>-12.96742916090608</v>
       </c>
       <c r="I94" t="n">
-        <v>1.126246320627383</v>
+        <v>3.324229438306774</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.7944910935560712</v>
+        <v>-1.901091472589895</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.3868275614966065</v>
+        <v>-0.9560601177204389</v>
       </c>
       <c r="L94" t="n">
-        <v>-5.474492833661516</v>
+        <v>-12.50035131290964</v>
       </c>
       <c r="M94" t="n">
         <v>0.01</v>
@@ -4488,38 +4488,38 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.05602894058925724</v>
+        <v>-0.2137218761016875</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1149328251937911</v>
+        <v>0.3434125436563941</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1472597115113345</v>
+        <v>0.3242266688867666</v>
       </c>
       <c r="G95" t="n">
-        <v>8825.258925192724</v>
+        <v>7553.767374921269</v>
       </c>
       <c r="H95" t="n">
-        <v>-5.197851629858086</v>
+        <v>-12.11299646469137</v>
       </c>
       <c r="I95" t="n">
-        <v>1.082234023660702</v>
+        <v>3.078369217287654</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.7600006118283866</v>
+        <v>-1.858097343527266</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.3708931679902912</v>
+        <v>-0.8764810584622834</v>
       </c>
       <c r="L95" t="n">
-        <v>-5.246511386016062</v>
+        <v>-11.76920564939327</v>
       </c>
       <c r="M95" t="n">
         <v>0.01</v>
@@ -4531,38 +4531,38 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-0.0541018485001602</v>
+        <v>-0.206371001136518</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1104302248069447</v>
+        <v>0.331262224266915</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1408209407669613</v>
+        <v>0.3122280578259926</v>
       </c>
       <c r="G96" t="n">
-        <v>8885.266620076556</v>
+        <v>7626.684365600945</v>
       </c>
       <c r="H96" t="n">
-        <v>-4.989398866572127</v>
+        <v>-11.87887986180814</v>
       </c>
       <c r="I96" t="n">
-        <v>1.040559811886685</v>
+        <v>3.047211717715822</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.7278158363749507</v>
+        <v>-1.767289007945664</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.355917709526523</v>
+        <v>-0.9110281839086416</v>
       </c>
       <c r="L96" t="n">
-        <v>-5.032572600586915</v>
+        <v>-11.50998533594663</v>
       </c>
       <c r="M96" t="n">
         <v>0.01</v>
@@ -4574,38 +4574,38 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.05224103794130099</v>
+        <v>-0.1992729564559182</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1061683541277194</v>
+        <v>0.3202476316779429</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1348182904660459</v>
+        <v>0.3024366880550619</v>
       </c>
       <c r="G97" t="n">
-        <v>8941.524845665428</v>
+        <v>7698.384816907394</v>
       </c>
       <c r="H97" t="n">
-        <v>-4.792752439953425</v>
+        <v>-11.91034368458233</v>
       </c>
       <c r="I97" t="n">
-        <v>1.001014470876039</v>
+        <v>2.967865971195362</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.6976825539332042</v>
+        <v>-1.704355805622615</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.3418040042132541</v>
+        <v>-0.8199908769912295</v>
       </c>
       <c r="L97" t="n">
-        <v>-4.831224527223845</v>
+        <v>-11.46682439600081</v>
       </c>
       <c r="M97" t="n">
         <v>0.01</v>
@@ -4617,38 +4617,38 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.05044422918703728</v>
+        <v>-0.1924190460674927</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1021255170077837</v>
+        <v>0.3108711487847108</v>
       </c>
       <c r="F98" t="n">
-        <v>0.129203219551866</v>
+        <v>0.2961302567930453</v>
       </c>
       <c r="G98" t="n">
-        <v>8994.288184035026</v>
+        <v>7768.422519377683</v>
       </c>
       <c r="H98" t="n">
-        <v>-4.606781793053648</v>
+        <v>-11.20994427845084</v>
       </c>
       <c r="I98" t="n">
-        <v>0.963416106568049</v>
+        <v>2.932471738717377</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.6693826244022847</v>
+        <v>-1.652107455587557</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.3284682438954771</v>
+        <v>-0.7725702971466052</v>
       </c>
       <c r="L98" t="n">
-        <v>-4.641216554783361</v>
+        <v>-10.70215029246763</v>
       </c>
       <c r="M98" t="n">
         <v>0.01</v>
@@ -4660,38 +4660,38 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0.0487092209219412</v>
+        <v>-0.1858008730738852</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0.09828285983352249</v>
+        <v>0.2996807358740866</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1239340972789532</v>
+        <v>0.2846996570005034</v>
       </c>
       <c r="G99" t="n">
-        <v>9043.796607127631</v>
+        <v>7836.144693047559</v>
       </c>
       <c r="H99" t="n">
-        <v>-4.430508454415276</v>
+        <v>-10.48555499790205</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9276060611407732</v>
+        <v>2.813430864783923</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.6427284698712762</v>
+        <v>-1.625777877513365</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.3158379667951198</v>
+        <v>-0.8923325105290586</v>
       </c>
       <c r="L99" t="n">
-        <v>-4.461468829940898</v>
+        <v>-10.19023452116055</v>
       </c>
       <c r="M99" t="n">
         <v>0.01</v>
@@ -4703,38 +4703,38 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.04703388754391279</v>
+        <v>-0.1794103293855283</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0.09462394621062516</v>
+        <v>0.2884991851502913</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1189751466667809</v>
+        <v>0.2727221394119075</v>
       </c>
       <c r="G100" t="n">
-        <v>9090.275516498108</v>
+        <v>7902.68985580576</v>
       </c>
       <c r="H100" t="n">
-        <v>-4.263083119583327</v>
+        <v>-10.57734830417052</v>
       </c>
       <c r="I100" t="n">
-        <v>0.8934454606746285</v>
+        <v>2.587629947099531</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.6175584204216618</v>
+        <v>-1.554490738953818</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.303850344783644</v>
+        <v>-0.790454024299289</v>
       </c>
       <c r="L100" t="n">
-        <v>-4.291046424114004</v>
+        <v>-10.33466312032409</v>
       </c>
       <c r="M100" t="n">
         <v>0.01</v>
@@ -4746,38 +4746,38 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-0.04541617656005151</v>
+        <v>-0.1732395857872201</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0.09113439745653494</v>
+        <v>0.2800315517273743</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1142955522412086</v>
+        <v>0.2669799148503854</v>
       </c>
       <c r="G101" t="n">
-        <v>9133.935991742985</v>
+        <v>7968.171277650039</v>
       </c>
       <c r="H101" t="n">
-        <v>-4.103766284571962</v>
+        <v>-10.23592010519206</v>
       </c>
       <c r="I101" t="n">
-        <v>0.8608122961100722</v>
+        <v>2.552599883343988</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.5937327829814208</v>
+        <v>-1.540083382384735</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.2924507361996742</v>
+        <v>-0.7597508169271455</v>
       </c>
       <c r="L101" t="n">
-        <v>-4.129137507642985</v>
+        <v>-9.983154421159954</v>
       </c>
       <c r="M101" t="n">
         <v>0.01</v>
@@ -4789,38 +4789,38 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>no_event</t>
+          <t>crisis</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.04385410607209565</v>
+        <v>-0.167281082346357</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0.08780158864055765</v>
+        <v>0.2712888795950893</v>
       </c>
       <c r="F102" t="n">
-        <v>0.109868706421155</v>
+        <v>0.2600194931218308</v>
       </c>
       <c r="G102" t="n">
-        <v>9174.975193840419</v>
+        <v>8031.338374021348</v>
       </c>
       <c r="H102" t="n">
-        <v>-3.951911877292386</v>
+        <v>-10.00626049449913</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8295989543831749</v>
+        <v>2.463254558670711</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.5711305203972731</v>
+        <v>-1.493000187920158</v>
       </c>
       <c r="K102" t="n">
-        <v>-0.2815914627913925</v>
+        <v>-0.8001681235695741</v>
       </c>
       <c r="L102" t="n">
-        <v>-3.975034906097877</v>
+        <v>-9.836174247318153</v>
       </c>
       <c r="M102" t="n">
         <v>0.01</v>

--- a/stock_simulation_results.xlsx
+++ b/stock_simulation_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>event state</t>
+          <t>event_state</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -454,30 +454,45 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>retail demand</t>
+          <t>ewma_price</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>contrarian demand</t>
+          <t>value_signal</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>momentum demand</t>
+          <t>retail_demand</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>institutional demand</t>
+          <t>contrarian_demand</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>total demand</t>
+          <t>momentum_demand</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
+        <is>
+          <t>institutional_demand</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value_demand</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>total_demand</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -499,31 +514,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03025847354963162</v>
+        <v>0.029126</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07564618387407905</v>
+        <v>0.075</v>
       </c>
       <c r="G2" t="n">
         <v>10000</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.323612281931698</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2313540128857879</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.330738078676345</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1151532774526489</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.538149625174904</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>96.96355846756651</v>
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>100.0019</v>
       </c>
     </row>
     <row r="3">
@@ -539,34 +563,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4996677928691061</v>
+        <v>4.7e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3241083583519422</v>
+        <v>0.017448</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06076920657619647</v>
+        <v>0.045</v>
       </c>
       <c r="G3" t="n">
-        <v>9984.870763225184</v>
+        <v>9985.436900000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.61068364663351</v>
+        <v>100.0001</v>
       </c>
       <c r="I3" t="n">
-        <v>4.49806641696779</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.563531835249902</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6516053978288181</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-9.327754462744442</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>92.36547590833906</v>
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>100.0027</v>
       </c>
     </row>
     <row r="4">
@@ -582,34 +615,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3655084686694272</v>
+        <v>2e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2712007086309213</v>
+        <v>0.010474</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1297390685731623</v>
+        <v>0.027</v>
       </c>
       <c r="G4" t="n">
-        <v>9824.329507726694</v>
+        <v>9978.169</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.446253346670838</v>
+        <v>100.0002</v>
       </c>
       <c r="I4" t="n">
-        <v>3.558841632318601</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.253051790735644</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5310809765041553</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-8.671544481592036</v>
+        <v>-0.1524</v>
       </c>
       <c r="M4" t="n">
-        <v>87.74588274777875</v>
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.1524</v>
+      </c>
+      <c r="P4" t="n">
+        <v>99.3412</v>
       </c>
     </row>
     <row r="5">
@@ -625,34 +667,43 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3039294042915368</v>
+        <v>-0.016537</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2481811969588492</v>
+        <v>0.016516</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1645588859598177</v>
+        <v>0.017724</v>
       </c>
       <c r="G5" t="n">
-        <v>9706.296202638565</v>
+        <v>9975.115100000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.59377103554869</v>
+        <v>99.96729999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>3.138068389946481</v>
+        <v>0.0063</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.152564577326629</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6265123143423998</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-8.234779537271237</v>
+        <v>-0.1429</v>
       </c>
       <c r="M5" t="n">
-        <v>83.10354799314058</v>
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.1429</v>
+      </c>
+      <c r="P5" t="n">
+        <v>98.7128</v>
       </c>
     </row>
     <row r="6">
@@ -668,34 +719,43 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2921673766612473</v>
+        <v>-0.015812</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2477336767761896</v>
+        <v>0.013896</v>
       </c>
       <c r="F6" t="n">
-        <v>0.181083126948603</v>
+        <v>0.012063</v>
       </c>
       <c r="G6" t="n">
-        <v>9611.575983895284</v>
+        <v>9969.345600000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-8.737470017729372</v>
+        <v>99.9045</v>
       </c>
       <c r="I6" t="n">
-        <v>3.065213381506956</v>
+        <v>0.0119</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.102395876264768</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6066782408477053</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.38133075333489</v>
+        <v>-0.1072</v>
       </c>
       <c r="M6" t="n">
-        <v>78.41449166601456</v>
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1072</v>
+      </c>
+      <c r="P6" t="n">
+        <v>98.2277</v>
       </c>
     </row>
     <row r="7">
@@ -711,34 +771,43 @@
         <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2931691165949571</v>
+        <v>-0.012286</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2528867434379786</v>
+        <v>0.010384</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1924631837025107</v>
+        <v>0.00831</v>
       </c>
       <c r="G7" t="n">
-        <v>9526.55154711766</v>
+        <v>9965.463100000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.943646354128244</v>
+        <v>99.8207</v>
       </c>
       <c r="I7" t="n">
-        <v>1.26609056884986</v>
+        <v>0.016</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.491832241492128</v>
+        <v>6.5871</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6139496040295962</v>
+        <v>-2.4568</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.555438422740915</v>
+        <v>3.4762</v>
       </c>
       <c r="M7" t="n">
-        <v>75.19149336852901</v>
+        <v>1.1664</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8.7729</v>
+      </c>
+      <c r="P7" t="n">
+        <v>102.7345</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +820,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6759237913802965</v>
+        <v>0.675924</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2475546994073098</v>
+        <v>0.114701</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2149457374239521</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1660322944489156</v>
+        <v>0.127715</v>
       </c>
       <c r="G8" t="n">
-        <v>9447.453020686906</v>
+        <v>9963.724899999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8705009730669263</v>
+        <v>99.96639999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8691521761509813</v>
+        <v>-0.0277</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.207064514798142</v>
+        <v>5.999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.606335942487909</v>
+        <v>-3.6814</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6020773692261783</v>
+        <v>2.9215</v>
       </c>
       <c r="M8" t="n">
-        <v>73.19440101387931</v>
+        <v>1.0444</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5592</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.8428</v>
+      </c>
+      <c r="P8" t="n">
+        <v>107.1121</v>
       </c>
     </row>
     <row r="9">
@@ -794,37 +872,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6526756739341637</v>
+        <v>0.652676</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1904817903043689</v>
+        <v>0.106529</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1700636101548717</v>
+        <v>0.007402</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1394363399306259</v>
+        <v>0.178853</v>
       </c>
       <c r="G9" t="n">
-        <v>9395.234849906239</v>
+        <v>9967.3524</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4703965659117559</v>
+        <v>100.3237</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3702403370928034</v>
+        <v>-0.0677</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8400318087630936</v>
+        <v>4.8733</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7422817772560196</v>
+        <v>-3.7478</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7428868714974852</v>
+        <v>2.578</v>
       </c>
       <c r="M9" t="n">
-        <v>75.47189861496528</v>
+        <v>0.8204</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5.2642</v>
+      </c>
+      <c r="P9" t="n">
+        <v>111.3273</v>
       </c>
     </row>
     <row r="10">
@@ -837,37 +924,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6302271658103858</v>
+        <v>0.630227</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2514921958582466</v>
+        <v>0.098381</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.017482</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1237244563700586</v>
+        <v>0.192587</v>
       </c>
       <c r="G10" t="n">
-        <v>9370.679559838178</v>
+        <v>9966.916300000001</v>
       </c>
       <c r="H10" t="n">
-        <v>6.797921361480688</v>
+        <v>100.8739</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.54558935994816</v>
+        <v>-0.1036</v>
       </c>
       <c r="J10" t="n">
-        <v>1.144660901826034</v>
+        <v>4.09</v>
       </c>
       <c r="K10" t="n">
-        <v>1.125971014020567</v>
+        <v>-3.7778</v>
       </c>
       <c r="L10" t="n">
-        <v>6.522963917379129</v>
+        <v>2.3881</v>
       </c>
       <c r="M10" t="n">
-        <v>80.06784668697443</v>
+        <v>0.6796</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.2908</v>
+      </c>
+      <c r="P10" t="n">
+        <v>115.3966</v>
       </c>
     </row>
     <row r="11">
@@ -880,37 +976,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.608550764779164</v>
+        <v>0.608551</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3561685105039341</v>
+        <v>0.091381</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.020543</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1709756712863457</v>
+        <v>0.189971</v>
       </c>
       <c r="G11" t="n">
-        <v>9433.611603854361</v>
+        <v>9961.484</v>
       </c>
       <c r="H11" t="n">
-        <v>7.055545905817059</v>
+        <v>101.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.87627337012655</v>
+        <v>-0.1358</v>
       </c>
       <c r="J11" t="n">
-        <v>1.349029795991075</v>
+        <v>3.6389</v>
       </c>
       <c r="K11" t="n">
-        <v>1.01393244630856</v>
+        <v>-3.8314</v>
       </c>
       <c r="L11" t="n">
-        <v>6.542234777990145</v>
+        <v>2.2954</v>
       </c>
       <c r="M11" t="n">
-        <v>84.63957873199975</v>
+        <v>0.5908</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.0826</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.7763</v>
+      </c>
+      <c r="P11" t="n">
+        <v>119.3649</v>
       </c>
     </row>
     <row r="12">
@@ -923,37 +1028,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.7</v>
+        <v>0.58762</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2877423004851905</v>
+        <v>0.08597100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.020667</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1984352887906671</v>
+        <v>0.182173</v>
       </c>
       <c r="G12" t="n">
-        <v>9490.250443468925</v>
+        <v>9955.0638</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6631917764983</v>
+        <v>102.4882</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.787179536142272</v>
+        <v>-0.1647</v>
       </c>
       <c r="J12" t="n">
-        <v>1.038858220818036</v>
+        <v>3.3303</v>
       </c>
       <c r="K12" t="n">
-        <v>1.109393435944511</v>
+        <v>-3.8941</v>
       </c>
       <c r="L12" t="n">
-        <v>6.024263897118574</v>
+        <v>2.2355</v>
       </c>
       <c r="M12" t="n">
-        <v>89.13717398784054</v>
+        <v>0.5252</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.2448</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.4417</v>
+      </c>
+      <c r="P12" t="n">
+        <v>123.2595</v>
       </c>
     </row>
     <row r="13">
@@ -966,37 +1080,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6759237913802965</v>
+        <v>0.5674090000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.247957346579736</v>
+        <v>0.08157</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.019708</v>
       </c>
       <c r="F13" t="n">
-        <v>0.214303812245586</v>
+        <v>0.173102</v>
       </c>
       <c r="G13" t="n">
-        <v>9541.225399122033</v>
+        <v>9949.224099999999</v>
       </c>
       <c r="H13" t="n">
-        <v>6.341972055243524</v>
+        <v>103.5268</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.660042539654189</v>
+        <v>-0.1906</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8039860267218379</v>
+        <v>3.0835</v>
       </c>
       <c r="K13" t="n">
-        <v>1.122949622979076</v>
+        <v>-3.954</v>
       </c>
       <c r="L13" t="n">
-        <v>5.608865165290249</v>
+        <v>2.1313</v>
       </c>
       <c r="M13" t="n">
-        <v>93.56294579945063</v>
+        <v>0.4704</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.3935</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.1248</v>
+      </c>
+      <c r="P13" t="n">
+        <v>127.0664</v>
       </c>
     </row>
     <row r="14">
@@ -1009,37 +1132,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6526756739341637</v>
+        <v>0.547893</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2272710177409026</v>
+        <v>0.077213</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.018509</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2184671285692689</v>
+        <v>0.163479</v>
       </c>
       <c r="G14" t="n">
-        <v>9587.10285920983</v>
+        <v>9944.447899999999</v>
       </c>
       <c r="H14" t="n">
-        <v>5.856237381709867</v>
+        <v>104.7038</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.582548919381228</v>
+        <v>-0.2136</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6884022818251666</v>
+        <v>2.8686</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9887376306701525</v>
+        <v>-3.9991</v>
       </c>
       <c r="L14" t="n">
-        <v>4.950828374823959</v>
+        <v>2.0387</v>
       </c>
       <c r="M14" t="n">
-        <v>97.88495899714702</v>
+        <v>0.4222</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.5255</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.8558</v>
+      </c>
+      <c r="P14" t="n">
+        <v>130.7914</v>
       </c>
     </row>
     <row r="15">
@@ -1052,37 +1184,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6302271658103858</v>
+        <v>0.529049</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2166454075067645</v>
+        <v>0.07328800000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.01713</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2132223445865091</v>
+        <v>0.15404</v>
       </c>
       <c r="G15" t="n">
-        <v>9628.392573288847</v>
+        <v>9940.748799999999</v>
       </c>
       <c r="H15" t="n">
-        <v>5.538893117401846</v>
+        <v>106.0082</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.465053233625696</v>
+        <v>-0.2338</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6403004509277628</v>
+        <v>2.6783</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9269306489995326</v>
+        <v>-4.0333</v>
       </c>
       <c r="L15" t="n">
-        <v>4.641070983703445</v>
+        <v>1.9543</v>
       </c>
       <c r="M15" t="n">
-        <v>102.1443563084671</v>
+        <v>0.3793</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.6417</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.6204</v>
+      </c>
+      <c r="P15" t="n">
+        <v>134.4357</v>
       </c>
     </row>
     <row r="16">
@@ -1095,37 +1236,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.608550764779164</v>
+        <v>0.510852</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2113828588885911</v>
+        <v>0.06966</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.015763</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2058554748794592</v>
+        <v>0.145081</v>
       </c>
       <c r="G16" t="n">
-        <v>9665.553315959962</v>
+        <v>9938.1091</v>
       </c>
       <c r="H16" t="n">
-        <v>5.602909215055477</v>
+        <v>107.4295</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.408954383828822</v>
+        <v>-0.2514</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6465396623397448</v>
+        <v>2.5043</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9455691178472176</v>
+        <v>-4.0553</v>
       </c>
       <c r="L16" t="n">
-        <v>4.786063611413617</v>
+        <v>1.8754</v>
       </c>
       <c r="M16" t="n">
-        <v>106.4053469904343</v>
+        <v>0.3403</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.7426</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.4072</v>
+      </c>
+      <c r="P16" t="n">
+        <v>137.9914</v>
       </c>
     </row>
     <row r="17">
@@ -1138,37 +1288,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5876199145384451</v>
+        <v>0.493282</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2067149592304304</v>
+        <v>0.066123</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.014555</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2018014592807699</v>
+        <v>0.136663</v>
       </c>
       <c r="G17" t="n">
-        <v>9698.997984363965</v>
+        <v>9936.416499999999</v>
       </c>
       <c r="H17" t="n">
-        <v>5.308762302249243</v>
+        <v>108.9576</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.349497760429776</v>
+        <v>-0.2665</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6124264856005166</v>
+        <v>2.3409</v>
       </c>
       <c r="K17" t="n">
-        <v>0.998676766005733</v>
+        <v>-4.0635</v>
       </c>
       <c r="L17" t="n">
-        <v>4.570367793425716</v>
+        <v>1.8003</v>
       </c>
       <c r="M17" t="n">
-        <v>110.6257335948738</v>
+        <v>0.3043</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.828</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.2101</v>
+      </c>
+      <c r="P17" t="n">
+        <v>141.4561</v>
       </c>
     </row>
     <row r="18">
@@ -1181,37 +1340,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5674089721791309</v>
+        <v>0.476315</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2021929669372726</v>
+        <v>0.06277000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.01344</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1961655492296414</v>
+        <v>0.128763</v>
       </c>
       <c r="G18" t="n">
-        <v>9729.098185927569</v>
+        <v>9935.4974</v>
       </c>
       <c r="H18" t="n">
-        <v>5.228471825253448</v>
+        <v>110.5826</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.238639226578286</v>
+        <v>-0.2792</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5802811037032868</v>
+        <v>2.1893</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9267548644227052</v>
+        <v>-4.0597</v>
       </c>
       <c r="L18" t="n">
-        <v>4.496868566801154</v>
+        <v>1.7287</v>
       </c>
       <c r="M18" t="n">
-        <v>114.8185822702993</v>
+        <v>0.2716</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.8992</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.0292</v>
+      </c>
+      <c r="P18" t="n">
+        <v>144.8274</v>
       </c>
     </row>
     <row r="19">
@@ -1224,37 +1392,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.5478931767693077</v>
+        <v>0.459933</v>
       </c>
       <c r="D19" t="n">
-        <v>0.198395678333039</v>
+        <v>0.059582</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.012424</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1910384638147529</v>
+        <v>0.121365</v>
       </c>
       <c r="G19" t="n">
-        <v>9756.188367334813</v>
+        <v>9935.2276</v>
       </c>
       <c r="H19" t="n">
-        <v>5.075894802543464</v>
+        <v>112.2948</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.14257339269232</v>
+        <v>-0.2897</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5890482383605603</v>
+        <v>2.0485</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9323568260001603</v>
+        <v>-4.0447</v>
       </c>
       <c r="L19" t="n">
-        <v>4.454726474211865</v>
+        <v>1.6604</v>
       </c>
       <c r="M19" t="n">
-        <v>118.9902304888847</v>
+        <v>0.2417</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.9571</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.8631</v>
+      </c>
+      <c r="P19" t="n">
+        <v>148.1033</v>
       </c>
     </row>
     <row r="20">
@@ -1267,37 +1444,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.5290486190190078</v>
+        <v>0.444114</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1947445541030108</v>
+        <v>0.056548</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.011505</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1865650018694358</v>
+        <v>0.114446</v>
       </c>
       <c r="G20" t="n">
-        <v>9780.569530601331</v>
+        <v>9935.4928</v>
       </c>
       <c r="H20" t="n">
-        <v>4.935888701250783</v>
+        <v>114.0852</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.125721888165964</v>
+        <v>-0.2982</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5643825443951642</v>
+        <v>1.9177</v>
       </c>
       <c r="K20" t="n">
-        <v>0.736446343891608</v>
+        <v>-4.0194</v>
       </c>
       <c r="L20" t="n">
-        <v>4.110995701371591</v>
+        <v>1.5951</v>
       </c>
       <c r="M20" t="n">
-        <v>123.0929377087893</v>
+        <v>0.2145</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.0027</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.7107</v>
+      </c>
+      <c r="P20" t="n">
+        <v>151.2803</v>
       </c>
     </row>
     <row r="21">
@@ -1310,37 +1496,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5108522119883397</v>
+        <v>0.428838</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1920840951601563</v>
+        <v>0.053629</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.010694</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1795013890863278</v>
+        <v>0.10798</v>
       </c>
       <c r="G21" t="n">
-        <v>9802.512577541198</v>
+        <v>9936.191199999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.633172944953363</v>
+        <v>115.945</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.08572728500243</v>
+        <v>-0.3048</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5652386805191422</v>
+        <v>1.7957</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8940650839564499</v>
+        <v>-3.9843</v>
       </c>
       <c r="L21" t="n">
-        <v>4.006749424426524</v>
+        <v>1.5326</v>
       </c>
       <c r="M21" t="n">
-        <v>127.1704210334471</v>
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.0367</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.3807</v>
+      </c>
+      <c r="P21" t="n">
+        <v>154.1991</v>
       </c>
     </row>
     <row r="22">
@@ -1353,37 +1548,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4932816628030994</v>
+        <v>0.414089</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1911318588378861</v>
+        <v>0.048234</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.010752</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1733109382954789</v>
+        <v>0.100037</v>
       </c>
       <c r="G22" t="n">
-        <v>9822.261319787078</v>
+        <v>9937.225200000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4.439622089877267</v>
+        <v>117.8577</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.972412766507279</v>
+        <v>-0.3083</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5683641381023755</v>
+        <v>1.6748</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8331144649401494</v>
+        <v>-3.9083</v>
       </c>
       <c r="L22" t="n">
-        <v>3.868687926412513</v>
+        <v>1.4773</v>
       </c>
       <c r="M22" t="n">
-        <v>131.2044314894984</v>
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.0494</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.2932</v>
+      </c>
+      <c r="P22" t="n">
+        <v>157.0368</v>
       </c>
     </row>
     <row r="23">
@@ -1396,37 +1600,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4763154453432114</v>
+        <v>0.399846</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1895647437536645</v>
+        <v>0.046007</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.009572000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1673375253815674</v>
+        <v>0.09365800000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>9840.035187808369</v>
+        <v>9938.126700000001</v>
       </c>
       <c r="H23" t="n">
-        <v>4.385082341645519</v>
+        <v>119.8166</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.879506252980812</v>
+        <v>-0.3106</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5614494071366158</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7904335542264644</v>
+        <v>-3.8569</v>
       </c>
       <c r="L23" t="n">
-        <v>3.857459050027787</v>
+        <v>1.4251</v>
       </c>
       <c r="M23" t="n">
-        <v>135.2333317660302</v>
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.0595</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.3723</v>
+      </c>
+      <c r="P23" t="n">
+        <v>155.6718</v>
       </c>
     </row>
     <row r="24">
@@ -1439,37 +1652,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.4599327738705397</v>
+        <v>0.386094</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1886264594280179</v>
+        <v>-0.02173</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.043692</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1627928779963789</v>
+        <v>0.07990999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>9856.031669027532</v>
+        <v>9939.527899999999</v>
       </c>
       <c r="H24" t="n">
-        <v>4.259557153956444</v>
+        <v>121.6094</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.939900134079144</v>
+        <v>-0.2801</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5587473510947716</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6812569004244646</v>
+        <v>-2.9065</v>
       </c>
       <c r="L24" t="n">
-        <v>3.559661271396536</v>
+        <v>1.2626</v>
       </c>
       <c r="M24" t="n">
-        <v>139.1883819038421</v>
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.7378</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="P24" t="n">
+        <v>156.106</v>
       </c>
     </row>
     <row r="25">
@@ -1482,37 +1704,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.4441135775637596</v>
+        <v>0.372814</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1871524311155532</v>
+        <v>0.006974</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.022419</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1562689782053197</v>
+        <v>0.068189</v>
       </c>
       <c r="G25" t="n">
-        <v>9870.42850212478</v>
+        <v>9923.7294</v>
       </c>
       <c r="H25" t="n">
-        <v>4.120341712526934</v>
+        <v>123.3342</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.890111818247764</v>
+        <v>-0.2657</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5671744043439525</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7457778435996361</v>
+        <v>-3.0942</v>
       </c>
       <c r="L25" t="n">
-        <v>3.543182142222759</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>143.1325222353879</v>
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.7218</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.0524</v>
+      </c>
+      <c r="P25" t="n">
+        <v>155.8553</v>
       </c>
     </row>
     <row r="26">
@@ -1525,37 +1756,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.4288384759290912</v>
+        <v>0.359991</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1871658838312215</v>
+        <v>-0.004016</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.025671</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1513988872236074</v>
+        <v>0.060078</v>
       </c>
       <c r="G26" t="n">
-        <v>9883.385651912302</v>
+        <v>9920.147000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>4.074810966276239</v>
+        <v>124.9603</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.789102987776878</v>
+        <v>-0.2472</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5769325547498985</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7130252091207017</v>
+        <v>-2.8237</v>
       </c>
       <c r="L26" t="n">
-        <v>3.57566574236996</v>
+        <v>1.2657</v>
       </c>
       <c r="M26" t="n">
-        <v>147.081368512084</v>
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.5901</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="P26" t="n">
+        <v>156.0116</v>
       </c>
     </row>
     <row r="27">
@@ -1568,37 +1808,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.4140887550567706</v>
+        <v>0.34761</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1863626802046272</v>
+        <v>0.002508</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.019653</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1480379135543186</v>
+        <v>0.054368</v>
       </c>
       <c r="G27" t="n">
-        <v>9895.047086721072</v>
+        <v>9915.297</v>
       </c>
       <c r="H27" t="n">
-        <v>3.968816437231742</v>
+        <v>126.5128</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.772381397834797</v>
+        <v>-0.2332</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5653657782170058</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6288910938281878</v>
+        <v>-2.7665</v>
       </c>
       <c r="L27" t="n">
-        <v>3.390691911442139</v>
+        <v>1.2429</v>
       </c>
       <c r="M27" t="n">
-        <v>150.9775109509027</v>
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.5204</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="P27" t="n">
+        <v>155.9932</v>
       </c>
     </row>
     <row r="28">
@@ -1611,37 +1860,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.3998463446941704</v>
+        <v>0.335654</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1846820709482549</v>
+        <v>-0.000295</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.019602</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1434341049998511</v>
+        <v>0.050034</v>
       </c>
       <c r="G28" t="n">
-        <v>9905.542378048964</v>
+        <v>9913.9408</v>
       </c>
       <c r="H28" t="n">
-        <v>3.839219278375527</v>
+        <v>127.9869</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.804786662174259</v>
+        <v>-0.2188</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5730141455686858</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7007780406851756</v>
+        <v>-2.6063</v>
       </c>
       <c r="L28" t="n">
-        <v>3.308224802455129</v>
+        <v>1.1922</v>
       </c>
       <c r="M28" t="n">
-        <v>154.8477476370996</v>
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.4271</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="P28" t="n">
+        <v>156.0567</v>
       </c>
     </row>
     <row r="29">
@@ -1654,37 +1912,46 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3860937961074808</v>
+        <v>0.324109</v>
       </c>
       <c r="D29" t="n">
-        <v>0.184242061159274</v>
+        <v>0.001018</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.017633</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1391350282591705</v>
+        <v>0.046933</v>
       </c>
       <c r="G29" t="n">
-        <v>9914.988140244068</v>
+        <v>9912.7454</v>
       </c>
       <c r="H29" t="n">
-        <v>3.751225666718328</v>
+        <v>129.3904</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.733323097625014</v>
+        <v>-0.2061</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5641883927056239</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6934771305250688</v>
+        <v>-2.4999</v>
       </c>
       <c r="L29" t="n">
-        <v>3.275568092324006</v>
+        <v>1.1783</v>
       </c>
       <c r="M29" t="n">
-        <v>158.7061555948783</v>
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.3512</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="P29" t="n">
+        <v>156.2</v>
       </c>
     </row>
     <row r="30">
@@ -1697,37 +1964,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.372814260704828</v>
+        <v>0.312962</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1838363227554643</v>
+        <v>0.002295</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.016007</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1355413876841164</v>
+        <v>0.04466</v>
       </c>
       <c r="G30" t="n">
-        <v>9923.48932621966</v>
+        <v>9912.6543</v>
       </c>
       <c r="H30" t="n">
-        <v>3.599023251030427</v>
+        <v>130.7308</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.663598857480747</v>
+        <v>-0.1948</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5743391165824226</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6293038682734385</v>
+        <v>-2.4024</v>
       </c>
       <c r="L30" t="n">
-        <v>3.139067378405542</v>
+        <v>1.1466</v>
       </c>
       <c r="M30" t="n">
-        <v>162.5258826453052</v>
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.2831</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="P30" t="n">
+        <v>156.3324</v>
       </c>
     </row>
     <row r="31">
@@ -1740,37 +2016,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.3599914693946423</v>
+        <v>0.302197</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1832263448740044</v>
+        <v>0.002119</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.015355</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1313562194297666</v>
+        <v>0.042718</v>
       </c>
       <c r="G31" t="n">
-        <v>9931.140393597694</v>
+        <v>9913.3856</v>
       </c>
       <c r="H31" t="n">
-        <v>3.543901529783929</v>
+        <v>132.0109</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.646598870449128</v>
+        <v>-0.1842</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5437821335122358</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5649646495606189</v>
+        <v>-2.2945</v>
       </c>
       <c r="L31" t="n">
-        <v>3.006049442407656</v>
+        <v>1.1162</v>
       </c>
       <c r="M31" t="n">
-        <v>166.2990932780192</v>
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.2158</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="P31" t="n">
+        <v>156.5138</v>
       </c>
     </row>
     <row r="32">
@@ -1783,37 +2068,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.4523902873460134</v>
+        <v>-0.508197</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1829854549833314</v>
+        <v>0.002901</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3933485341766821</v>
+        <v>0.507673</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1268737995516686</v>
+        <v>0.041116</v>
       </c>
       <c r="G32" t="n">
-        <v>9938.026354237925</v>
+        <v>9914.3694</v>
       </c>
       <c r="H32" t="n">
-        <v>-12.80244618278454</v>
+        <v>133.2361</v>
       </c>
       <c r="I32" t="n">
-        <v>3.411842118116737</v>
+        <v>-0.1747</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.626753402872955</v>
+        <v>-16.2055</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.9912828764460441</v>
+        <v>3.4362</v>
       </c>
       <c r="L32" t="n">
-        <v>-11.00864034398681</v>
+        <v>-4.9879</v>
       </c>
       <c r="M32" t="n">
-        <v>161.5991090602387</v>
+        <v>-1.8287</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-19.586</v>
+      </c>
+      <c r="P32" t="n">
+        <v>151.595</v>
       </c>
     </row>
     <row r="33">
@@ -1826,37 +2120,46 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.4368305117236274</v>
+        <v>-0.490717</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.151775588277352</v>
+        <v>-0.078567</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6023801379583863</v>
+        <v>0.607835</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1862106831708693</v>
+        <v>0.22053</v>
       </c>
       <c r="G33" t="n">
-        <v>9747.549451725792</v>
+        <v>9669.096100000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-18.85087121720436</v>
+        <v>134.154</v>
       </c>
       <c r="I33" t="n">
-        <v>6.497836298066606</v>
+        <v>-0.13</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.350760297048842</v>
+        <v>-20.0772</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.388649993581946</v>
+        <v>4.804</v>
       </c>
       <c r="L33" t="n">
-        <v>-16.09244520976854</v>
+        <v>-6.0287</v>
       </c>
       <c r="M33" t="n">
-        <v>156.6277258392016</v>
+        <v>-2.3933</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-0.8764999999999999</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-24.5716</v>
+      </c>
+      <c r="P33" t="n">
+        <v>146.4787</v>
       </c>
     </row>
     <row r="34">
@@ -1869,37 +2172,46 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.4218059081068991</v>
+        <v>-0.473839</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.112831771053524</v>
+        <v>-0.08437500000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5985653155390963</v>
+        <v>0.655998</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2726508620002069</v>
+        <v>0.378034</v>
       </c>
       <c r="G34" t="n">
-        <v>9471.60443757402</v>
+        <v>9398.269200000001</v>
       </c>
       <c r="H34" t="n">
-        <v>-19.66386466045723</v>
+        <v>134.7702</v>
       </c>
       <c r="I34" t="n">
-        <v>6.077629648261476</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.543049054039896</v>
+        <v>-22.2306</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.413175247251687</v>
+        <v>5.3102</v>
       </c>
       <c r="L34" t="n">
-        <v>-17.54245931348733</v>
+        <v>-6.7762</v>
       </c>
       <c r="M34" t="n">
-        <v>151.4968747599034</v>
+        <v>-2.7178</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-1.311</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-27.7253</v>
+      </c>
+      <c r="P34" t="n">
+        <v>141.1972</v>
       </c>
     </row>
     <row r="35">
@@ -1912,37 +2224,46 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.4072980694774631</v>
+        <v>-0.457542</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.09662771544827389</v>
+        <v>-0.07153</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6008807428804264</v>
+        <v>0.68164</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3390151103349975</v>
+        <v>0.504074</v>
       </c>
       <c r="G35" t="n">
-        <v>9225.161336047069</v>
+        <v>9130.4431</v>
       </c>
       <c r="H35" t="n">
-        <v>-20.80967902707849</v>
+        <v>135.0916</v>
       </c>
       <c r="I35" t="n">
-        <v>6.041497442574101</v>
+        <v>-0.0452</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.7858348007561</v>
+        <v>-23.5232</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.327770539129056</v>
+        <v>5.5488</v>
       </c>
       <c r="L35" t="n">
-        <v>-18.88178692438954</v>
+        <v>-7.3118</v>
       </c>
       <c r="M35" t="n">
-        <v>146.2163504903455</v>
+        <v>-2.917</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-1.657</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-29.8602</v>
+      </c>
+      <c r="P35" t="n">
+        <v>135.7521</v>
       </c>
     </row>
     <row r="36">
@@ -1955,37 +2276,46 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.393289221918689</v>
+        <v>-0.441805</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0888660659149634</v>
+        <v>-0.064161</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6034996356456246</v>
+        <v>0.699728</v>
       </c>
       <c r="F36" t="n">
-        <v>0.392226935444894</v>
+        <v>0.601046</v>
       </c>
       <c r="G36" t="n">
-        <v>9002.204831002149</v>
+        <v>8876.5787</v>
       </c>
       <c r="H36" t="n">
-        <v>-20.71348096951827</v>
+        <v>135.1246</v>
       </c>
       <c r="I36" t="n">
-        <v>5.912986369683222</v>
+        <v>-0.0046</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.915261649881848</v>
+        <v>-24.4289</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.56160734041288</v>
+        <v>5.7857</v>
       </c>
       <c r="L36" t="n">
-        <v>-19.27736359012977</v>
+        <v>-7.706</v>
       </c>
       <c r="M36" t="n">
-        <v>140.8124624884782</v>
+        <v>-3.056</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1.9722</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-31.3774</v>
+      </c>
+      <c r="P36" t="n">
+        <v>130.1375</v>
       </c>
     </row>
     <row r="37">
@@ -1998,37 +2328,46 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.3797622028404101</v>
+        <v>-0.426609</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.08632870634715389</v>
+        <v>-0.061327</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6028033455159961</v>
+        <v>0.711811</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4281097971682341</v>
+        <v>0.6744019999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>8800.234530079122</v>
+        <v>8639.0568</v>
       </c>
       <c r="H37" t="n">
-        <v>-21.06943007847561</v>
+        <v>134.8753</v>
       </c>
       <c r="I37" t="n">
-        <v>5.707721789017106</v>
+        <v>0.0351</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.054887001931874</v>
+        <v>-25.0236</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.597924479471877</v>
+        <v>6.0238</v>
       </c>
       <c r="L37" t="n">
-        <v>-20.01451977086226</v>
+        <v>-7.9887</v>
       </c>
       <c r="M37" t="n">
-        <v>135.2824800952994</v>
+        <v>-3.1466</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-2.2634</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-32.3986</v>
+      </c>
+      <c r="P37" t="n">
+        <v>124.3821</v>
       </c>
     </row>
     <row r="38">
@@ -2041,37 +2380,46 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.3667004399526046</v>
+        <v>-0.411936</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.08593219979751958</v>
+        <v>-0.060697</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6010641902349415</v>
+        <v>0.718257</v>
       </c>
       <c r="F38" t="n">
-        <v>0.457011076009563</v>
+        <v>0.728627</v>
       </c>
       <c r="G38" t="n">
-        <v>8618.809404313211</v>
+        <v>8419.2454</v>
       </c>
       <c r="H38" t="n">
-        <v>-20.83481608489528</v>
+        <v>134.3506</v>
       </c>
       <c r="I38" t="n">
-        <v>5.743750556414533</v>
+        <v>0.0742</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.135836621247416</v>
+        <v>-25.3427</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.36516062020394</v>
+        <v>6.2473</v>
       </c>
       <c r="L38" t="n">
-        <v>-19.59206276993211</v>
+        <v>-8.1366</v>
       </c>
       <c r="M38" t="n">
-        <v>129.6507285041121</v>
+        <v>-3.1945</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-2.5319</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-32.9584</v>
+      </c>
+      <c r="P38" t="n">
+        <v>118.4838</v>
       </c>
     </row>
     <row r="39">
@@ -2084,37 +2432,46 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.3540879309622675</v>
+        <v>-0.397768</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0885495763028616</v>
+        <v>-0.061846</v>
       </c>
       <c r="E39" t="n">
-        <v>0.595268586066008</v>
+        <v>0.71998</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4701272733050589</v>
+        <v>0.76676</v>
       </c>
       <c r="G39" t="n">
-        <v>8456.396368764419</v>
+        <v>8218.1921</v>
       </c>
       <c r="H39" t="n">
-        <v>-20.19253922219737</v>
+        <v>133.5573</v>
       </c>
       <c r="I39" t="n">
-        <v>5.679930555880334</v>
+        <v>0.1129</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.246316784146357</v>
+        <v>-25.4295</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.436804304930771</v>
+        <v>6.4596</v>
       </c>
       <c r="L39" t="n">
-        <v>-19.19572975539417</v>
+        <v>-8.203799999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>123.9289093289177</v>
+        <v>-3.2064</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-2.7824</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-33.1625</v>
+      </c>
+      <c r="P39" t="n">
+        <v>112.4351</v>
       </c>
     </row>
     <row r="40">
@@ -2127,37 +2484,46 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.3419092239686008</v>
+        <v>-0.384087</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.09310006517765554</v>
+        <v>-0.064484</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5873827276899849</v>
+        <v>0.717912</v>
       </c>
       <c r="F40" t="n">
-        <v>0.474033661536977</v>
+        <v>0.791681</v>
       </c>
       <c r="G40" t="n">
-        <v>8313.122438854973</v>
+        <v>8036.3831</v>
       </c>
       <c r="H40" t="n">
-        <v>-21.14336309637715</v>
+        <v>132.5011</v>
       </c>
       <c r="I40" t="n">
-        <v>5.740753069230189</v>
+        <v>0.1514</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.252077605312701</v>
+        <v>-25.3272</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.578925979374565</v>
+        <v>6.6652</v>
       </c>
       <c r="L40" t="n">
-        <v>-20.23361361183422</v>
+        <v>-8.206</v>
       </c>
       <c r="M40" t="n">
-        <v>118.1072007491779</v>
+        <v>-3.1886</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-3.0198</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-33.0764</v>
+      </c>
+      <c r="P40" t="n">
+        <v>106.2639</v>
       </c>
     </row>
     <row r="41">
@@ -2170,37 +2536,46 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.3301493985325023</v>
+        <v>-0.370876</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.09650864623815968</v>
+        <v>-0.068117</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5827571194916095</v>
+        <v>0.7126749999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4867563330405284</v>
+        <v>0.805773</v>
       </c>
       <c r="G41" t="n">
-        <v>8188.118831124483</v>
+        <v>7873.7887</v>
       </c>
       <c r="H41" t="n">
-        <v>-20.27509822055644</v>
+        <v>131.1893</v>
       </c>
       <c r="I41" t="n">
-        <v>5.693436422007673</v>
+        <v>0.19</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.144408424864499</v>
+        <v>-25.0674</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.544021238676996</v>
+        <v>6.8638</v>
       </c>
       <c r="L41" t="n">
-        <v>-19.27009146209026</v>
+        <v>-8.1553</v>
       </c>
       <c r="M41" t="n">
-        <v>112.2181272116428</v>
+        <v>-3.1462</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-3.2464</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-32.7515</v>
+      </c>
+      <c r="P41" t="n">
+        <v>99.9787</v>
       </c>
     </row>
     <row r="42">
@@ -2213,37 +2588,46 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.318794047397162</v>
+        <v>-0.35812</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1028604830529064</v>
+        <v>-0.072933</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5744122230069937</v>
+        <v>0.705118</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4847547144452196</v>
+        <v>0.810979</v>
       </c>
       <c r="G42" t="n">
-        <v>8077.92838826623</v>
+        <v>7730.0722</v>
       </c>
       <c r="H42" t="n">
-        <v>-20.39365661208092</v>
+        <v>129.6288</v>
       </c>
       <c r="I42" t="n">
-        <v>5.68635669506325</v>
+        <v>0.2287</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.172062928196368</v>
+        <v>-24.6861</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.417675970740699</v>
+        <v>7.0625</v>
       </c>
       <c r="L42" t="n">
-        <v>-19.29703881595474</v>
+        <v>-8.062900000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>106.2593061001598</v>
+        <v>-3.0843</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-3.4665</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-32.2373</v>
+      </c>
+      <c r="P42" t="n">
+        <v>93.61020000000001</v>
       </c>
     </row>
     <row r="43">
@@ -2256,37 +2640,46 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.3078292588373711</v>
+        <v>-0.345803</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1097515409326269</v>
+        <v>-0.07874100000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5672094701276188</v>
+        <v>0.695759</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4838232168266791</v>
+        <v>0.80896</v>
       </c>
       <c r="G43" t="n">
-        <v>7982.929437936111</v>
+        <v>7604.5058</v>
       </c>
       <c r="H43" t="n">
-        <v>-19.85829532860398</v>
+        <v>127.8278</v>
       </c>
       <c r="I43" t="n">
-        <v>5.585341080942801</v>
+        <v>0.2677</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.230570712204374</v>
+        <v>-24.2082</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.545106222844742</v>
+        <v>7.2627</v>
       </c>
       <c r="L43" t="n">
-        <v>-19.0486311827103</v>
+        <v>-7.9378</v>
       </c>
       <c r="M43" t="n">
-        <v>100.2499038134538</v>
+        <v>-3.0068</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-3.6817</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-31.5719</v>
+      </c>
+      <c r="P43" t="n">
+        <v>87.1353</v>
       </c>
     </row>
     <row r="44">
@@ -2299,37 +2692,46 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.2972415996159179</v>
+        <v>-0.333909</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1176298899531141</v>
+        <v>-0.086342</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5601316303570306</v>
+        <v>0.685585</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4807802419231104</v>
+        <v>0.801095</v>
       </c>
       <c r="G44" t="n">
-        <v>7901.031759078691</v>
+        <v>7496.1759</v>
       </c>
       <c r="H44" t="n">
-        <v>-19.97525458237191</v>
+        <v>125.7932</v>
       </c>
       <c r="I44" t="n">
-        <v>5.331261656532018</v>
+        <v>0.3073</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.229037543514802</v>
+        <v>-23.6695</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.36300923529851</v>
+        <v>7.4786</v>
       </c>
       <c r="L44" t="n">
-        <v>-19.2360397046532</v>
+        <v>-7.7897</v>
       </c>
       <c r="M44" t="n">
-        <v>94.18580122585136</v>
+        <v>-2.9187</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-3.8985</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-30.7979</v>
+      </c>
+      <c r="P44" t="n">
+        <v>80.58839999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2342,37 +2744,46 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.2870180985261932</v>
+        <v>-0.322424</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1258033874898242</v>
+        <v>-0.095272</v>
       </c>
       <c r="E45" t="n">
-        <v>0.554831547900247</v>
+        <v>0.674798</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4808285422003983</v>
+        <v>0.788636</v>
       </c>
       <c r="G45" t="n">
-        <v>7830.862767992307</v>
+        <v>7403.7659</v>
       </c>
       <c r="H45" t="n">
-        <v>-19.72758626008873</v>
+        <v>123.533</v>
       </c>
       <c r="I45" t="n">
-        <v>5.396593245844348</v>
+        <v>0.3476</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.178274804499448</v>
+        <v>-23.083</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.454782358039411</v>
+        <v>7.7076</v>
       </c>
       <c r="L45" t="n">
-        <v>-18.96405017678324</v>
+        <v>-7.6245</v>
       </c>
       <c r="M45" t="n">
-        <v>88.07933851345904</v>
+        <v>-2.8221</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-4.1175</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-29.9395</v>
+      </c>
+      <c r="P45" t="n">
+        <v>73.99120000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2385,37 +2796,46 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.27714623050084</v>
+        <v>-0.311335</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1355973964900053</v>
+        <v>-0.105962</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5497597192300717</v>
+        <v>0.664022</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4781376270880714</v>
+        <v>0.772576</v>
       </c>
       <c r="G46" t="n">
-        <v>7770.360717242953</v>
+        <v>7325.9903</v>
       </c>
       <c r="H46" t="n">
-        <v>-19.79167003467731</v>
+        <v>121.0559</v>
       </c>
       <c r="I46" t="n">
-        <v>5.52077669554891</v>
+        <v>0.3888</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.221167964455383</v>
+        <v>-22.4726</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.516136653698422</v>
+        <v>7.9572</v>
       </c>
       <c r="L46" t="n">
-        <v>-19.0081979572822</v>
+        <v>-7.4493</v>
       </c>
       <c r="M46" t="n">
-        <v>81.91986433892284</v>
+        <v>-2.7204</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-4.3417</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-29.0267</v>
+      </c>
+      <c r="P46" t="n">
+        <v>67.32729999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2428,37 +2848,46 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.2676139012669791</v>
+        <v>-0.300626</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.14661671586473</v>
+        <v>-0.119478</v>
       </c>
       <c r="E47" t="n">
-        <v>0.546369753116083</v>
+        <v>0.654212</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4769645558256648</v>
+        <v>0.753813</v>
       </c>
       <c r="G47" t="n">
-        <v>7718.444785903622</v>
+        <v>7261.3805</v>
       </c>
       <c r="H47" t="n">
-        <v>-19.18509258432118</v>
+        <v>118.3694</v>
       </c>
       <c r="I47" t="n">
-        <v>5.348257409559563</v>
+        <v>0.4312</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.23848714602016</v>
+        <v>-21.8706</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.360984812066302</v>
+        <v>8.2433</v>
       </c>
       <c r="L47" t="n">
-        <v>-18.43630713284808</v>
+        <v>-7.2721</v>
       </c>
       <c r="M47" t="n">
-        <v>75.7420568773959</v>
+        <v>-2.618</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-4.5772</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-28.0945</v>
+      </c>
+      <c r="P47" t="n">
+        <v>60.6347</v>
       </c>
     </row>
     <row r="48">
@@ -2471,37 +2900,46 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.2584094325292127</v>
+        <v>-0.290286</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1602680417579939</v>
+        <v>-0.135569</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5427869795135608</v>
+        <v>0.645554</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4705418048238796</v>
+        <v>0.733233</v>
       </c>
       <c r="G48" t="n">
-        <v>7673.415430755218</v>
+        <v>7208.1365</v>
       </c>
       <c r="H48" t="n">
-        <v>-20.17739640906662</v>
+        <v>115.4827</v>
       </c>
       <c r="I48" t="n">
-        <v>5.342300808897448</v>
+        <v>0.4749</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.329142273264792</v>
+        <v>-21.2875</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.525177386989814</v>
+        <v>8.565200000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>-19.68941526042378</v>
+        <v>-7.0982</v>
       </c>
       <c r="M48" t="n">
-        <v>69.50482733683812</v>
+        <v>-2.5166</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-4.8248</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-27.1618</v>
+      </c>
+      <c r="P48" t="n">
+        <v>53.9121</v>
       </c>
     </row>
     <row r="49">
@@ -2514,37 +2952,46 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.2495215476622519</v>
+        <v>-0.280302</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1718384672818029</v>
+        <v>-0.155815</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5443123222307599</v>
+        <v>0.6392370000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4792192354985656</v>
+        <v>0.711558</v>
       </c>
       <c r="G49" t="n">
-        <v>7634.680397922915</v>
+        <v>7164.5456</v>
       </c>
       <c r="H49" t="n">
-        <v>-19.72858244207124</v>
+        <v>112.4042</v>
       </c>
       <c r="I49" t="n">
-        <v>5.61572141137388</v>
+        <v>0.5204</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.359458608248911</v>
+        <v>-20.762</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.571452025319822</v>
+        <v>8.9436</v>
       </c>
       <c r="L49" t="n">
-        <v>-19.04377166426609</v>
+        <v>-6.9361</v>
       </c>
       <c r="M49" t="n">
-        <v>63.25929282710329</v>
+        <v>-2.4213</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-5.0912</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-26.267</v>
+      </c>
+      <c r="P49" t="n">
+        <v>47.1466</v>
       </c>
     </row>
     <row r="50">
@@ -2557,37 +3004,46 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.240939357895641</v>
+        <v>-0.270661</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1879986276693534</v>
+        <v>-0.181976</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5449262376739731</v>
+        <v>0.636591</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4779692579418002</v>
+        <v>0.689604</v>
       </c>
       <c r="G50" t="n">
-        <v>7599.056197015244</v>
+        <v>7128.4725</v>
       </c>
       <c r="H50" t="n">
-        <v>-19.80384179843477</v>
+        <v>109.1413</v>
       </c>
       <c r="I50" t="n">
-        <v>5.371496275488852</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.481043475626199</v>
+        <v>-20.337</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.314837595841458</v>
+        <v>9.4024</v>
       </c>
       <c r="L50" t="n">
-        <v>-19.22822659441358</v>
+        <v>-6.7967</v>
       </c>
       <c r="M50" t="n">
-        <v>56.98300706144302</v>
+        <v>-2.3381</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-5.3844</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-25.4538</v>
+      </c>
+      <c r="P50" t="n">
+        <v>40.3632</v>
       </c>
     </row>
     <row r="51">
@@ -2600,37 +3056,46 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.2326523489736513</v>
+        <v>-0.261352</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2071023384988598</v>
+        <v>-0.21529</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5485392803566536</v>
+        <v>0.638686</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4790638207092159</v>
+        <v>0.668301</v>
       </c>
       <c r="G51" t="n">
-        <v>7566.687458476733</v>
+        <v>7097.3298</v>
       </c>
       <c r="H51" t="n">
-        <v>-19.74652274783305</v>
+        <v>105.7024</v>
       </c>
       <c r="I51" t="n">
-        <v>5.715197822364983</v>
+        <v>0.6181</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.46272520705438</v>
+        <v>-20.0495</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.509488913930533</v>
+        <v>9.9581</v>
       </c>
       <c r="L51" t="n">
-        <v>-19.00353904645298</v>
+        <v>-6.691</v>
       </c>
       <c r="M51" t="n">
-        <v>50.67642535992832</v>
+        <v>-2.2719</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-5.7097</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-24.764</v>
+      </c>
+      <c r="P51" t="n">
+        <v>33.57</v>
       </c>
     </row>
     <row r="52">
@@ -2643,37 +3108,46 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.2246503682740031</v>
+        <v>-0.252363</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2317924165445613</v>
+        <v>-0.259477</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5547152913567637</v>
+        <v>0.648056</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4774736828900593</v>
+        <v>0.648621</v>
       </c>
       <c r="G52" t="n">
-        <v>7535.749072450732</v>
+        <v>7068.254</v>
       </c>
       <c r="H52" t="n">
-        <v>-20.00759849442262</v>
+        <v>102.0958</v>
       </c>
       <c r="I52" t="n">
-        <v>5.560036631685492</v>
+        <v>0.6712</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.640468685004988</v>
+        <v>-19.9808</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.374691633065545</v>
+        <v>10.6557</v>
       </c>
       <c r="L52" t="n">
-        <v>-19.46272218080767</v>
+        <v>-6.6369</v>
       </c>
       <c r="M52" t="n">
-        <v>44.34439708808146</v>
+        <v>-2.234</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-6.0794</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-24.2754</v>
+      </c>
+      <c r="P52" t="n">
+        <v>26.7544</v>
       </c>
     </row>
     <row r="53">
@@ -2686,37 +3160,46 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.2169236123696343</v>
+        <v>-0.243683</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2597115094103403</v>
+        <v>-0.321282</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5651950906326835</v>
+        <v>0.669148</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4811114315421123</v>
+        <v>0.631927</v>
       </c>
       <c r="G53" t="n">
-        <v>7504.816519527277</v>
+        <v>7037.4006</v>
       </c>
       <c r="H53" t="n">
-        <v>-20.32928203548345</v>
+        <v>98.3287</v>
       </c>
       <c r="I53" t="n">
-        <v>5.956907784878978</v>
+        <v>0.7279</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.836561556690926</v>
+        <v>-20.272</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.48283296895041</v>
+        <v>11.5749</v>
       </c>
       <c r="L53" t="n">
-        <v>-19.69176877624581</v>
+        <v>-6.6657</v>
       </c>
       <c r="M53" t="n">
-        <v>37.97877815031804</v>
+        <v>-2.2435</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-6.5144</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-24.1206</v>
+      </c>
+      <c r="P53" t="n">
+        <v>19.903</v>
       </c>
     </row>
     <row r="54">
@@ -2729,37 +3212,46 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.2094626150182758</v>
+        <v>-0.235302</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.2956221868180877</v>
+        <v>-0.412795</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5810697457842185</v>
+        <v>0.709829</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4855845466877254</v>
+        <v>0.620363</v>
       </c>
       <c r="G54" t="n">
-        <v>7471.737322258207</v>
+        <v>6999.0864</v>
       </c>
       <c r="H54" t="n">
-        <v>-20.71008044600415</v>
+        <v>94.4074</v>
       </c>
       <c r="I54" t="n">
-        <v>6.061624418631421</v>
+        <v>0.7892</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.837269597543254</v>
+        <v>-21.1735</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.420885401147645</v>
+        <v>12.8556</v>
       </c>
       <c r="L54" t="n">
-        <v>-19.90661102606363</v>
+        <v>-6.8304</v>
       </c>
       <c r="M54" t="n">
-        <v>31.57964671183564</v>
+        <v>-2.3346</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-7.0489</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-24.5318</v>
+      </c>
+      <c r="P54" t="n">
+        <v>12.9927</v>
       </c>
     </row>
     <row r="55">
@@ -2772,37 +3264,46 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.2022582355651206</v>
+        <v>-0.227209</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3435695523592577</v>
+        <v>-0.562235</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6045667022899838</v>
+        <v>0.787926</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4904168382732715</v>
+        <v>0.6175349999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>7434.028717140278</v>
+        <v>6944.2634</v>
       </c>
       <c r="H55" t="n">
-        <v>-20.89507868022617</v>
+        <v>90.33669999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>6.527852628327554</v>
+        <v>0.8562</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.160612400917737</v>
+        <v>-23.2497</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.619223681743943</v>
+        <v>12.897</v>
       </c>
       <c r="L55" t="n">
-        <v>-20.14706213456029</v>
+        <v>-7.2409</v>
       </c>
       <c r="M55" t="n">
-        <v>25.13680564131991</v>
+        <v>-2.5847</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-7.7565</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-27.9348</v>
+      </c>
+      <c r="P55" t="n">
+        <v>5.9575</v>
       </c>
     </row>
     <row r="56">
@@ -2815,37 +3316,46 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.1953016477443792</v>
+        <v>-0.219394</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4115599215184635</v>
+        <v>-0.833203</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6405258903792836</v>
+        <v>0.9507409999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4957207243095659</v>
+        <v>0.649869</v>
       </c>
       <c r="G56" t="n">
-        <v>7388.342494281258</v>
+        <v>6855.8741</v>
       </c>
       <c r="H56" t="n">
-        <v>-22.47463246923616</v>
+        <v>86.1177</v>
       </c>
       <c r="I56" t="n">
-        <v>7.074346480319852</v>
+        <v>0.9308</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.464514053449682</v>
+        <v>-28.0961</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.761503522647113</v>
+        <v>12.897</v>
       </c>
       <c r="L56" t="n">
-        <v>-21.6263035650131</v>
+        <v>-8.2478</v>
       </c>
       <c r="M56" t="n">
-        <v>18.61073358629342</v>
+        <v>-3.2175</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-8.821300000000001</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-35.4856</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="57">
@@ -2858,37 +3368,46 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.1885843288659999</v>
+        <v>-0.211848</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.505400935260617</v>
+        <v>-1</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6973030781167183</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5136954702358706</v>
+        <v>0.7447780000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>7329.24529966349</v>
+        <v>6694.9162</v>
       </c>
       <c r="H57" t="n">
-        <v>-24.81507082722591</v>
+        <v>81.81229999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>7.752183819094636</v>
+        <v>0.9999</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.95669770351566</v>
+        <v>-30.6746</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.783867273605719</v>
+        <v>12.897</v>
       </c>
       <c r="L57" t="n">
-        <v>-23.80345198525265</v>
+        <v>-9.218400000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>11.99749491118305</v>
+        <v>-3.6677</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-9.5502</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-40.2138</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="58">
@@ -2901,37 +3420,46 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.1820980493743076</v>
+        <v>-0.204561</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6505157590748637</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7909082256168454</v>
+        <v>0.528314</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5462518019940488</v>
+        <v>0.849005</v>
       </c>
       <c r="G58" t="n">
-        <v>7247.669230638782</v>
+        <v>6525.4246</v>
       </c>
       <c r="H58" t="n">
-        <v>-27.76303411661754</v>
+        <v>77.7222</v>
       </c>
       <c r="I58" t="n">
-        <v>9.040387331365361</v>
+        <v>0.9999</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.61679079765811</v>
+        <v>-15.8144</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.684925583811379</v>
+        <v>9.964600000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>-26.02436316672167</v>
+        <v>-8.109299999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>5.235607692289728</v>
+        <v>-1.5612</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-7.6407</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-23.161</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="59">
@@ -2944,36 +3472,45 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-0.1758348627657692</v>
+        <v>-0.197526</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.9585260660340319</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9861483875316468</v>
+        <v>0.479544</v>
       </c>
       <c r="F59" t="n">
-        <v>0.587994712863646</v>
+        <v>0.741013</v>
       </c>
       <c r="G59" t="n">
-        <v>7127.448194766481</v>
+        <v>6608.7252</v>
       </c>
       <c r="H59" t="n">
-        <v>-33.9200229261997</v>
+        <v>73.8366</v>
       </c>
       <c r="I59" t="n">
-        <v>11.65571604268671</v>
+        <v>0.9999</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.004391470640032</v>
+        <v>-13.7268</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.240622049478463</v>
+        <v>9.6858</v>
       </c>
       <c r="L59" t="n">
-        <v>-31.50932040363148</v>
+        <v>-8.071400000000001</v>
       </c>
       <c r="M59" t="n">
+        <v>-1.2555</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-7.4844</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-20.8524</v>
+      </c>
+      <c r="P59" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2987,36 +3524,45 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.1697870958535327</v>
+        <v>-0.190732</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.494392721239313</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0.43882</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6678900317545025</v>
+        <v>0.653132</v>
       </c>
       <c r="G60" t="n">
-        <v>6921.629181524009</v>
+        <v>6708.0806</v>
       </c>
       <c r="H60" t="n">
-        <v>-38.98456132034288</v>
+        <v>70.14530000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>13.5609686622817</v>
+        <v>0.9999</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.79556761566856</v>
+        <v>-11.9972</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.166995123189411</v>
+        <v>9.449299999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>-38.38615539691915</v>
+        <v>-8.5647</v>
       </c>
       <c r="M60" t="n">
+        <v>-1.0036</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-7.3546</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-19.4707</v>
+      </c>
+      <c r="P60" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3030,36 +3576,45 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.1639473393668137</v>
+        <v>-0.184172</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4777855685755709</v>
+        <v>0.406608</v>
       </c>
       <c r="F61" t="n">
-        <v>0.784595573021893</v>
+        <v>0.5865860000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>6729.466263371608</v>
+        <v>6817.8625</v>
       </c>
       <c r="H61" t="n">
-        <v>-19.83739109770651</v>
+        <v>66.63849999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>4.005190670118395</v>
+        <v>0.9998</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.922063204480237</v>
+        <v>-10.6465</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.336182184576543</v>
+        <v>9.2577</v>
       </c>
       <c r="L61" t="n">
-        <v>-21.09044581664489</v>
+        <v>-10.0061</v>
       </c>
       <c r="M61" t="n">
+        <v>-0.8087</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-7.2528</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-19.4564</v>
+      </c>
+      <c r="P61" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3073,36 +3628,45 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.6783582395846885</v>
+        <v>-0.177837</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9510229603765225</v>
+        <v>0.384896</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6816618019795847</v>
+        <v>0.546515</v>
       </c>
       <c r="G62" t="n">
-        <v>6817.626852746662</v>
+        <v>6932.7724</v>
       </c>
       <c r="H62" t="n">
-        <v>-33.7179099592189</v>
+        <v>63.3071</v>
       </c>
       <c r="I62" t="n">
-        <v>8.96577585542645</v>
+        <v>0.9998</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.403538551208298</v>
+        <v>-9.7643</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.399122663503443</v>
+        <v>9.1212</v>
       </c>
       <c r="L62" t="n">
-        <v>-31.55479531850419</v>
+        <v>-3.6746</v>
       </c>
       <c r="M62" t="n">
+        <v>-0.6842</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-7.1856</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-12.1876</v>
+      </c>
+      <c r="P62" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3116,36 +3680,45 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.6550263903059231</v>
+        <v>-0.171721</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9448444040550402</v>
+        <v>0.341393</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7245450343727927</v>
+        <v>0.449786</v>
       </c>
       <c r="G63" t="n">
-        <v>6660.352687283735</v>
+        <v>7047.047</v>
       </c>
       <c r="H63" t="n">
-        <v>-33.03879445433884</v>
+        <v>60.1422</v>
       </c>
       <c r="I63" t="n">
-        <v>8.775843456344807</v>
+        <v>0.9998</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.51164723869297</v>
+        <v>-7.8998</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.375902246462719</v>
+        <v>8.872999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>-31.15050048314972</v>
+        <v>-3.0734</v>
       </c>
       <c r="M63" t="n">
+        <v>-0.411</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-7.0461</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-9.5572</v>
+      </c>
+      <c r="P63" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3159,36 +3732,45 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-0.6324970302710422</v>
+        <v>-0.165814</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9309898404531114</v>
+        <v>0.302905</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7462320254551729</v>
+        <v>0.365443</v>
       </c>
       <c r="G64" t="n">
-        <v>6521.895216527841</v>
+        <v>7171.6458</v>
       </c>
       <c r="H64" t="n">
-        <v>-32.5501318938768</v>
+        <v>57.1356</v>
       </c>
       <c r="I64" t="n">
-        <v>8.828646481545986</v>
+        <v>0.9998</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.528000016328138</v>
+        <v>-6.2575</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.635842742245273</v>
+        <v>8.6516</v>
       </c>
       <c r="L64" t="n">
-        <v>-30.88532817090422</v>
+        <v>-2.5439</v>
       </c>
       <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-6.923</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-7.0729</v>
+      </c>
+      <c r="P64" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3202,36 +3784,45 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.6107425581965442</v>
+        <v>-0.160111</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9133795569894027</v>
+        <v>0.268067</v>
       </c>
       <c r="F65" t="n">
-        <v>0.756592496982146</v>
+        <v>0.289995</v>
       </c>
       <c r="G65" t="n">
-        <v>6404.210774648501</v>
+        <v>7303.0289</v>
       </c>
       <c r="H65" t="n">
-        <v>-31.74711588245246</v>
+        <v>54.2793</v>
       </c>
       <c r="I65" t="n">
-        <v>8.633207300053595</v>
+        <v>0.9998</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.611230059910187</v>
+        <v>-4.7763</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.376580520106641</v>
+        <v>8.4497</v>
       </c>
       <c r="L65" t="n">
-        <v>-30.10171916241569</v>
+        <v>-2.0665</v>
       </c>
       <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-6.8119</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-5.205</v>
+      </c>
+      <c r="P65" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3245,36 +3836,45 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-0.5897363221335852</v>
+        <v>-0.154604</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0.891725398058963</v>
+        <v>0.237886</v>
       </c>
       <c r="F66" t="n">
-        <v>0.7549726898134446</v>
+        <v>0.226047</v>
       </c>
       <c r="G66" t="n">
-        <v>6307.099918688949</v>
+        <v>7438.6925</v>
       </c>
       <c r="H66" t="n">
-        <v>-32.70323019488668</v>
+        <v>51.5659</v>
       </c>
       <c r="I66" t="n">
-        <v>8.318103676895714</v>
+        <v>0.9998</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.548802158779874</v>
+        <v>-3.5014</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.158675091389358</v>
+        <v>8.2727</v>
       </c>
       <c r="L66" t="n">
-        <v>-31.0926037681602</v>
+        <v>-1.6558</v>
       </c>
       <c r="M66" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-6.716</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-3.3707</v>
+      </c>
+      <c r="P66" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3288,36 +3888,45 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.5694525868160069</v>
+        <v>-0.149287</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8750164474438744</v>
+        <v>0.2107</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7639096515696687</v>
+        <v>0.169335</v>
       </c>
       <c r="G67" t="n">
-        <v>6230.527227790573</v>
+        <v>7575.8801</v>
       </c>
       <c r="H67" t="n">
-        <v>-31.35808416851622</v>
+        <v>48.9881</v>
       </c>
       <c r="I67" t="n">
-        <v>8.253797219734132</v>
+        <v>0.9998</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.509548900920925</v>
+        <v>-2.3583</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.580640259450209</v>
+        <v>8.111800000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>-30.19447610915322</v>
+        <v>-1.2877</v>
       </c>
       <c r="M67" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-6.6299</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-1.7689</v>
+      </c>
+      <c r="P67" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3331,37 +3940,46 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.5498665021314183</v>
+        <v>-0.144152</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8539827229447516</v>
+        <v>0.18628</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7602905520333334</v>
+        <v>0.11929</v>
       </c>
       <c r="G68" t="n">
-        <v>6169.966281289579</v>
+        <v>7712.9422</v>
       </c>
       <c r="H68" t="n">
-        <v>-29.85635991158985</v>
+        <v>46.5392</v>
       </c>
       <c r="I68" t="n">
-        <v>7.820406968547336</v>
+        <v>0.9998</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.399816264960658</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.002046170236864</v>
+        <v>7.9659</v>
       </c>
       <c r="L68" t="n">
-        <v>-28.43781537824004</v>
+        <v>-0.9588</v>
       </c>
       <c r="M68" t="n">
-        <v>0.01</v>
+        <v>0.5423</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-6.5528</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="P68" t="n">
+        <v>3.1878</v>
       </c>
     </row>
     <row r="69">
@@ -3374,37 +3992,46 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.5309540726767001</v>
+        <v>-0.139194</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8271750666776603</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7405524850024003</v>
+        <v>0.08154</v>
       </c>
       <c r="G69" t="n">
-        <v>6125.978291688245</v>
+        <v>7848.5081</v>
       </c>
       <c r="H69" t="n">
-        <v>-29.87242368842933</v>
+        <v>44.3716</v>
       </c>
       <c r="I69" t="n">
-        <v>7.810495365425036</v>
+        <v>0.9282</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.461051935118359</v>
+        <v>8.9373</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.043411990138225</v>
+        <v>-1.2144</v>
       </c>
       <c r="L69" t="n">
-        <v>-28.56639224826087</v>
+        <v>6.0034</v>
       </c>
       <c r="M69" t="n">
-        <v>0.01</v>
+        <v>2.4903</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-4.7151</v>
+      </c>
+      <c r="O69" t="n">
+        <v>11.5014</v>
+      </c>
+      <c r="P69" t="n">
+        <v>8.894</v>
       </c>
     </row>
     <row r="70">
@@ -3417,37 +4044,46 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.5126921283606354</v>
+        <v>-0.134406</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0.804690293754255</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7299954134840489</v>
+        <v>0.163938</v>
       </c>
       <c r="G70" t="n">
-        <v>6099.79292918059</v>
+        <v>8063.6573</v>
       </c>
       <c r="H70" t="n">
-        <v>-30.25674198286794</v>
+        <v>42.5977</v>
       </c>
       <c r="I70" t="n">
-        <v>7.415589703511766</v>
+        <v>0.7912</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.216692203883072</v>
+        <v>7.5026</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.03630938984347</v>
+        <v>-2.1161</v>
       </c>
       <c r="L70" t="n">
-        <v>-29.09415387308272</v>
+        <v>5.5535</v>
       </c>
       <c r="M70" t="n">
-        <v>0.01</v>
+        <v>2.1464</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-3.9263</v>
+      </c>
+      <c r="O70" t="n">
+        <v>9.1602</v>
+      </c>
+      <c r="P70" t="n">
+        <v>14.3516</v>
       </c>
     </row>
     <row r="71">
@@ -3460,37 +4096,46 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-0.4950582960176489</v>
+        <v>-0.129784</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7866338107461515</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7289387868212565</v>
+        <v>0.189964</v>
       </c>
       <c r="G71" t="n">
-        <v>6087.468489385404</v>
+        <v>8257.291499999999</v>
       </c>
       <c r="H71" t="n">
-        <v>-28.98576109625762</v>
+        <v>41.1854</v>
       </c>
       <c r="I71" t="n">
-        <v>7.403786940720227</v>
+        <v>0.6515</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.161198820202999</v>
+        <v>6.6065</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.341554356752769</v>
+        <v>-3.0346</v>
       </c>
       <c r="L71" t="n">
-        <v>-28.08472733249316</v>
+        <v>5.3292</v>
       </c>
       <c r="M71" t="n">
-        <v>0.01</v>
+        <v>1.9193</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-3.0926</v>
+      </c>
+      <c r="O71" t="n">
+        <v>7.7278</v>
+      </c>
+      <c r="P71" t="n">
+        <v>19.6004</v>
       </c>
     </row>
     <row r="72">
@@ -3503,37 +4148,46 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.4780309719978834</v>
+        <v>-0.12532</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>0.914324</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7653151901649576</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7182105454176855</v>
+        <v>0.191257</v>
       </c>
       <c r="G72" t="n">
-        <v>6085.404735073788</v>
+        <v>8431.562400000001</v>
       </c>
       <c r="H72" t="n">
-        <v>-27.93506141350417</v>
+        <v>40.1062</v>
       </c>
       <c r="I72" t="n">
-        <v>7.174361753483435</v>
+        <v>0.5113</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.054416168344997</v>
+        <v>5.388</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.859217176682098</v>
+        <v>-3.2933</v>
       </c>
       <c r="L72" t="n">
-        <v>-26.67433300504782</v>
+        <v>3.6218</v>
       </c>
       <c r="M72" t="n">
-        <v>0.01</v>
+        <v>1.5975</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-2.3294</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4.9846</v>
+      </c>
+      <c r="P72" t="n">
+        <v>24.4516</v>
       </c>
     </row>
     <row r="73">
@@ -3546,37 +4200,46 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.4615892957000254</v>
+        <v>-0.121009</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>0.618766</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7406571586204611</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6976696573010894</v>
+        <v>0.1646</v>
       </c>
       <c r="G73" t="n">
-        <v>6094.20666648393</v>
+        <v>8588.406199999999</v>
       </c>
       <c r="H73" t="n">
-        <v>-26.37548155573994</v>
+        <v>39.3234</v>
       </c>
       <c r="I73" t="n">
-        <v>6.710226104774095</v>
+        <v>0.3782</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.917055068221644</v>
+        <v>3.1034</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.038303683619717</v>
+        <v>-1.8812</v>
       </c>
       <c r="L73" t="n">
-        <v>-25.6206142028072</v>
+        <v>2.3377</v>
       </c>
       <c r="M73" t="n">
-        <v>0.01</v>
+        <v>0.9852</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-1.8069</v>
+      </c>
+      <c r="O73" t="n">
+        <v>2.7382</v>
+      </c>
+      <c r="P73" t="n">
+        <v>28.65</v>
       </c>
     </row>
     <row r="74">
@@ -3589,37 +4252,46 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-0.4457131240144599</v>
+        <v>-0.116847</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>0.429252</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7156362985779502</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6748079364087256</v>
+        <v>0.126143</v>
       </c>
       <c r="G74" t="n">
-        <v>6114.457420525307</v>
+        <v>8729.565500000001</v>
       </c>
       <c r="H74" t="n">
-        <v>-25.20870234739602</v>
+        <v>38.7898</v>
       </c>
       <c r="I74" t="n">
-        <v>6.639072091829056</v>
+        <v>0.2614</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.868472913693005</v>
+        <v>1.7077</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.838752926283129</v>
+        <v>-1.1839</v>
       </c>
       <c r="L74" t="n">
-        <v>-24.2768560955431</v>
+        <v>1.3621</v>
       </c>
       <c r="M74" t="n">
-        <v>0.01</v>
+        <v>0.6004</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-1.2703</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="P74" t="n">
+        <v>31.7502</v>
       </c>
     </row>
     <row r="75">
@@ -3632,37 +4304,46 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-0.4303830066454429</v>
+        <v>-0.112828</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>0.270527</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6894443357657094</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6476533228006663</v>
+        <v>0.08784500000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>6145.193529183801</v>
+        <v>8856.609</v>
       </c>
       <c r="H75" t="n">
-        <v>-24.66138913696641</v>
+        <v>38.4378</v>
       </c>
       <c r="I75" t="n">
-        <v>6.450573510312288</v>
+        <v>0.174</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.701131388021401</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.938867296994072</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>-23.8508143116696</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>0.01</v>
+        <v>0.3053</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-0.8804</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="P75" t="n">
+        <v>32.3665</v>
       </c>
     </row>
     <row r="76">
@@ -3675,37 +4356,46 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-0.4155801622820559</v>
+        <v>-0.108948</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>0.048524</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6664202170008942</v>
+        <v>0.098458</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6271001367970959</v>
+        <v>0.053947</v>
       </c>
       <c r="G76" t="n">
-        <v>6185.952008382566</v>
+        <v>8970.9481</v>
       </c>
       <c r="H76" t="n">
-        <v>-23.45574329359362</v>
+        <v>38.1342</v>
       </c>
       <c r="I76" t="n">
-        <v>6.08875265334787</v>
+        <v>0.1512</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.681196667774822</v>
+        <v>-2.4733</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.673092953876485</v>
+        <v>1.5293</v>
       </c>
       <c r="L76" t="n">
-        <v>-22.72128026189706</v>
+        <v>-0.0948</v>
       </c>
       <c r="M76" t="n">
-        <v>0.01</v>
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-1.146</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-2.1849</v>
+      </c>
+      <c r="P76" t="n">
+        <v>28.5662</v>
       </c>
     </row>
     <row r="77">
@@ -3718,37 +4408,46 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.4012864555887516</v>
+        <v>-0.105201</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>-0.293534</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6426756094676429</v>
+        <v>0.294183</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6034728846972282</v>
+        <v>0.054217</v>
       </c>
       <c r="G77" t="n">
-        <v>6234.146699043863</v>
+        <v>9024.624</v>
       </c>
       <c r="H77" t="n">
-        <v>-23.76719277788225</v>
+        <v>37.6558</v>
       </c>
       <c r="I77" t="n">
-        <v>6.139216618612207</v>
+        <v>0.2414</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.475559473345021</v>
+        <v>-8.0806</v>
       </c>
       <c r="K77" t="n">
-        <v>-1.741336395139849</v>
+        <v>5.7527</v>
       </c>
       <c r="L77" t="n">
-        <v>-22.84487202775492</v>
+        <v>-1.3062</v>
       </c>
       <c r="M77" t="n">
-        <v>0.01</v>
+        <v>-0.8662</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-2.4284</v>
+      </c>
+      <c r="O77" t="n">
+        <v>-6.9287</v>
+      </c>
+      <c r="P77" t="n">
+        <v>23.6973</v>
       </c>
     </row>
     <row r="78">
@@ -3761,37 +4460,46 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.3874843749872999</v>
+        <v>-0.101582</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>-0.426102</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6236973554256544</v>
+        <v>0.386379</v>
       </c>
       <c r="F78" t="n">
-        <v>0.590532451095886</v>
+        <v>0.101817</v>
       </c>
       <c r="G78" t="n">
-        <v>6289.394224405656</v>
+        <v>8975.070299999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-22.49101823241928</v>
+        <v>36.9579</v>
       </c>
       <c r="I78" t="n">
-        <v>5.754958780333</v>
+        <v>0.3588</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.396455106240725</v>
+        <v>-10.6149</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.516947446613637</v>
+        <v>7.9973</v>
       </c>
       <c r="L78" t="n">
-        <v>-21.64946200494063</v>
+        <v>-2.1681</v>
       </c>
       <c r="M78" t="n">
-        <v>0.01</v>
+        <v>-1.1564</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-3.4798</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-9.421900000000001</v>
+      </c>
+      <c r="P78" t="n">
+        <v>18.6126</v>
       </c>
     </row>
     <row r="79">
@@ -3804,37 +4512,46 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.3741570112029147</v>
+        <v>-0.09808799999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>-0.536428</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6024826474856899</v>
+        <v>0.468028</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5708140907069379</v>
+        <v>0.155309</v>
       </c>
       <c r="G79" t="n">
-        <v>6348.606124252263</v>
+        <v>8884.3737</v>
       </c>
       <c r="H79" t="n">
-        <v>-21.81167497562931</v>
+        <v>36.0406</v>
       </c>
       <c r="I79" t="n">
-        <v>5.501881731791387</v>
+        <v>0.4836</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.260575814962352</v>
+        <v>-12.8193</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.596531669513306</v>
+        <v>10.0633</v>
       </c>
       <c r="L79" t="n">
-        <v>-21.16690072831359</v>
+        <v>-2.9636</v>
       </c>
       <c r="M79" t="n">
-        <v>0.01</v>
+        <v>-1.3983</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-4.5351</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-11.653</v>
+      </c>
+      <c r="P79" t="n">
+        <v>13.3605</v>
       </c>
     </row>
     <row r="80">
@@ -3847,37 +4564,46 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.3612880365482775</v>
+        <v>-0.09471499999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>-0.705448</v>
       </c>
       <c r="E80" t="n">
-        <v>0.582951021231197</v>
+        <v>0.5843390000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5541574617072986</v>
+        <v>0.209715</v>
       </c>
       <c r="G80" t="n">
-        <v>6412.504188084192</v>
+        <v>8761.9223</v>
       </c>
       <c r="H80" t="n">
-        <v>-20.96918507030432</v>
+        <v>34.9066</v>
       </c>
       <c r="I80" t="n">
-        <v>5.452054916068389</v>
+        <v>0.6173</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.135031314712217</v>
+        <v>-16.0553</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.454925416658829</v>
+        <v>12.8202</v>
       </c>
       <c r="L80" t="n">
-        <v>-20.10708688560698</v>
+        <v>-3.9134</v>
       </c>
       <c r="M80" t="n">
-        <v>0.01</v>
+        <v>-1.7759</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-5.7737</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-14.6981</v>
+      </c>
+      <c r="P80" t="n">
+        <v>7.9158</v>
       </c>
     </row>
     <row r="81">
@@ -3890,37 +4616,46 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-0.3488616849200784</v>
+        <v>-0.091457</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E81" t="n">
-        <v>0.5622878232722579</v>
+        <v>0.777263</v>
       </c>
       <c r="F81" t="n">
-        <v>0.533565345880449</v>
+        <v>0.272811</v>
       </c>
       <c r="G81" t="n">
-        <v>6479.778258660174</v>
+        <v>8593.5605</v>
       </c>
       <c r="H81" t="n">
-        <v>-20.37469298476505</v>
+        <v>33.5571</v>
       </c>
       <c r="I81" t="n">
-        <v>5.145353868815303</v>
+        <v>0.7641</v>
       </c>
       <c r="J81" t="n">
-        <v>-3.004409098455757</v>
+        <v>-21.6398</v>
       </c>
       <c r="K81" t="n">
-        <v>-1.392090705996787</v>
+        <v>12.897</v>
       </c>
       <c r="L81" t="n">
-        <v>-19.62583892040229</v>
+        <v>-5.2366</v>
       </c>
       <c r="M81" t="n">
-        <v>0.01</v>
+        <v>-2.4686</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-7.3774</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-23.8253</v>
+      </c>
+      <c r="P81" t="n">
+        <v>2.1705</v>
       </c>
     </row>
     <row r="82">
@@ -3933,36 +4668,45 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.3368627324835682</v>
+        <v>-0.088311</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E82" t="n">
-        <v>0.5434217711764852</v>
+        <v>0.824357</v>
       </c>
       <c r="F82" t="n">
-        <v>0.5163975967322924</v>
+        <v>0.40194</v>
       </c>
       <c r="G82" t="n">
-        <v>6550.656521158028</v>
+        <v>8345.5728</v>
       </c>
       <c r="H82" t="n">
-        <v>-19.45450918729392</v>
+        <v>31.9878</v>
       </c>
       <c r="I82" t="n">
-        <v>4.943060019834414</v>
+        <v>0.9321</v>
       </c>
       <c r="J82" t="n">
-        <v>-2.990331068630997</v>
+        <v>-22.9769</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.312783283460255</v>
+        <v>12.897</v>
       </c>
       <c r="L82" t="n">
-        <v>-18.81456351955076</v>
+        <v>-6.2344</v>
       </c>
       <c r="M82" t="n">
+        <v>-2.5842</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-8.5517</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-27.4502</v>
+      </c>
+      <c r="P82" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3976,36 +4720,45 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.3252764790214572</v>
+        <v>-0.085274</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E83" t="n">
-        <v>0.5244701563154104</v>
+        <v>0.865573</v>
       </c>
       <c r="F83" t="n">
-        <v>0.497984193234883</v>
+        <v>0.515666</v>
       </c>
       <c r="G83" t="n">
-        <v>6623.879983453983</v>
+        <v>8098.8372</v>
       </c>
       <c r="H83" t="n">
-        <v>-18.2982372966642</v>
+        <v>30.3889</v>
       </c>
       <c r="I83" t="n">
-        <v>4.902971158900785</v>
+        <v>0.9997</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.834085599090726</v>
+        <v>-24.542</v>
       </c>
       <c r="K83" t="n">
-        <v>-1.467405004072265</v>
+        <v>12.897</v>
       </c>
       <c r="L83" t="n">
-        <v>-17.69675674092641</v>
+        <v>-7.2303</v>
       </c>
       <c r="M83" t="n">
+        <v>-2.7886</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-9.098800000000001</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-30.7627</v>
+      </c>
+      <c r="P83" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4019,36 +4772,45 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-0.3140887299243098</v>
+        <v>-0.082341</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0.5043919632643874</v>
+        <v>0.319565</v>
       </c>
       <c r="F84" t="n">
-        <v>0.4757580833501939</v>
+        <v>0.617027</v>
       </c>
       <c r="G84" t="n">
-        <v>6699.25690695088</v>
+        <v>7856.1669</v>
       </c>
       <c r="H84" t="n">
-        <v>-18.54021490235323</v>
+        <v>28.8699</v>
       </c>
       <c r="I84" t="n">
-        <v>4.7823774700829</v>
+        <v>0.9997</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.672352121201712</v>
+        <v>-8.236599999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-1.382546937700945</v>
+        <v>8.413399999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>-17.81273649117299</v>
+        <v>-5.9074</v>
       </c>
       <c r="M84" t="n">
+        <v>-0.588</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-7.0402</v>
+      </c>
+      <c r="O84" t="n">
+        <v>-13.3589</v>
+      </c>
+      <c r="P84" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4062,36 +4824,45 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-0.3032857788003735</v>
+        <v>-0.079509</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0.488718664769112</v>
+        <v>0.272845</v>
       </c>
       <c r="F85" t="n">
-        <v>0.4635822149218463</v>
+        <v>0.5038049999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>6777.135234623599</v>
+        <v>7910.7678</v>
       </c>
       <c r="H85" t="n">
-        <v>-17.61291429150478</v>
+        <v>27.4269</v>
       </c>
       <c r="I85" t="n">
-        <v>4.494595615829653</v>
+        <v>0.9996</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.635553668388734</v>
+        <v>-6.1793</v>
       </c>
       <c r="K85" t="n">
-        <v>-1.407916492876251</v>
+        <v>8.1614</v>
       </c>
       <c r="L85" t="n">
-        <v>-17.16178883694011</v>
+        <v>-6.0156</v>
       </c>
       <c r="M85" t="n">
+        <v>-0.281</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-6.8875</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-11.202</v>
+      </c>
+      <c r="P85" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4105,36 +4876,45 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-0.2928543906835349</v>
+        <v>-0.076774</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4727612776125384</v>
+        <v>0.235432</v>
       </c>
       <c r="F86" t="n">
-        <v>0.4497672173225088</v>
+        <v>0.414303</v>
       </c>
       <c r="G86" t="n">
-        <v>6855.062378776683</v>
+        <v>7983.2684</v>
       </c>
       <c r="H86" t="n">
-        <v>-16.85594425894774</v>
+        <v>26.0561</v>
       </c>
       <c r="I86" t="n">
-        <v>4.463289356298301</v>
+        <v>0.9996</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.554023316256315</v>
+        <v>-4.5386</v>
       </c>
       <c r="K86" t="n">
-        <v>-1.377343208790723</v>
+        <v>7.9576</v>
       </c>
       <c r="L86" t="n">
-        <v>-16.32402142769648</v>
+        <v>-6.7822</v>
       </c>
       <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-6.7655</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-10.1287</v>
+      </c>
+      <c r="P86" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4148,36 +4928,45 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-0.2827817858188307</v>
+        <v>-0.07413400000000001</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0.4560220036870187</v>
+        <v>0.207846</v>
       </c>
       <c r="F87" t="n">
-        <v>0.43310054467047</v>
+        <v>0.349869</v>
       </c>
       <c r="G87" t="n">
-        <v>6933.175502092745</v>
+        <v>8067.2253</v>
       </c>
       <c r="H87" t="n">
-        <v>-16.18680624275287</v>
+        <v>24.7538</v>
       </c>
       <c r="I87" t="n">
-        <v>4.236611713061921</v>
+        <v>0.9996</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.382087712780686</v>
+        <v>-3.3381</v>
       </c>
       <c r="K87" t="n">
-        <v>-1.139843584007507</v>
+        <v>7.805</v>
       </c>
       <c r="L87" t="n">
-        <v>-15.47212582647914</v>
+        <v>-7.5894</v>
       </c>
       <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-6.676</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-9.798500000000001</v>
+      </c>
+      <c r="P87" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4191,36 +4980,45 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-0.27305562400565</v>
+        <v>-0.07158399999999999</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4388882580324794</v>
+        <v>0.189074</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4145815850670734</v>
+        <v>0.307907</v>
       </c>
       <c r="G88" t="n">
-        <v>7011.846950039961</v>
+        <v>8156.5799</v>
       </c>
       <c r="H88" t="n">
-        <v>-15.68347373135643</v>
+        <v>23.5166</v>
       </c>
       <c r="I88" t="n">
-        <v>4.087169245734005</v>
+        <v>0.9996</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.412425403509401</v>
+        <v>-2.5324</v>
       </c>
       <c r="K88" t="n">
-        <v>-1.158225542434353</v>
+        <v>7.6981</v>
       </c>
       <c r="L88" t="n">
-        <v>-15.16695543156618</v>
+        <v>-1.3685</v>
       </c>
       <c r="M88" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-6.6156</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-2.5592</v>
+      </c>
+      <c r="P88" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4234,37 +5032,46 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.2636639894794452</v>
+        <v>-0.069122</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4238313916218076</v>
+        <v>0.148792</v>
       </c>
       <c r="F89" t="n">
-        <v>0.4004185053559058</v>
+        <v>0.210336</v>
       </c>
       <c r="G89" t="n">
-        <v>7091.218126019725</v>
+        <v>8246.3848</v>
       </c>
       <c r="H89" t="n">
-        <v>-15.30671842214072</v>
+        <v>22.3413</v>
       </c>
       <c r="I89" t="n">
-        <v>3.932042820659372</v>
+        <v>0.9996</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.328468670397693</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>-1.149135652774204</v>
+        <v>7.4807</v>
       </c>
       <c r="L89" t="n">
-        <v>-14.85227992465325</v>
+        <v>-0.7955</v>
       </c>
       <c r="M89" t="n">
-        <v>0.01</v>
+        <v>0.5238</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-6.4839</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="P89" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="90">
@@ -4277,37 +5084,46 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-0.2545953763134304</v>
+        <v>-0.066744</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4101049372974608</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3887739024600759</v>
+        <v>0.133452</v>
       </c>
       <c r="G90" t="n">
-        <v>7170.180617606849</v>
+        <v>8347.3501</v>
       </c>
       <c r="H90" t="n">
-        <v>-14.33543252725649</v>
+        <v>21.3505</v>
       </c>
       <c r="I90" t="n">
-        <v>3.827321090409245</v>
+        <v>0.8817</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.232392220069968</v>
+        <v>8.9108</v>
       </c>
       <c r="K90" t="n">
-        <v>-1.142237993663569</v>
+        <v>-1.7944</v>
       </c>
       <c r="L90" t="n">
-        <v>-13.88274165058078</v>
+        <v>6.1134</v>
       </c>
       <c r="M90" t="n">
-        <v>0.01</v>
+        <v>2.4436</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-4.4239</v>
+      </c>
+      <c r="O90" t="n">
+        <v>11.2495</v>
+      </c>
+      <c r="P90" t="n">
+        <v>7.9214</v>
       </c>
     </row>
     <row r="91">
@@ -4320,37 +5136,46 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-0.2458386743223817</v>
+        <v>-0.06444900000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>0.394675377515123</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3720917579818534</v>
+        <v>0.192566</v>
       </c>
       <c r="G91" t="n">
-        <v>7248.110087197434</v>
+        <v>8512.615100000001</v>
       </c>
       <c r="H91" t="n">
-        <v>-14.28962579311549</v>
+        <v>20.679</v>
       </c>
       <c r="I91" t="n">
-        <v>3.671353977603379</v>
+        <v>0.6169</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.115051140067537</v>
+        <v>7.0527</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.9638123124655853</v>
+        <v>-3.5106</v>
       </c>
       <c r="L91" t="n">
-        <v>-13.69713526804523</v>
+        <v>5.6156</v>
       </c>
       <c r="M91" t="n">
-        <v>0.01</v>
+        <v>1.9812</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-2.8518</v>
+      </c>
+      <c r="O91" t="n">
+        <v>8.287100000000001</v>
+      </c>
+      <c r="P91" t="n">
+        <v>13.0754</v>
       </c>
     </row>
     <row r="92">
@@ -4363,37 +5188,46 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.2373831554512717</v>
+        <v>-0.062232</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3814737184390975</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3602264074695644</v>
+        <v>0.19841</v>
       </c>
       <c r="G92" t="n">
-        <v>7325.961389720129</v>
+        <v>8661.3536</v>
       </c>
       <c r="H92" t="n">
-        <v>-13.33151973329908</v>
+        <v>20.2989</v>
       </c>
       <c r="I92" t="n">
-        <v>3.501272192174293</v>
+        <v>0.3559</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.024066872132321</v>
+        <v>5.735</v>
       </c>
       <c r="K92" t="n">
-        <v>-1.053380472059468</v>
+        <v>-5.2027</v>
       </c>
       <c r="L92" t="n">
-        <v>-12.90769488531658</v>
+        <v>5.3377</v>
       </c>
       <c r="M92" t="n">
-        <v>0.01</v>
+        <v>1.6373</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-1.2751</v>
+      </c>
+      <c r="O92" t="n">
+        <v>6.2322</v>
+      </c>
+      <c r="P92" t="n">
+        <v>17.9764</v>
       </c>
     </row>
     <row r="93">
@@ -4406,37 +5240,46 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-0.2292184606320598</v>
+        <v>-0.060091</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>0.937056</v>
       </c>
       <c r="E93" t="n">
-        <v>0.3673035779660216</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3452127933349044</v>
+        <v>0.181368</v>
       </c>
       <c r="G93" t="n">
-        <v>7402.628391528567</v>
+        <v>8795.218199999999</v>
       </c>
       <c r="H93" t="n">
-        <v>-12.8368609170425</v>
+        <v>20.1827</v>
       </c>
       <c r="I93" t="n">
-        <v>3.387020505244534</v>
+        <v>0.1093</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.978839860445702</v>
+        <v>4.3007</v>
       </c>
       <c r="K93" t="n">
-        <v>-1.062411420607097</v>
+        <v>-6.3137</v>
       </c>
       <c r="L93" t="n">
-        <v>-12.49109169285076</v>
+        <v>3.7226</v>
       </c>
       <c r="M93" t="n">
-        <v>0.01</v>
+        <v>1.2533</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>2.9628</v>
+      </c>
+      <c r="P93" t="n">
+        <v>22.1695</v>
       </c>
     </row>
     <row r="94">
@@ -4449,37 +5292,46 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.2213345870925387</v>
+        <v>-0.058025</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>0.583135</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3541500242643189</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.3320385929294503</v>
+        <v>0.138449</v>
       </c>
       <c r="G94" t="n">
-        <v>7478.713763392699</v>
+        <v>8915.696400000001</v>
       </c>
       <c r="H94" t="n">
-        <v>-12.96742916090608</v>
+        <v>20.2821</v>
       </c>
       <c r="I94" t="n">
-        <v>3.324229438306774</v>
+        <v>-0.0931</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.901091472589895</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.9560601177204389</v>
+        <v>-4.888</v>
       </c>
       <c r="L94" t="n">
-        <v>-12.50035131290964</v>
+        <v>2.3035</v>
       </c>
       <c r="M94" t="n">
-        <v>0.01</v>
+        <v>0.4831</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1.0512</v>
+      </c>
+      <c r="O94" t="n">
+        <v>-1.0502</v>
+      </c>
+      <c r="P94" t="n">
+        <v>19.3287</v>
       </c>
     </row>
     <row r="95">
@@ -4492,37 +5344,46 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.2137218761016875</v>
+        <v>-0.056029</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>-0.320349</v>
       </c>
       <c r="E95" t="n">
-        <v>0.3434125436563941</v>
+        <v>0.277347</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3242266688867666</v>
+        <v>0.093572</v>
       </c>
       <c r="G95" t="n">
-        <v>7553.767374921269</v>
+        <v>9024.1268</v>
       </c>
       <c r="H95" t="n">
-        <v>-12.11299646469137</v>
+        <v>20.2344</v>
       </c>
       <c r="I95" t="n">
-        <v>3.078369217287654</v>
+        <v>0.0448</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.858097343527266</v>
+        <v>-8.794600000000001</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.8764810584622834</v>
+        <v>4.4151</v>
       </c>
       <c r="L95" t="n">
-        <v>-11.76920564939327</v>
+        <v>-0.1378</v>
       </c>
       <c r="M95" t="n">
-        <v>0.01</v>
+        <v>-1.1429</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-1.2277</v>
+      </c>
+      <c r="O95" t="n">
+        <v>-6.8879</v>
+      </c>
+      <c r="P95" t="n">
+        <v>14.4713</v>
       </c>
     </row>
     <row r="96">
@@ -4535,37 +5396,46 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-0.206371001136518</v>
+        <v>-0.054102</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>-0.628267</v>
       </c>
       <c r="E96" t="n">
-        <v>0.331262224266915</v>
+        <v>0.467059</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3122280578259926</v>
+        <v>0.125022</v>
       </c>
       <c r="G96" t="n">
-        <v>7626.684365600945</v>
+        <v>8983.040800000001</v>
       </c>
       <c r="H96" t="n">
-        <v>-11.87887986180814</v>
+        <v>19.9462</v>
       </c>
       <c r="I96" t="n">
-        <v>3.047211717715822</v>
+        <v>0.2745</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.767289007945664</v>
+        <v>-13.6988</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.9110281839086416</v>
+        <v>9.250500000000001</v>
       </c>
       <c r="L96" t="n">
-        <v>-11.50998533594663</v>
+        <v>-1.9069</v>
       </c>
       <c r="M96" t="n">
-        <v>0.01</v>
+        <v>-1.6826</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-3.3241</v>
+      </c>
+      <c r="O96" t="n">
+        <v>-11.362</v>
+      </c>
+      <c r="P96" t="n">
+        <v>9.281700000000001</v>
       </c>
     </row>
     <row r="97">
@@ -4578,37 +5448,46 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.1992729564559182</v>
+        <v>-0.052241</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>-0.896526</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3202476316779429</v>
+        <v>0.646223</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3024366880550619</v>
+        <v>0.188633</v>
       </c>
       <c r="G97" t="n">
-        <v>7698.384816907394</v>
+        <v>8851.207200000001</v>
       </c>
       <c r="H97" t="n">
-        <v>-11.91034368458233</v>
+        <v>19.413</v>
       </c>
       <c r="I97" t="n">
-        <v>2.967865971195362</v>
+        <v>0.5219</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.704355805622615</v>
+        <v>-18.366</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.8199908769912295</v>
+        <v>12.897</v>
       </c>
       <c r="L97" t="n">
-        <v>-11.46682439600081</v>
+        <v>-3.3954</v>
       </c>
       <c r="M97" t="n">
-        <v>0.01</v>
+        <v>-2.187</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-5.4824</v>
+      </c>
+      <c r="O97" t="n">
+        <v>-16.5338</v>
+      </c>
+      <c r="P97" t="n">
+        <v>3.8223</v>
       </c>
     </row>
     <row r="98">
@@ -4621,36 +5500,45 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1924190460674927</v>
+        <v>-0.050444</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3108711487847108</v>
+        <v>0.739661</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2961302567930453</v>
+        <v>0.278518</v>
       </c>
       <c r="G98" t="n">
-        <v>7768.422519377683</v>
+        <v>8642.975</v>
       </c>
       <c r="H98" t="n">
-        <v>-11.20994427845084</v>
+        <v>18.6335</v>
       </c>
       <c r="I98" t="n">
-        <v>2.932471738717377</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.652107455587557</v>
+        <v>-20.4034</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.7725702971466052</v>
+        <v>12.897</v>
       </c>
       <c r="L98" t="n">
-        <v>-10.70215029246763</v>
+        <v>-4.6255</v>
       </c>
       <c r="M98" t="n">
+        <v>-2.3229</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-7.4698</v>
+      </c>
+      <c r="O98" t="n">
+        <v>-21.9246</v>
+      </c>
+      <c r="P98" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4664,36 +5552,45 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0.1858008730738852</v>
+        <v>-0.048709</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2996807358740866</v>
+        <v>0.779856</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2846996570005034</v>
+        <v>0.386356</v>
       </c>
       <c r="G99" t="n">
-        <v>7836.144693047559</v>
+        <v>8408.846799999999</v>
       </c>
       <c r="H99" t="n">
-        <v>-10.48555499790205</v>
+        <v>17.7023</v>
       </c>
       <c r="I99" t="n">
-        <v>2.813430864783923</v>
+        <v>0.9994</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.625777877513365</v>
+        <v>-21.2304</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.8923325105290586</v>
+        <v>12.897</v>
       </c>
       <c r="L99" t="n">
-        <v>-10.19023452116055</v>
+        <v>-5.93</v>
       </c>
       <c r="M99" t="n">
+        <v>-2.3396</v>
+      </c>
+      <c r="N99" t="n">
+        <v>-8.841100000000001</v>
+      </c>
+      <c r="O99" t="n">
+        <v>-25.4441</v>
+      </c>
+      <c r="P99" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4707,36 +5604,45 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.1794103293855283</v>
+        <v>-0.047034</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2884991851502913</v>
+        <v>0.234501</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2727221394119075</v>
+        <v>0.486255</v>
       </c>
       <c r="G100" t="n">
-        <v>7902.68985580576</v>
+        <v>8178.034</v>
       </c>
       <c r="H100" t="n">
-        <v>-10.57734830417052</v>
+        <v>16.8177</v>
       </c>
       <c r="I100" t="n">
-        <v>2.587629947099531</v>
+        <v>0.9994</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.554490738953818</v>
+        <v>-4.936</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.790454024299289</v>
+        <v>7.8364</v>
       </c>
       <c r="L100" t="n">
-        <v>-10.33466312032409</v>
+        <v>-4.6652</v>
       </c>
       <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-6.7836</v>
+      </c>
+      <c r="O100" t="n">
+        <v>-8.548400000000001</v>
+      </c>
+      <c r="P100" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4750,36 +5656,45 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-0.1732395857872201</v>
+        <v>-0.045416</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0.2800315517273743</v>
+        <v>0.190593</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2669799148503854</v>
+        <v>0.377237</v>
       </c>
       <c r="G101" t="n">
-        <v>7968.171277650039</v>
+        <v>8242.9802</v>
       </c>
       <c r="H101" t="n">
-        <v>-10.23592010519206</v>
+        <v>15.9773</v>
       </c>
       <c r="I101" t="n">
-        <v>2.552599883343988</v>
+        <v>0.9994</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.540083382384735</v>
+        <v>-2.9871</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.7597508169271455</v>
+        <v>7.6034</v>
       </c>
       <c r="L101" t="n">
-        <v>-9.983154421159954</v>
+        <v>-4.7199</v>
       </c>
       <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-6.6392</v>
+      </c>
+      <c r="O101" t="n">
+        <v>-6.7428</v>
+      </c>
+      <c r="P101" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4793,36 +5708,45 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.167281082346357</v>
+        <v>-0.043854</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0.2712888795950893</v>
+        <v>0.156662</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2600194931218308</v>
+        <v>0.29377</v>
       </c>
       <c r="G102" t="n">
-        <v>8031.338374021348</v>
+        <v>8323.3855</v>
       </c>
       <c r="H102" t="n">
-        <v>-10.00626049449913</v>
+        <v>15.1789</v>
       </c>
       <c r="I102" t="n">
-        <v>2.463254558670711</v>
+        <v>0.9993</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.493000187920158</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>-0.8001681235695741</v>
+        <v>7.4221</v>
       </c>
       <c r="L102" t="n">
-        <v>-9.836174247318153</v>
+        <v>-5.344</v>
       </c>
       <c r="M102" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="N102" t="n">
+        <v>-6.5278</v>
+      </c>
+      <c r="O102" t="n">
+        <v>-4.0715</v>
+      </c>
+      <c r="P102" t="n">
         <v>0.01</v>
       </c>
     </row>

--- a/stock_simulation_results.xlsx
+++ b/stock_simulation_results.xlsx
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.029126</v>
+        <v>0.016667</v>
       </c>
       <c r="F2" t="n">
         <v>0.075</v>
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>100.0019</v>
+        <v>99.9986</v>
       </c>
     </row>
     <row r="3">
@@ -563,22 +563,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7e-05</v>
+        <v>-3.4e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.017448</v>
+        <v>0.010011</v>
       </c>
       <c r="F3" t="n">
         <v>0.045</v>
       </c>
       <c r="G3" t="n">
-        <v>9985.436900000001</v>
+        <v>9991.6667</v>
       </c>
       <c r="H3" t="n">
-        <v>100.0001</v>
+        <v>99.9999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>100.0027</v>
+        <v>99.9969</v>
       </c>
     </row>
     <row r="4">
@@ -615,22 +615,22 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2e-05</v>
+        <v>-4.3e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.010474</v>
+        <v>0.006014</v>
       </c>
       <c r="F4" t="n">
         <v>0.027</v>
       </c>
       <c r="G4" t="n">
-        <v>9978.169</v>
+        <v>9987.4943</v>
       </c>
       <c r="H4" t="n">
-        <v>100.0002</v>
+        <v>99.99979999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1524</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -648,10 +648,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1524</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>99.3412</v>
+        <v>99.9949</v>
       </c>
     </row>
     <row r="5">
@@ -667,22 +667,22 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.016537</v>
+        <v>-5e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.016516</v>
+        <v>0.003617</v>
       </c>
       <c r="F5" t="n">
-        <v>0.017724</v>
+        <v>0.0162</v>
       </c>
       <c r="G5" t="n">
-        <v>9975.115100000001</v>
+        <v>9985.7377</v>
       </c>
       <c r="H5" t="n">
-        <v>99.96729999999999</v>
+        <v>99.9995</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0063</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1429</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1429</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>98.7128</v>
+        <v>99.9952</v>
       </c>
     </row>
     <row r="6">
@@ -719,22 +719,22 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.015812</v>
+        <v>8e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>0.013896</v>
+        <v>0.002222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.012063</v>
+        <v>0.01</v>
       </c>
       <c r="G6" t="n">
-        <v>9969.345600000001</v>
+        <v>9985.355600000001</v>
       </c>
       <c r="H6" t="n">
-        <v>99.9045</v>
+        <v>99.99930000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0119</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1072</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -752,10 +752,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1072</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>98.2277</v>
+        <v>99.99509999999999</v>
       </c>
     </row>
     <row r="7">
@@ -771,43 +771,43 @@
         <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.012286</v>
+        <v>-4e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.010384</v>
+        <v>0.002223</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00831</v>
+        <v>0.01</v>
       </c>
       <c r="G7" t="n">
-        <v>9965.463100000001</v>
+        <v>9985.7089</v>
       </c>
       <c r="H7" t="n">
-        <v>99.8207</v>
+        <v>99.9991</v>
       </c>
       <c r="I7" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>6.5871</v>
+        <v>7.1464</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.4568</v>
+        <v>-2.6187</v>
       </c>
       <c r="L7" t="n">
-        <v>3.4762</v>
+        <v>3.4546</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1664</v>
+        <v>1.1454</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8.7729</v>
+        <v>9.127700000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>102.7345</v>
+        <v>104.5082</v>
       </c>
     </row>
     <row r="8">
@@ -823,43 +823,43 @@
         <v>0.675924</v>
       </c>
       <c r="D8" t="n">
-        <v>0.114701</v>
+        <v>0.112832</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.021617</v>
       </c>
       <c r="F8" t="n">
-        <v>0.127715</v>
+        <v>0.097277</v>
       </c>
       <c r="G8" t="n">
-        <v>9963.724899999999</v>
+        <v>9986.0263</v>
       </c>
       <c r="H8" t="n">
-        <v>99.96639999999999</v>
+        <v>100.2246</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0277</v>
+        <v>-0.0427</v>
       </c>
       <c r="J8" t="n">
-        <v>5.999</v>
+        <v>6.1425</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.6814</v>
+        <v>-3.547</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9215</v>
+        <v>2.9184</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0444</v>
+        <v>1.0336</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5592</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6.8428</v>
+        <v>6.5475</v>
       </c>
       <c r="P8" t="n">
-        <v>107.1121</v>
+        <v>108.8564</v>
       </c>
     </row>
     <row r="9">
@@ -875,43 +875,43 @@
         <v>0.652676</v>
       </c>
       <c r="D9" t="n">
-        <v>0.106529</v>
+        <v>0.104017</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007402</v>
+        <v>0.02752</v>
       </c>
       <c r="F9" t="n">
-        <v>0.178853</v>
+        <v>0.123842</v>
       </c>
       <c r="G9" t="n">
-        <v>9967.3524</v>
+        <v>9976.615100000001</v>
       </c>
       <c r="H9" t="n">
-        <v>100.3237</v>
+        <v>100.6562</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0677</v>
+        <v>-0.0815</v>
       </c>
       <c r="J9" t="n">
-        <v>4.8733</v>
+        <v>5.2371</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.7478</v>
+        <v>-3.6063</v>
       </c>
       <c r="L9" t="n">
-        <v>2.578</v>
+        <v>2.6846</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8204</v>
+        <v>0.8687</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7403</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5.2642</v>
+        <v>5.184</v>
       </c>
       <c r="P9" t="n">
-        <v>111.3273</v>
+        <v>113.0622</v>
       </c>
     </row>
     <row r="10">
@@ -927,43 +927,43 @@
         <v>0.630227</v>
       </c>
       <c r="D10" t="n">
-        <v>0.098381</v>
+        <v>0.09658899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.017482</v>
+        <v>0.028032</v>
       </c>
       <c r="F10" t="n">
-        <v>0.192587</v>
+        <v>0.126145</v>
       </c>
       <c r="G10" t="n">
-        <v>9966.916300000001</v>
+        <v>9965.193499999999</v>
       </c>
       <c r="H10" t="n">
-        <v>100.8739</v>
+        <v>101.2765</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1036</v>
+        <v>-0.1164</v>
       </c>
       <c r="J10" t="n">
-        <v>4.09</v>
+        <v>4.7349</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.7778</v>
+        <v>-3.6821</v>
       </c>
       <c r="L10" t="n">
-        <v>2.3881</v>
+        <v>2.5734</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6796</v>
+        <v>0.7696</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9109</v>
+        <v>-1.1339</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2908</v>
+        <v>3.2618</v>
       </c>
       <c r="P10" t="n">
-        <v>115.3966</v>
+        <v>116.9049</v>
       </c>
     </row>
     <row r="11">
@@ -979,43 +979,43 @@
         <v>0.608551</v>
       </c>
       <c r="D11" t="n">
-        <v>0.091381</v>
+        <v>0.08497</v>
       </c>
       <c r="E11" t="n">
-        <v>0.020543</v>
+        <v>0.024068</v>
       </c>
       <c r="F11" t="n">
-        <v>0.189971</v>
+        <v>0.108305</v>
       </c>
       <c r="G11" t="n">
-        <v>9961.484</v>
+        <v>9954.657999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>101.6</v>
+        <v>102.0579</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1358</v>
+        <v>-0.1455</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6389</v>
+        <v>4.5451</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.8314</v>
+        <v>-3.7155</v>
       </c>
       <c r="L11" t="n">
-        <v>2.2954</v>
+        <v>2.5631</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5908</v>
+        <v>0.7197</v>
       </c>
       <c r="N11" t="n">
-        <v>1.0826</v>
+        <v>-1.5359</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7763</v>
+        <v>2.5766</v>
       </c>
       <c r="P11" t="n">
-        <v>119.3649</v>
+        <v>120.5244</v>
       </c>
     </row>
     <row r="12">
@@ -1031,43 +1031,43 @@
         <v>0.58762</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08597100000000001</v>
+        <v>0.077403</v>
       </c>
       <c r="E12" t="n">
-        <v>0.020667</v>
+        <v>0.020166</v>
       </c>
       <c r="F12" t="n">
-        <v>0.182173</v>
+        <v>0.090748</v>
       </c>
       <c r="G12" t="n">
-        <v>9955.0638</v>
+        <v>9947.158299999999</v>
       </c>
       <c r="H12" t="n">
-        <v>102.4882</v>
+        <v>102.9812</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1647</v>
+        <v>-0.1704</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3303</v>
+        <v>4.409</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.8941</v>
+        <v>-3.7553</v>
       </c>
       <c r="L12" t="n">
-        <v>2.2355</v>
+        <v>2.5534</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5252</v>
+        <v>0.6825</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2448</v>
+        <v>-1.8745</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4417</v>
+        <v>2.0151</v>
       </c>
       <c r="P12" t="n">
-        <v>123.2595</v>
+        <v>123.8848</v>
       </c>
     </row>
     <row r="13">
@@ -1083,43 +1083,43 @@
         <v>0.5674090000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08157</v>
+        <v>0.069704</v>
       </c>
       <c r="E13" t="n">
-        <v>0.019708</v>
+        <v>0.016578</v>
       </c>
       <c r="F13" t="n">
-        <v>0.173102</v>
+        <v>0.074601</v>
       </c>
       <c r="G13" t="n">
-        <v>9949.224099999999</v>
+        <v>9942.3593</v>
       </c>
       <c r="H13" t="n">
-        <v>103.5268</v>
+        <v>104.0264</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1906</v>
+        <v>-0.1909</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0835</v>
+        <v>4.2809</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.954</v>
+        <v>-3.7682</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1313</v>
+        <v>2.4902</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4704</v>
+        <v>0.6484</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3935</v>
+        <v>-2.1561</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1248</v>
+        <v>1.4952</v>
       </c>
       <c r="P13" t="n">
-        <v>127.0664</v>
+        <v>126.9012</v>
       </c>
     </row>
     <row r="14">
@@ -1135,43 +1135,43 @@
         <v>0.547893</v>
       </c>
       <c r="D14" t="n">
-        <v>0.077213</v>
+        <v>0.06087</v>
       </c>
       <c r="E14" t="n">
-        <v>0.018509</v>
+        <v>0.013269</v>
       </c>
       <c r="F14" t="n">
-        <v>0.163479</v>
+        <v>0.059712</v>
       </c>
       <c r="G14" t="n">
-        <v>9944.447899999999</v>
+        <v>9939.8344</v>
       </c>
       <c r="H14" t="n">
-        <v>104.7038</v>
+        <v>105.1701</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2136</v>
+        <v>-0.2066</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8686</v>
+        <v>4.1583</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.9991</v>
+        <v>-3.7435</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0387</v>
+        <v>2.429</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4222</v>
+        <v>0.6166</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5255</v>
+        <v>-2.3756</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8558</v>
+        <v>1.0847</v>
       </c>
       <c r="P14" t="n">
-        <v>130.7914</v>
+        <v>129.5168</v>
       </c>
     </row>
     <row r="15">
@@ -1187,43 +1187,43 @@
         <v>0.529049</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07328800000000001</v>
+        <v>0.051529</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01713</v>
+        <v>0.010372</v>
       </c>
       <c r="F15" t="n">
-        <v>0.15404</v>
+        <v>0.046675</v>
       </c>
       <c r="G15" t="n">
-        <v>9940.748799999999</v>
+        <v>9939.2163</v>
       </c>
       <c r="H15" t="n">
-        <v>106.0082</v>
+        <v>106.3875</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2338</v>
+        <v>-0.2174</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6783</v>
+        <v>4.037</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.0333</v>
+        <v>-3.6846</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9543</v>
+        <v>2.3663</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3793</v>
+        <v>0.5868</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6417</v>
+        <v>-2.531</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6204</v>
+        <v>0.7746</v>
       </c>
       <c r="P15" t="n">
-        <v>134.4357</v>
+        <v>131.7109</v>
       </c>
     </row>
     <row r="16">
@@ -1239,43 +1239,43 @@
         <v>0.510852</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06966</v>
+        <v>0.042351</v>
       </c>
       <c r="E16" t="n">
-        <v>0.015763</v>
+        <v>0.007945000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.145081</v>
+        <v>0.035751</v>
       </c>
       <c r="G16" t="n">
-        <v>9938.1091</v>
+        <v>9940.1086</v>
       </c>
       <c r="H16" t="n">
-        <v>107.4295</v>
+        <v>107.6536</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2514</v>
+        <v>-0.2235</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5043</v>
+        <v>3.9165</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.0553</v>
+        <v>-3.5973</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8754</v>
+        <v>2.3022</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3403</v>
+        <v>0.5594</v>
       </c>
       <c r="N16" t="n">
-        <v>1.7426</v>
+        <v>-2.6249</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4072</v>
+        <v>0.5557</v>
       </c>
       <c r="P16" t="n">
-        <v>137.9914</v>
+        <v>133.5077</v>
       </c>
     </row>
     <row r="17">
@@ -1291,43 +1291,43 @@
         <v>0.493282</v>
       </c>
       <c r="D17" t="n">
-        <v>0.066123</v>
+        <v>0.034104</v>
       </c>
       <c r="E17" t="n">
-        <v>0.014555</v>
+        <v>0.006002</v>
       </c>
       <c r="F17" t="n">
-        <v>0.136663</v>
+        <v>0.027008</v>
       </c>
       <c r="G17" t="n">
-        <v>9936.416499999999</v>
+        <v>9942.1255</v>
       </c>
       <c r="H17" t="n">
-        <v>108.9576</v>
+        <v>108.9463</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2665</v>
+        <v>-0.2254</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3409</v>
+        <v>3.7973</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.0635</v>
+        <v>-3.4915</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8003</v>
+        <v>2.2344</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3043</v>
+        <v>0.5345</v>
       </c>
       <c r="N17" t="n">
-        <v>1.828</v>
+        <v>-2.6648</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2101</v>
+        <v>0.4099</v>
       </c>
       <c r="P17" t="n">
-        <v>141.4561</v>
+        <v>134.968</v>
       </c>
     </row>
     <row r="18">
@@ -1343,43 +1343,43 @@
         <v>0.476315</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06277000000000001</v>
+        <v>0.027346</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01344</v>
+        <v>0.004512</v>
       </c>
       <c r="F18" t="n">
-        <v>0.128763</v>
+        <v>0.020304</v>
       </c>
       <c r="G18" t="n">
-        <v>9935.4974</v>
+        <v>9944.9121</v>
       </c>
       <c r="H18" t="n">
-        <v>110.5826</v>
+        <v>110.2474</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2792</v>
+        <v>-0.2242</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1893</v>
+        <v>3.6808</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.0597</v>
+        <v>-3.3768</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7287</v>
+        <v>2.1633</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2716</v>
+        <v>0.5122</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8992</v>
+        <v>-2.6618</v>
       </c>
       <c r="O18" t="n">
-        <v>2.0292</v>
+        <v>0.3178</v>
       </c>
       <c r="P18" t="n">
-        <v>144.8274</v>
+        <v>136.1796</v>
       </c>
     </row>
     <row r="19">
@@ -1395,43 +1395,43 @@
         <v>0.459933</v>
       </c>
       <c r="D19" t="n">
-        <v>0.059582</v>
+        <v>0.022443</v>
       </c>
       <c r="E19" t="n">
-        <v>0.012424</v>
+        <v>0.003413</v>
       </c>
       <c r="F19" t="n">
-        <v>0.121365</v>
+        <v>0.01536</v>
       </c>
       <c r="G19" t="n">
-        <v>9935.2276</v>
+        <v>9948.1649</v>
       </c>
       <c r="H19" t="n">
-        <v>112.2948</v>
+        <v>111.544</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2897</v>
+        <v>-0.2209</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0485</v>
+        <v>3.5679</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.0447</v>
+        <v>-3.2628</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6604</v>
+        <v>2.0906</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2417</v>
+        <v>0.4926</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9571</v>
+        <v>-2.6289</v>
       </c>
       <c r="O19" t="n">
-        <v>1.8631</v>
+        <v>0.2595</v>
       </c>
       <c r="P19" t="n">
-        <v>148.1033</v>
+        <v>137.2145</v>
       </c>
     </row>
     <row r="20">
@@ -1447,43 +1447,43 @@
         <v>0.444114</v>
       </c>
       <c r="D20" t="n">
-        <v>0.056548</v>
+        <v>0.018998</v>
       </c>
       <c r="E20" t="n">
-        <v>0.011505</v>
+        <v>0.002625</v>
       </c>
       <c r="F20" t="n">
-        <v>0.114446</v>
+        <v>0.011811</v>
       </c>
       <c r="G20" t="n">
-        <v>9935.4928</v>
+        <v>9951.6417</v>
       </c>
       <c r="H20" t="n">
-        <v>114.0852</v>
+        <v>112.8276</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2982</v>
+        <v>-0.2161</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9177</v>
+        <v>3.4571</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.0194</v>
+        <v>-3.1519</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5951</v>
+        <v>2.0181</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2145</v>
+        <v>0.4747</v>
       </c>
       <c r="N20" t="n">
-        <v>2.0027</v>
+        <v>-2.5771</v>
       </c>
       <c r="O20" t="n">
-        <v>1.7107</v>
+        <v>0.221</v>
       </c>
       <c r="P20" t="n">
-        <v>151.2803</v>
+        <v>138.1233</v>
       </c>
     </row>
     <row r="21">
@@ -1499,43 +1499,43 @@
         <v>0.428838</v>
       </c>
       <c r="D21" t="n">
-        <v>0.053629</v>
+        <v>0.016559</v>
       </c>
       <c r="E21" t="n">
-        <v>0.010694</v>
+        <v>0.002222</v>
       </c>
       <c r="F21" t="n">
-        <v>0.10798</v>
+        <v>0.01</v>
       </c>
       <c r="G21" t="n">
-        <v>9936.191199999999</v>
+        <v>9955.165199999999</v>
       </c>
       <c r="H21" t="n">
-        <v>115.945</v>
+        <v>114.0923</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3048</v>
+        <v>-0.2106</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7957</v>
+        <v>3.3369</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.9843</v>
+        <v>-3.0436</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5326</v>
+        <v>1.9438</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.4563</v>
       </c>
       <c r="N21" t="n">
-        <v>2.0367</v>
+        <v>-2.5151</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3807</v>
+        <v>0.1783</v>
       </c>
       <c r="P21" t="n">
-        <v>154.1991</v>
+        <v>138.8817</v>
       </c>
     </row>
     <row r="22">
@@ -1551,43 +1551,43 @@
         <v>0.414089</v>
       </c>
       <c r="D22" t="n">
-        <v>0.048234</v>
+        <v>0.013726</v>
       </c>
       <c r="E22" t="n">
-        <v>0.010752</v>
+        <v>0.002222</v>
       </c>
       <c r="F22" t="n">
-        <v>0.100037</v>
+        <v>0.01</v>
       </c>
       <c r="G22" t="n">
-        <v>9937.225200000001</v>
+        <v>9958.5376</v>
       </c>
       <c r="H22" t="n">
-        <v>117.8577</v>
+        <v>115.3318</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3083</v>
+        <v>-0.2042</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6748</v>
+        <v>3.197</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.9083</v>
+        <v>-2.9266</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4773</v>
+        <v>1.8667</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="N22" t="n">
-        <v>2.0494</v>
+        <v>-2.4434</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2932</v>
+        <v>0.1287</v>
       </c>
       <c r="P22" t="n">
-        <v>157.0368</v>
+        <v>139.4523</v>
       </c>
     </row>
     <row r="23">
@@ -1603,43 +1603,43 @@
         <v>0.399846</v>
       </c>
       <c r="D23" t="n">
-        <v>0.046007</v>
+        <v>0.010272</v>
       </c>
       <c r="E23" t="n">
-        <v>0.009572000000000001</v>
+        <v>0.002222</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09365800000000001</v>
+        <v>0.01</v>
       </c>
       <c r="G23" t="n">
-        <v>9938.126700000001</v>
+        <v>9961.572700000001</v>
       </c>
       <c r="H23" t="n">
-        <v>119.8166</v>
+        <v>116.5378</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3106</v>
+        <v>-0.1966</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3.064</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.8569</v>
+        <v>-2.7998</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4251</v>
+        <v>1.7948</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="N23" t="n">
-        <v>2.0595</v>
+        <v>-2.357</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3723</v>
+        <v>0.117</v>
       </c>
       <c r="P23" t="n">
-        <v>155.6718</v>
+        <v>139.9773</v>
       </c>
     </row>
     <row r="24">
@@ -1655,43 +1655,43 @@
         <v>0.386094</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.02173</v>
+        <v>0.009412999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.043692</v>
+        <v>0.002222</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07990999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="G24" t="n">
-        <v>9939.527899999999</v>
+        <v>9964.3043</v>
       </c>
       <c r="H24" t="n">
-        <v>121.6094</v>
+        <v>117.7098</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2801</v>
+        <v>-0.1892</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.9535</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.9065</v>
+        <v>-2.695</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2626</v>
+        <v>1.7272</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>0.3999</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7378</v>
+        <v>-2.2679</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0939</v>
+        <v>0.1178</v>
       </c>
       <c r="P24" t="n">
-        <v>156.106</v>
+        <v>140.5067</v>
       </c>
     </row>
     <row r="25">
@@ -1707,43 +1707,43 @@
         <v>0.372814</v>
       </c>
       <c r="D25" t="n">
-        <v>0.006974</v>
+        <v>0.009455</v>
       </c>
       <c r="E25" t="n">
-        <v>0.022419</v>
+        <v>0.002222</v>
       </c>
       <c r="F25" t="n">
-        <v>0.068189</v>
+        <v>0.01</v>
       </c>
       <c r="G25" t="n">
-        <v>9923.7294</v>
+        <v>9966.7628</v>
       </c>
       <c r="H25" t="n">
-        <v>123.3342</v>
+        <v>118.8497</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2657</v>
+        <v>-0.1822</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.8516</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.0942</v>
+        <v>-2.6018</v>
       </c>
       <c r="L25" t="n">
-        <v>1.32</v>
+        <v>1.6631</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.3865</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7218</v>
+        <v>-2.1838</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0524</v>
+        <v>0.1156</v>
       </c>
       <c r="P25" t="n">
-        <v>155.8553</v>
+        <v>141.0261</v>
       </c>
     </row>
     <row r="26">
@@ -1759,43 +1759,43 @@
         <v>0.359991</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.004016</v>
+        <v>0.009242</v>
       </c>
       <c r="E26" t="n">
-        <v>0.025671</v>
+        <v>0.002222</v>
       </c>
       <c r="F26" t="n">
-        <v>0.060078</v>
+        <v>0.01</v>
       </c>
       <c r="G26" t="n">
-        <v>9920.147000000001</v>
+        <v>9968.975399999999</v>
       </c>
       <c r="H26" t="n">
-        <v>124.9603</v>
+        <v>119.9585</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2472</v>
+        <v>-0.1756</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.7509</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.8237</v>
+        <v>-2.5107</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2657</v>
+        <v>1.6021</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5901</v>
+        <v>-2.1045</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0322</v>
+        <v>0.1106</v>
       </c>
       <c r="P26" t="n">
-        <v>156.0116</v>
+        <v>141.5251</v>
       </c>
     </row>
     <row r="27">
@@ -1811,43 +1811,43 @@
         <v>0.34761</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002508</v>
+        <v>0.008845</v>
       </c>
       <c r="E27" t="n">
-        <v>0.019653</v>
+        <v>0.002222</v>
       </c>
       <c r="F27" t="n">
-        <v>0.054368</v>
+        <v>0.01</v>
       </c>
       <c r="G27" t="n">
-        <v>9915.297</v>
+        <v>9970.966700000001</v>
       </c>
       <c r="H27" t="n">
-        <v>126.5128</v>
+        <v>121.0368</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2332</v>
+        <v>-0.1693</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.6521</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.7665</v>
+        <v>-2.4215</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2429</v>
+        <v>1.5441</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.3596</v>
       </c>
       <c r="N27" t="n">
-        <v>1.5204</v>
+        <v>-2.0286</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.0032</v>
+        <v>0.1059</v>
       </c>
       <c r="P27" t="n">
-        <v>155.9932</v>
+        <v>142.0052</v>
       </c>
     </row>
     <row r="28">
@@ -1863,43 +1863,43 @@
         <v>0.335654</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.000295</v>
+        <v>0.008482</v>
       </c>
       <c r="E28" t="n">
-        <v>0.019602</v>
+        <v>0.002222</v>
       </c>
       <c r="F28" t="n">
-        <v>0.050034</v>
+        <v>0.01</v>
       </c>
       <c r="G28" t="n">
-        <v>9913.9408</v>
+        <v>9972.759</v>
       </c>
       <c r="H28" t="n">
-        <v>127.9869</v>
+        <v>122.0852</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2188</v>
+        <v>-0.1632</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2.5568</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.6063</v>
+        <v>-2.3356</v>
       </c>
       <c r="L28" t="n">
-        <v>1.1922</v>
+        <v>1.4895</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.3467</v>
       </c>
       <c r="N28" t="n">
-        <v>1.4271</v>
+        <v>-1.9555</v>
       </c>
       <c r="O28" t="n">
-        <v>0.013</v>
+        <v>0.102</v>
       </c>
       <c r="P28" t="n">
-        <v>156.0567</v>
+        <v>142.4704</v>
       </c>
     </row>
     <row r="29">
@@ -1915,43 +1915,43 @@
         <v>0.324109</v>
       </c>
       <c r="D29" t="n">
-        <v>0.001018</v>
+        <v>0.008189</v>
       </c>
       <c r="E29" t="n">
-        <v>0.017633</v>
+        <v>0.002222</v>
       </c>
       <c r="F29" t="n">
-        <v>0.046933</v>
+        <v>0.01</v>
       </c>
       <c r="G29" t="n">
-        <v>9912.7454</v>
+        <v>9974.3719</v>
       </c>
       <c r="H29" t="n">
-        <v>129.3904</v>
+        <v>123.1045</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2061</v>
+        <v>-0.1573</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.465</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.4999</v>
+        <v>-2.2533</v>
       </c>
       <c r="L29" t="n">
-        <v>1.1783</v>
+        <v>1.437</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.3342</v>
       </c>
       <c r="N29" t="n">
-        <v>1.3512</v>
+        <v>-1.8855</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0295</v>
+        <v>0.0974</v>
       </c>
       <c r="P29" t="n">
-        <v>156.2</v>
+        <v>142.9167</v>
       </c>
     </row>
     <row r="30">
@@ -1967,43 +1967,43 @@
         <v>0.312962</v>
       </c>
       <c r="D30" t="n">
-        <v>0.002295</v>
+        <v>0.007832</v>
       </c>
       <c r="E30" t="n">
-        <v>0.016007</v>
+        <v>0.002222</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04466</v>
+        <v>0.01</v>
       </c>
       <c r="G30" t="n">
-        <v>9912.6543</v>
+        <v>9975.8236</v>
       </c>
       <c r="H30" t="n">
-        <v>130.7308</v>
+        <v>124.0951</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1948</v>
+        <v>-0.1517</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2.3757</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.4024</v>
+        <v>-2.1734</v>
       </c>
       <c r="L30" t="n">
-        <v>1.1466</v>
+        <v>1.3861</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.3221</v>
       </c>
       <c r="N30" t="n">
-        <v>1.2831</v>
+        <v>-1.8181</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0274</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>156.3324</v>
+        <v>143.3395</v>
       </c>
     </row>
     <row r="31">
@@ -2019,43 +2019,43 @@
         <v>0.302197</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002119</v>
+        <v>0.007395</v>
       </c>
       <c r="E31" t="n">
-        <v>0.015355</v>
+        <v>0.002222</v>
       </c>
       <c r="F31" t="n">
-        <v>0.042718</v>
+        <v>0.01</v>
       </c>
       <c r="G31" t="n">
-        <v>9913.3856</v>
+        <v>9977.1302</v>
       </c>
       <c r="H31" t="n">
-        <v>132.0109</v>
+        <v>125.0573</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1842</v>
+        <v>-0.1462</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2.289</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.2945</v>
+        <v>-2.0954</v>
       </c>
       <c r="L31" t="n">
-        <v>1.1162</v>
+        <v>1.3368</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="N31" t="n">
-        <v>1.2158</v>
+        <v>-1.7527</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0376</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>156.5138</v>
+        <v>143.745</v>
       </c>
     </row>
     <row r="32">
@@ -2064,50 +2064,50 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.508197</v>
+        <v>0.291803</v>
       </c>
       <c r="D32" t="n">
-        <v>0.002901</v>
+        <v>0.007073</v>
       </c>
       <c r="E32" t="n">
-        <v>0.507673</v>
+        <v>0.002222</v>
       </c>
       <c r="F32" t="n">
-        <v>0.041116</v>
+        <v>0.01</v>
       </c>
       <c r="G32" t="n">
-        <v>9914.3694</v>
+        <v>9978.306</v>
       </c>
       <c r="H32" t="n">
-        <v>133.2361</v>
+        <v>125.9917</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1747</v>
+        <v>-0.1409</v>
       </c>
       <c r="J32" t="n">
-        <v>-16.2055</v>
+        <v>2.2059</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4362</v>
+        <v>-2.0208</v>
       </c>
       <c r="L32" t="n">
-        <v>-4.9879</v>
+        <v>1.2892</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.8287</v>
+        <v>0.299</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>-1.6896</v>
       </c>
       <c r="O32" t="n">
-        <v>-19.586</v>
+        <v>0.0837</v>
       </c>
       <c r="P32" t="n">
-        <v>151.595</v>
+        <v>144.1338</v>
       </c>
     </row>
     <row r="33">
@@ -2116,50 +2116,50 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.490717</v>
+        <v>0.281767</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.078567</v>
+        <v>0.006761</v>
       </c>
       <c r="E33" t="n">
-        <v>0.607835</v>
+        <v>0.002222</v>
       </c>
       <c r="F33" t="n">
-        <v>0.22053</v>
+        <v>0.01</v>
       </c>
       <c r="G33" t="n">
-        <v>9669.096100000001</v>
+        <v>9979.364299999999</v>
       </c>
       <c r="H33" t="n">
-        <v>134.154</v>
+        <v>126.8988</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.13</v>
+        <v>-0.1358</v>
       </c>
       <c r="J33" t="n">
-        <v>-20.0772</v>
+        <v>2.1257</v>
       </c>
       <c r="K33" t="n">
-        <v>4.804</v>
+        <v>-1.9489</v>
       </c>
       <c r="L33" t="n">
-        <v>-6.0287</v>
+        <v>1.2433</v>
       </c>
       <c r="M33" t="n">
-        <v>-2.3933</v>
+        <v>0.2881</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-1.6288</v>
       </c>
       <c r="O33" t="n">
-        <v>-24.5716</v>
+        <v>0.0794</v>
       </c>
       <c r="P33" t="n">
-        <v>146.4787</v>
+        <v>144.5016</v>
       </c>
     </row>
     <row r="34">
@@ -2168,50 +2168,50 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.473839</v>
+        <v>0.272076</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.08437500000000001</v>
+        <v>0.006381</v>
       </c>
       <c r="E34" t="n">
-        <v>0.655998</v>
+        <v>0.002222</v>
       </c>
       <c r="F34" t="n">
-        <v>0.378034</v>
+        <v>0.01</v>
       </c>
       <c r="G34" t="n">
-        <v>9398.269200000001</v>
+        <v>9980.316800000001</v>
       </c>
       <c r="H34" t="n">
-        <v>134.7702</v>
+        <v>127.7789</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.1309</v>
       </c>
       <c r="J34" t="n">
-        <v>-22.2306</v>
+        <v>2.0478</v>
       </c>
       <c r="K34" t="n">
-        <v>5.3102</v>
+        <v>-1.8787</v>
       </c>
       <c r="L34" t="n">
-        <v>-6.7762</v>
+        <v>1.1988</v>
       </c>
       <c r="M34" t="n">
-        <v>-2.7178</v>
+        <v>0.2775</v>
       </c>
       <c r="N34" t="n">
-        <v>-1.311</v>
+        <v>-1.5698</v>
       </c>
       <c r="O34" t="n">
-        <v>-27.7253</v>
+        <v>0.0757</v>
       </c>
       <c r="P34" t="n">
-        <v>141.1972</v>
+        <v>144.8543</v>
       </c>
     </row>
     <row r="35">
@@ -2220,50 +2220,50 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.457542</v>
+        <v>0.262718</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.07153</v>
+        <v>0.006101</v>
       </c>
       <c r="E35" t="n">
-        <v>0.68164</v>
+        <v>0.002222</v>
       </c>
       <c r="F35" t="n">
-        <v>0.504074</v>
+        <v>0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>9130.4431</v>
+        <v>9981.174000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>135.0916</v>
+        <v>128.6327</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0452</v>
+        <v>-0.1261</v>
       </c>
       <c r="J35" t="n">
-        <v>-23.5232</v>
+        <v>1.9731</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5488</v>
+        <v>-1.8116</v>
       </c>
       <c r="L35" t="n">
-        <v>-7.3118</v>
+        <v>1.1559</v>
       </c>
       <c r="M35" t="n">
-        <v>-2.917</v>
+        <v>0.2673</v>
       </c>
       <c r="N35" t="n">
-        <v>-1.657</v>
+        <v>-1.5128</v>
       </c>
       <c r="O35" t="n">
-        <v>-29.8602</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P35" t="n">
-        <v>135.7521</v>
+        <v>145.1925</v>
       </c>
     </row>
     <row r="36">
@@ -2272,50 +2272,50 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.441805</v>
+        <v>0.253682</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.064161</v>
+        <v>0.005837</v>
       </c>
       <c r="E36" t="n">
-        <v>0.699728</v>
+        <v>0.002222</v>
       </c>
       <c r="F36" t="n">
-        <v>0.601046</v>
+        <v>0.01</v>
       </c>
       <c r="G36" t="n">
-        <v>8876.5787</v>
+        <v>9981.9455</v>
       </c>
       <c r="H36" t="n">
-        <v>135.1246</v>
+        <v>129.4607</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0046</v>
+        <v>-0.1215</v>
       </c>
       <c r="J36" t="n">
-        <v>-24.4289</v>
+        <v>1.901</v>
       </c>
       <c r="K36" t="n">
-        <v>5.7857</v>
+        <v>-1.7469</v>
       </c>
       <c r="L36" t="n">
-        <v>-7.706</v>
+        <v>1.1146</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.056</v>
+        <v>0.2575</v>
       </c>
       <c r="N36" t="n">
-        <v>-1.9722</v>
+        <v>-1.4579</v>
       </c>
       <c r="O36" t="n">
-        <v>-31.3774</v>
+        <v>0.0683</v>
       </c>
       <c r="P36" t="n">
-        <v>130.1375</v>
+        <v>145.5113</v>
       </c>
     </row>
     <row r="37">
@@ -2324,50 +2324,50 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.426609</v>
+        <v>0.244956</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.061327</v>
+        <v>0.00549</v>
       </c>
       <c r="E37" t="n">
-        <v>0.711811</v>
+        <v>0.002222</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6744019999999999</v>
+        <v>0.01</v>
       </c>
       <c r="G37" t="n">
-        <v>8639.0568</v>
+        <v>9982.639800000001</v>
       </c>
       <c r="H37" t="n">
-        <v>134.8753</v>
+        <v>130.2632</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0351</v>
+        <v>-0.1171</v>
       </c>
       <c r="J37" t="n">
-        <v>-25.0236</v>
+        <v>1.8309</v>
       </c>
       <c r="K37" t="n">
-        <v>6.0238</v>
+        <v>-1.6835</v>
       </c>
       <c r="L37" t="n">
-        <v>-7.9887</v>
+        <v>1.0746</v>
       </c>
       <c r="M37" t="n">
-        <v>-3.1466</v>
+        <v>0.248</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.2634</v>
+        <v>-1.4047</v>
       </c>
       <c r="O37" t="n">
-        <v>-32.3986</v>
+        <v>0.0653</v>
       </c>
       <c r="P37" t="n">
-        <v>124.3821</v>
+        <v>145.8189</v>
       </c>
     </row>
     <row r="38">
@@ -2376,50 +2376,50 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.411936</v>
+        <v>0.236531</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.060697</v>
+        <v>0.005285</v>
       </c>
       <c r="E38" t="n">
-        <v>0.718257</v>
+        <v>0.002222</v>
       </c>
       <c r="F38" t="n">
-        <v>0.728627</v>
+        <v>0.01</v>
       </c>
       <c r="G38" t="n">
-        <v>8419.2454</v>
+        <v>9983.2647</v>
       </c>
       <c r="H38" t="n">
-        <v>134.3506</v>
+        <v>131.041</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0742</v>
+        <v>-0.1128</v>
       </c>
       <c r="J38" t="n">
-        <v>-25.3427</v>
+        <v>1.764</v>
       </c>
       <c r="K38" t="n">
-        <v>6.2473</v>
+        <v>-1.6235</v>
       </c>
       <c r="L38" t="n">
-        <v>-8.1366</v>
+        <v>1.036</v>
       </c>
       <c r="M38" t="n">
-        <v>-3.1945</v>
+        <v>0.2389</v>
       </c>
       <c r="N38" t="n">
-        <v>-2.5319</v>
+        <v>-1.3534</v>
       </c>
       <c r="O38" t="n">
-        <v>-32.9584</v>
+        <v>0.062</v>
       </c>
       <c r="P38" t="n">
-        <v>118.4838</v>
+        <v>146.1107</v>
       </c>
     </row>
     <row r="39">
@@ -2428,50 +2428,50 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.397768</v>
+        <v>0.228396</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.061846</v>
+        <v>0.005003</v>
       </c>
       <c r="E39" t="n">
-        <v>0.71998</v>
+        <v>0.002222</v>
       </c>
       <c r="F39" t="n">
-        <v>0.76676</v>
+        <v>0.01</v>
       </c>
       <c r="G39" t="n">
-        <v>8218.1921</v>
+        <v>9983.8271</v>
       </c>
       <c r="H39" t="n">
-        <v>133.5573</v>
+        <v>131.7945</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1129</v>
+        <v>-0.1086</v>
       </c>
       <c r="J39" t="n">
-        <v>-25.4295</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>6.4596</v>
+        <v>-1.5649</v>
       </c>
       <c r="L39" t="n">
-        <v>-8.203799999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.2064</v>
+        <v>0.2301</v>
       </c>
       <c r="N39" t="n">
-        <v>-2.7824</v>
+        <v>-1.3039</v>
       </c>
       <c r="O39" t="n">
-        <v>-33.1625</v>
+        <v>-1.6399</v>
       </c>
       <c r="P39" t="n">
-        <v>112.4351</v>
+        <v>142.9982</v>
       </c>
     </row>
     <row r="40">
@@ -2480,50 +2480,50 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.384087</v>
+        <v>0.22054</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.064484</v>
+        <v>-0.053256</v>
       </c>
       <c r="E40" t="n">
-        <v>0.717912</v>
+        <v>0.02273</v>
       </c>
       <c r="F40" t="n">
-        <v>0.791681</v>
+        <v>0.022399</v>
       </c>
       <c r="G40" t="n">
-        <v>8036.3831</v>
+        <v>9984.3333</v>
       </c>
       <c r="H40" t="n">
-        <v>132.5011</v>
+        <v>132.3547</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1514</v>
+        <v>-0.0804</v>
       </c>
       <c r="J40" t="n">
-        <v>-25.3272</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>6.6652</v>
+        <v>-0.8182</v>
       </c>
       <c r="L40" t="n">
-        <v>-8.206</v>
+        <v>0.8273</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.1886</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>-3.0198</v>
+        <v>-1.0868</v>
       </c>
       <c r="O40" t="n">
-        <v>-33.0764</v>
+        <v>-1.0777</v>
       </c>
       <c r="P40" t="n">
-        <v>106.2639</v>
+        <v>140.3972</v>
       </c>
     </row>
     <row r="41">
@@ -2532,50 +2532,50 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.370876</v>
+        <v>0.212955</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.068117</v>
+        <v>-0.045472</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7126749999999999</v>
+        <v>0.020539</v>
       </c>
       <c r="F41" t="n">
-        <v>0.805773</v>
+        <v>0.024216</v>
       </c>
       <c r="G41" t="n">
-        <v>7873.7887</v>
+        <v>9974.5352</v>
       </c>
       <c r="H41" t="n">
-        <v>131.1893</v>
+        <v>132.7568</v>
       </c>
       <c r="I41" t="n">
-        <v>0.19</v>
+        <v>-0.0576</v>
       </c>
       <c r="J41" t="n">
-        <v>-25.0674</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>6.8638</v>
+        <v>-0.7159</v>
       </c>
       <c r="L41" t="n">
-        <v>-8.1553</v>
+        <v>0.7894</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.1462</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>-3.2464</v>
+        <v>-0.7664</v>
       </c>
       <c r="O41" t="n">
-        <v>-32.7515</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="P41" t="n">
-        <v>99.9787</v>
+        <v>138.3456</v>
       </c>
     </row>
     <row r="42">
@@ -2584,50 +2584,50 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.35812</v>
+        <v>0.20563</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.072933</v>
+        <v>-0.036532</v>
       </c>
       <c r="E42" t="n">
-        <v>0.705118</v>
+        <v>0.016946</v>
       </c>
       <c r="F42" t="n">
-        <v>0.810979</v>
+        <v>0.02146</v>
       </c>
       <c r="G42" t="n">
-        <v>7730.0722</v>
+        <v>9966.8123</v>
       </c>
       <c r="H42" t="n">
-        <v>129.6288</v>
+        <v>133.0363</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2287</v>
+        <v>-0.0399</v>
       </c>
       <c r="J42" t="n">
-        <v>-24.6861</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>7.0625</v>
+        <v>-0.6631</v>
       </c>
       <c r="L42" t="n">
-        <v>-8.062900000000001</v>
+        <v>0.7758</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.0843</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>-3.4665</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>-32.2373</v>
+        <v>0.1126</v>
       </c>
       <c r="P42" t="n">
-        <v>93.61020000000001</v>
+        <v>138.8552</v>
       </c>
     </row>
     <row r="43">
@@ -2636,50 +2636,50 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.345803</v>
+        <v>0.198558</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.07874100000000001</v>
+        <v>0.009209</v>
       </c>
       <c r="E43" t="n">
-        <v>0.695759</v>
+        <v>0.003112</v>
       </c>
       <c r="F43" t="n">
-        <v>0.80896</v>
+        <v>0.014002</v>
       </c>
       <c r="G43" t="n">
-        <v>7604.5058</v>
+        <v>9961.657999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>127.8278</v>
+        <v>133.3272</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2677</v>
+        <v>-0.0415</v>
       </c>
       <c r="J43" t="n">
-        <v>-24.2082</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>7.2627</v>
+        <v>-1.0593</v>
       </c>
       <c r="L43" t="n">
-        <v>-7.9378</v>
+        <v>0.8252</v>
       </c>
       <c r="M43" t="n">
-        <v>-3.0068</v>
+        <v>0.2619</v>
       </c>
       <c r="N43" t="n">
-        <v>-3.6817</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>-31.5719</v>
+        <v>0.0278</v>
       </c>
       <c r="P43" t="n">
-        <v>87.1353</v>
+        <v>138.992</v>
       </c>
     </row>
     <row r="44">
@@ -2688,50 +2688,50 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.333909</v>
+        <v>0.191729</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.086342</v>
+        <v>0.002463</v>
       </c>
       <c r="E44" t="n">
-        <v>0.685585</v>
+        <v>0.002222</v>
       </c>
       <c r="F44" t="n">
-        <v>0.801095</v>
+        <v>0.01</v>
       </c>
       <c r="G44" t="n">
-        <v>7496.1759</v>
+        <v>9963.936400000001</v>
       </c>
       <c r="H44" t="n">
-        <v>125.7932</v>
+        <v>133.6104</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3073</v>
+        <v>-0.0403</v>
       </c>
       <c r="J44" t="n">
-        <v>-23.6695</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>7.4786</v>
+        <v>-0.98</v>
       </c>
       <c r="L44" t="n">
-        <v>-7.7897</v>
+        <v>0.8099</v>
       </c>
       <c r="M44" t="n">
-        <v>-2.9187</v>
+        <v>0.2502</v>
       </c>
       <c r="N44" t="n">
-        <v>-3.8985</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>-30.7979</v>
+        <v>0.0801</v>
       </c>
       <c r="P44" t="n">
-        <v>80.58839999999999</v>
+        <v>139.3642</v>
       </c>
     </row>
     <row r="45">
@@ -2740,50 +2740,50 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.322424</v>
+        <v>0.185134</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.095272</v>
+        <v>0.006694</v>
       </c>
       <c r="E45" t="n">
-        <v>0.674798</v>
+        <v>0.002222</v>
       </c>
       <c r="F45" t="n">
-        <v>0.788636</v>
+        <v>0.01</v>
       </c>
       <c r="G45" t="n">
-        <v>7403.7659</v>
+        <v>9966.431699999999</v>
       </c>
       <c r="H45" t="n">
-        <v>123.533</v>
+        <v>133.8981</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3476</v>
+        <v>-0.0408</v>
       </c>
       <c r="J45" t="n">
-        <v>-23.083</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>7.7076</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>-7.6245</v>
+        <v>0.8056</v>
       </c>
       <c r="M45" t="n">
-        <v>-2.8221</v>
+        <v>0.2456</v>
       </c>
       <c r="N45" t="n">
-        <v>-4.1175</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>-29.9395</v>
+        <v>0.0608</v>
       </c>
       <c r="P45" t="n">
-        <v>73.99120000000001</v>
+        <v>139.6497</v>
       </c>
     </row>
     <row r="46">
@@ -2792,50 +2792,50 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.311335</v>
+        <v>0.178766</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.105962</v>
+        <v>0.005122</v>
       </c>
       <c r="E46" t="n">
-        <v>0.664022</v>
+        <v>0.002222</v>
       </c>
       <c r="F46" t="n">
-        <v>0.772576</v>
+        <v>0.01</v>
       </c>
       <c r="G46" t="n">
-        <v>7325.9903</v>
+        <v>9968.6774</v>
       </c>
       <c r="H46" t="n">
-        <v>121.0559</v>
+        <v>134.1857</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3888</v>
+        <v>-0.0407</v>
       </c>
       <c r="J46" t="n">
-        <v>-22.4726</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>7.9572</v>
+        <v>-0.954</v>
       </c>
       <c r="L46" t="n">
-        <v>-7.4493</v>
+        <v>0.7986</v>
       </c>
       <c r="M46" t="n">
-        <v>-2.7204</v>
+        <v>0.2324</v>
       </c>
       <c r="N46" t="n">
-        <v>-4.3417</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>-29.0267</v>
+        <v>0.077</v>
       </c>
       <c r="P46" t="n">
-        <v>67.32729999999999</v>
+        <v>140.0075</v>
       </c>
     </row>
     <row r="47">
@@ -2844,50 +2844,50 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.300626</v>
+        <v>0.172618</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.119478</v>
+        <v>0.006405</v>
       </c>
       <c r="E47" t="n">
-        <v>0.654212</v>
+        <v>0.002222</v>
       </c>
       <c r="F47" t="n">
-        <v>0.753813</v>
+        <v>0.01</v>
       </c>
       <c r="G47" t="n">
-        <v>7261.3805</v>
+        <v>9970.6986</v>
       </c>
       <c r="H47" t="n">
-        <v>118.3694</v>
+        <v>134.4768</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4312</v>
+        <v>-0.0411</v>
       </c>
       <c r="J47" t="n">
-        <v>-21.8706</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>8.2433</v>
+        <v>-0.9431</v>
       </c>
       <c r="L47" t="n">
-        <v>-7.2721</v>
+        <v>0.7882</v>
       </c>
       <c r="M47" t="n">
-        <v>-2.618</v>
+        <v>0.2238</v>
       </c>
       <c r="N47" t="n">
-        <v>-4.5772</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>-28.0945</v>
+        <v>0.0689</v>
       </c>
       <c r="P47" t="n">
-        <v>60.6347</v>
+        <v>140.3317</v>
       </c>
     </row>
     <row r="48">
@@ -2896,50 +2896,50 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.290286</v>
+        <v>0.166681</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.135569</v>
+        <v>0.005789</v>
       </c>
       <c r="E48" t="n">
-        <v>0.645554</v>
+        <v>0.002222</v>
       </c>
       <c r="F48" t="n">
-        <v>0.733233</v>
+        <v>0.01</v>
       </c>
       <c r="G48" t="n">
-        <v>7208.1365</v>
+        <v>9972.517599999999</v>
       </c>
       <c r="H48" t="n">
-        <v>115.4827</v>
+        <v>134.7695</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4749</v>
+        <v>-0.0413</v>
       </c>
       <c r="J48" t="n">
-        <v>-21.2875</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>8.565200000000001</v>
+        <v>-0.9171</v>
       </c>
       <c r="L48" t="n">
-        <v>-7.0982</v>
+        <v>0.7567</v>
       </c>
       <c r="M48" t="n">
-        <v>-2.5166</v>
+        <v>0.2127</v>
       </c>
       <c r="N48" t="n">
-        <v>-4.8248</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-27.1618</v>
+        <v>0.0523</v>
       </c>
       <c r="P48" t="n">
-        <v>53.9121</v>
+        <v>140.5825</v>
       </c>
     </row>
     <row r="49">
@@ -2948,50 +2948,50 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.280302</v>
+        <v>0.160948</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.155815</v>
+        <v>0.004468</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6392370000000001</v>
+        <v>0.002222</v>
       </c>
       <c r="F49" t="n">
-        <v>0.711558</v>
+        <v>0.01</v>
       </c>
       <c r="G49" t="n">
-        <v>7164.5456</v>
+        <v>9974.154699999999</v>
       </c>
       <c r="H49" t="n">
-        <v>112.4042</v>
+        <v>135.0602</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5204</v>
+        <v>-0.0409</v>
       </c>
       <c r="J49" t="n">
-        <v>-20.762</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>8.9436</v>
+        <v>-0.8832</v>
       </c>
       <c r="L49" t="n">
-        <v>-6.9361</v>
+        <v>0.7294</v>
       </c>
       <c r="M49" t="n">
-        <v>-2.4213</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>-5.0912</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>-26.267</v>
+        <v>-0.1539</v>
       </c>
       <c r="P49" t="n">
-        <v>47.1466</v>
+        <v>139.9135</v>
       </c>
     </row>
     <row r="50">
@@ -3000,50 +3000,50 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.270661</v>
+        <v>0.155412</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.181976</v>
+        <v>-0.011897</v>
       </c>
       <c r="E50" t="n">
-        <v>0.636591</v>
+        <v>0.006188</v>
       </c>
       <c r="F50" t="n">
-        <v>0.689604</v>
+        <v>0.01</v>
       </c>
       <c r="G50" t="n">
-        <v>7128.4725</v>
+        <v>9975.6281</v>
       </c>
       <c r="H50" t="n">
-        <v>109.1413</v>
+        <v>135.3029</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5679999999999999</v>
+        <v>-0.0341</v>
       </c>
       <c r="J50" t="n">
-        <v>-20.337</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>9.4024</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>-6.7967</v>
+        <v>0.6836</v>
       </c>
       <c r="M50" t="n">
-        <v>-2.3381</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-5.3844</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-25.4538</v>
+        <v>0.0067</v>
       </c>
       <c r="P50" t="n">
-        <v>40.3632</v>
+        <v>139.9487</v>
       </c>
     </row>
     <row r="51">
@@ -3052,50 +3052,50 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.261352</v>
+        <v>0.150067</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.21529</v>
+        <v>0.00063</v>
       </c>
       <c r="E51" t="n">
-        <v>0.638686</v>
+        <v>0.002222</v>
       </c>
       <c r="F51" t="n">
-        <v>0.668301</v>
+        <v>0.01</v>
       </c>
       <c r="G51" t="n">
-        <v>7097.3298</v>
+        <v>9974.971299999999</v>
       </c>
       <c r="H51" t="n">
-        <v>105.7024</v>
+        <v>135.5352</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6181</v>
+        <v>-0.0326</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.0495</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>9.9581</v>
+        <v>-0.7614</v>
       </c>
       <c r="L51" t="n">
-        <v>-6.691</v>
+        <v>0.6721</v>
       </c>
       <c r="M51" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>-5.7097</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-24.764</v>
+        <v>-0.0893</v>
       </c>
       <c r="P51" t="n">
-        <v>33.57</v>
+        <v>139.5364</v>
       </c>
     </row>
     <row r="52">
@@ -3104,50 +3104,50 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.252363</v>
+        <v>0.144905</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.259477</v>
+        <v>-0.007366</v>
       </c>
       <c r="E52" t="n">
-        <v>0.648056</v>
+        <v>0.004677</v>
       </c>
       <c r="F52" t="n">
-        <v>0.648621</v>
+        <v>0.01</v>
       </c>
       <c r="G52" t="n">
-        <v>7068.254</v>
+        <v>9976.3631</v>
       </c>
       <c r="H52" t="n">
-        <v>102.0958</v>
+        <v>135.7352</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6712</v>
+        <v>-0.028</v>
       </c>
       <c r="J52" t="n">
-        <v>-19.9808</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>10.6557</v>
+        <v>-0.641</v>
       </c>
       <c r="L52" t="n">
-        <v>-6.6369</v>
+        <v>0.6344</v>
       </c>
       <c r="M52" t="n">
-        <v>-2.234</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>-6.0794</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>-24.2754</v>
+        <v>-0.0066</v>
       </c>
       <c r="P52" t="n">
-        <v>26.7544</v>
+        <v>139.5051</v>
       </c>
     </row>
     <row r="53">
@@ -3156,50 +3156,50 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.243683</v>
+        <v>0.139921</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.321282</v>
+        <v>-0.00056</v>
       </c>
       <c r="E53" t="n">
-        <v>0.669148</v>
+        <v>0.002409</v>
       </c>
       <c r="F53" t="n">
-        <v>0.631927</v>
+        <v>0.01</v>
       </c>
       <c r="G53" t="n">
-        <v>7037.4006</v>
+        <v>9976.3881</v>
       </c>
       <c r="H53" t="n">
-        <v>98.3287</v>
+        <v>135.9237</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7279</v>
+        <v>-0.0263</v>
       </c>
       <c r="J53" t="n">
-        <v>-20.272</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>11.5749</v>
+        <v>-0.6745</v>
       </c>
       <c r="L53" t="n">
-        <v>-6.6657</v>
+        <v>0.6172</v>
       </c>
       <c r="M53" t="n">
-        <v>-2.2435</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-6.5144</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>-24.1206</v>
+        <v>-0.0573</v>
       </c>
       <c r="P53" t="n">
-        <v>19.903</v>
+        <v>139.2315</v>
       </c>
     </row>
     <row r="54">
@@ -3208,50 +3208,50 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.235302</v>
+        <v>0.135109</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.412795</v>
+        <v>-0.004903</v>
       </c>
       <c r="E54" t="n">
-        <v>0.709829</v>
+        <v>0.003857</v>
       </c>
       <c r="F54" t="n">
-        <v>0.620363</v>
+        <v>0.01</v>
       </c>
       <c r="G54" t="n">
-        <v>6999.0864</v>
+        <v>9977.5447</v>
       </c>
       <c r="H54" t="n">
-        <v>94.4074</v>
+        <v>136.0891</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7892</v>
+        <v>-0.0231</v>
       </c>
       <c r="J54" t="n">
-        <v>-21.1735</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>12.8556</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-6.8304</v>
+        <v>0.586</v>
       </c>
       <c r="M54" t="n">
-        <v>-2.3346</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>-7.0489</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-24.5318</v>
+        <v>0.586</v>
       </c>
       <c r="P54" t="n">
-        <v>12.9927</v>
+        <v>141.0815</v>
       </c>
     </row>
     <row r="55">
@@ -3260,50 +3260,50 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.227209</v>
+        <v>0.130462</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.562235</v>
+        <v>0.033217</v>
       </c>
       <c r="E55" t="n">
-        <v>0.787926</v>
+        <v>0.002636</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6175349999999999</v>
+        <v>0.01186</v>
       </c>
       <c r="G55" t="n">
-        <v>6944.2634</v>
+        <v>9977.861999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>90.33669999999999</v>
+        <v>136.3387</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8562</v>
+        <v>-0.0348</v>
       </c>
       <c r="J55" t="n">
-        <v>-23.2497</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>12.897</v>
+        <v>-0.9444</v>
       </c>
       <c r="L55" t="n">
-        <v>-7.2409</v>
+        <v>0.5702</v>
       </c>
       <c r="M55" t="n">
-        <v>-2.5847</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>-7.7565</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>-27.9348</v>
+        <v>-0.3743</v>
       </c>
       <c r="P55" t="n">
-        <v>5.9575</v>
+        <v>139.7162</v>
       </c>
     </row>
     <row r="56">
@@ -3312,50 +3312,50 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.219394</v>
+        <v>0.125975</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.833203</v>
+        <v>-0.024194</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9507409999999999</v>
+        <v>0.010478</v>
       </c>
       <c r="F56" t="n">
-        <v>0.649869</v>
+        <v>0.010859</v>
       </c>
       <c r="G56" t="n">
-        <v>6855.8741</v>
+        <v>9978.758</v>
       </c>
       <c r="H56" t="n">
-        <v>86.1177</v>
+        <v>136.5076</v>
       </c>
       <c r="I56" t="n">
-        <v>0.9308</v>
+        <v>-0.0235</v>
       </c>
       <c r="J56" t="n">
-        <v>-28.0961</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>12.897</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-8.2478</v>
+        <v>0.5196</v>
       </c>
       <c r="M56" t="n">
-        <v>-3.2175</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>-8.821300000000001</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-35.4856</v>
+        <v>0.5196</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01</v>
+        <v>141.4296</v>
       </c>
     </row>
     <row r="57">
@@ -3364,50 +3364,50 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.211848</v>
+        <v>0.121642</v>
       </c>
       <c r="D57" t="n">
-        <v>-1</v>
+        <v>0.03066</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.002602</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7447780000000001</v>
+        <v>0.011711</v>
       </c>
       <c r="G57" t="n">
-        <v>6694.9162</v>
+        <v>9975.6433</v>
       </c>
       <c r="H57" t="n">
-        <v>81.81229999999999</v>
+        <v>136.7537</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9999</v>
+        <v>-0.0342</v>
       </c>
       <c r="J57" t="n">
-        <v>-30.6746</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>12.897</v>
+        <v>-0.8885</v>
       </c>
       <c r="L57" t="n">
-        <v>-9.218400000000001</v>
+        <v>0.5336</v>
       </c>
       <c r="M57" t="n">
-        <v>-3.6677</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>-9.5502</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>-40.2138</v>
+        <v>-0.355</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01</v>
+        <v>140.1159</v>
       </c>
     </row>
     <row r="58">
@@ -3416,50 +3416,50 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.204561</v>
+        <v>0.117458</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>-0.023222</v>
       </c>
       <c r="E58" t="n">
-        <v>0.528314</v>
+        <v>0.010091</v>
       </c>
       <c r="F58" t="n">
-        <v>0.849005</v>
+        <v>0.010576</v>
       </c>
       <c r="G58" t="n">
-        <v>6525.4246</v>
+        <v>9976.777700000001</v>
       </c>
       <c r="H58" t="n">
-        <v>77.7222</v>
+        <v>136.9218</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9999</v>
+        <v>-0.0233</v>
       </c>
       <c r="J58" t="n">
-        <v>-15.8144</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>9.964600000000001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-8.109299999999999</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-1.5612</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>-7.6407</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>-23.161</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01</v>
+        <v>140.1174</v>
       </c>
     </row>
     <row r="59">
@@ -3468,50 +3468,50 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-0.197526</v>
+        <v>0.113418</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="E59" t="n">
-        <v>0.479544</v>
+        <v>0.002222</v>
       </c>
       <c r="F59" t="n">
-        <v>0.741013</v>
+        <v>0.01</v>
       </c>
       <c r="G59" t="n">
-        <v>6608.7252</v>
+        <v>9974.0545</v>
       </c>
       <c r="H59" t="n">
-        <v>73.8366</v>
+        <v>137.0816</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9999</v>
+        <v>-0.0221</v>
       </c>
       <c r="J59" t="n">
-        <v>-13.7268</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>9.6858</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>-8.071400000000001</v>
+        <v>0.5041</v>
       </c>
       <c r="M59" t="n">
-        <v>-1.2555</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>-7.4844</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>-20.8524</v>
+        <v>0.5041</v>
       </c>
       <c r="P59" t="n">
-        <v>0.01</v>
+        <v>141.799</v>
       </c>
     </row>
     <row r="60">
@@ -3520,50 +3520,50 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-0.190732</v>
+        <v>0.109517</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.030003</v>
       </c>
       <c r="E60" t="n">
-        <v>0.43882</v>
+        <v>0.002454</v>
       </c>
       <c r="F60" t="n">
-        <v>0.653132</v>
+        <v>0.011041</v>
       </c>
       <c r="G60" t="n">
-        <v>6708.0806</v>
+        <v>9975.537899999999</v>
       </c>
       <c r="H60" t="n">
-        <v>70.14530000000001</v>
+        <v>137.3175</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9999</v>
+        <v>-0.0326</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.9972</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>9.449299999999999</v>
+        <v>-0.829</v>
       </c>
       <c r="L60" t="n">
-        <v>-8.5647</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-1.0036</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>-7.3546</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>-19.4707</v>
+        <v>-0.829</v>
       </c>
       <c r="P60" t="n">
-        <v>0.01</v>
+        <v>139.5283</v>
       </c>
     </row>
     <row r="61">
@@ -3572,50 +3572,50 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.184172</v>
+        <v>0.10575</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>-0.040033</v>
       </c>
       <c r="E61" t="n">
-        <v>0.406608</v>
+        <v>0.016659</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5865860000000001</v>
+        <v>0.014915</v>
       </c>
       <c r="G61" t="n">
-        <v>6817.8625</v>
+        <v>9976.757299999999</v>
       </c>
       <c r="H61" t="n">
-        <v>66.63849999999999</v>
+        <v>137.428</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9998</v>
+        <v>-0.0153</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.6465</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>9.2577</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>-10.0061</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.8087</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>-7.2528</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>-19.4564</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.01</v>
+        <v>139.5294</v>
       </c>
     </row>
     <row r="62">
@@ -3624,50 +3624,50 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.177837</v>
+        <v>0.102113</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2e-05</v>
       </c>
       <c r="E62" t="n">
-        <v>0.384896</v>
+        <v>0.002222</v>
       </c>
       <c r="F62" t="n">
-        <v>0.546515</v>
+        <v>0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>6932.7724</v>
+        <v>9970.7521</v>
       </c>
       <c r="H62" t="n">
-        <v>63.3071</v>
+        <v>137.5331</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9998</v>
+        <v>-0.0145</v>
       </c>
       <c r="J62" t="n">
-        <v>-9.7643</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>9.1212</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>-3.6746</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6842</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>-7.1856</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>-12.1876</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.01</v>
+        <v>139.5313</v>
       </c>
     </row>
     <row r="63">
@@ -3676,50 +3676,50 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.171721</v>
+        <v>0.09860099999999999</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="E63" t="n">
-        <v>0.341393</v>
+        <v>0.002222</v>
       </c>
       <c r="F63" t="n">
-        <v>0.449786</v>
+        <v>0.01</v>
       </c>
       <c r="G63" t="n">
-        <v>7047.047</v>
+        <v>9972.5658</v>
       </c>
       <c r="H63" t="n">
-        <v>60.1422</v>
+        <v>137.633</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9998</v>
+        <v>-0.0138</v>
       </c>
       <c r="J63" t="n">
-        <v>-7.8998</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>8.872999999999999</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>-3.0734</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.411</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>-7.0461</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>-9.5572</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.01</v>
+        <v>139.5301</v>
       </c>
     </row>
     <row r="64">
@@ -3728,50 +3728,50 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-0.165814</v>
+        <v>0.09521</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>-2.1e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>0.302905</v>
+        <v>0.002229</v>
       </c>
       <c r="F64" t="n">
-        <v>0.365443</v>
+        <v>0.01</v>
       </c>
       <c r="G64" t="n">
-        <v>7171.6458</v>
+        <v>9974.1981</v>
       </c>
       <c r="H64" t="n">
-        <v>57.1356</v>
+        <v>137.7278</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9998</v>
+        <v>-0.0131</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.2575</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>8.6516</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>-2.5439</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>-6.923</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>-7.0729</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.01</v>
+        <v>139.5303</v>
       </c>
     </row>
     <row r="65">
@@ -3780,50 +3780,50 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.160111</v>
+        <v>0.091935</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="E65" t="n">
-        <v>0.268067</v>
+        <v>0.002222</v>
       </c>
       <c r="F65" t="n">
-        <v>0.289995</v>
+        <v>0.01</v>
       </c>
       <c r="G65" t="n">
-        <v>7303.0289</v>
+        <v>9975.6636</v>
       </c>
       <c r="H65" t="n">
-        <v>54.2793</v>
+        <v>137.818</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9998</v>
+        <v>-0.0124</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.7763</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>8.4497</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>-2.0665</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>-6.8119</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>-5.205</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0.01</v>
+        <v>139.5297</v>
       </c>
     </row>
     <row r="66">
@@ -3832,50 +3832,50 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-0.154604</v>
+        <v>0.088773</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>-1.1e-05</v>
       </c>
       <c r="E66" t="n">
-        <v>0.237886</v>
+        <v>0.002226</v>
       </c>
       <c r="F66" t="n">
-        <v>0.226047</v>
+        <v>0.01</v>
       </c>
       <c r="G66" t="n">
-        <v>7438.6925</v>
+        <v>9976.9861</v>
       </c>
       <c r="H66" t="n">
-        <v>51.5659</v>
+        <v>137.9036</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9998</v>
+        <v>-0.0118</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.5014</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>8.2727</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>-1.6558</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.2298</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>-6.716</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.3707</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0.01</v>
+        <v>139.53</v>
       </c>
     </row>
     <row r="67">
@@ -3884,50 +3884,50 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.149287</v>
+        <v>0.085719</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2107</v>
+        <v>0.002222</v>
       </c>
       <c r="F67" t="n">
-        <v>0.169335</v>
+        <v>0.01</v>
       </c>
       <c r="G67" t="n">
-        <v>7575.8801</v>
+        <v>9978.1746</v>
       </c>
       <c r="H67" t="n">
-        <v>48.9881</v>
+        <v>137.9849</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9998</v>
+        <v>-0.0112</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.3583</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>8.111800000000001</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>-1.2877</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.3951</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>-6.6299</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>-1.7689</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01</v>
+        <v>139.5295</v>
       </c>
     </row>
     <row r="68">
@@ -3936,50 +3936,50 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.144152</v>
+        <v>0.082771</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>-9e-06</v>
       </c>
       <c r="E68" t="n">
-        <v>0.18628</v>
+        <v>0.002225</v>
       </c>
       <c r="F68" t="n">
-        <v>0.11929</v>
+        <v>0.01</v>
       </c>
       <c r="G68" t="n">
-        <v>7712.9422</v>
+        <v>9979.245999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>46.5392</v>
+        <v>138.0621</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9998</v>
+        <v>-0.0106</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>7.9659</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>-0.9588</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5423</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>-6.5528</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.9966</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>3.1878</v>
+        <v>139.5309</v>
       </c>
     </row>
     <row r="69">
@@ -3988,50 +3988,50 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.139194</v>
+        <v>0.079924</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2.4e-05</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F69" t="n">
-        <v>0.08154</v>
+        <v>0.01</v>
       </c>
       <c r="G69" t="n">
-        <v>7848.5081</v>
+        <v>9980.2088</v>
       </c>
       <c r="H69" t="n">
-        <v>44.3716</v>
+        <v>138.1355</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9282</v>
+        <v>-0.0101</v>
       </c>
       <c r="J69" t="n">
-        <v>8.9373</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.2144</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>6.0034</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>2.4903</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>-4.7151</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>11.5014</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>8.894</v>
+        <v>139.5311</v>
       </c>
     </row>
     <row r="70">
@@ -4040,50 +4040,50 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.134406</v>
+        <v>0.07717499999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>5e-06</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F70" t="n">
-        <v>0.163938</v>
+        <v>0.01</v>
       </c>
       <c r="G70" t="n">
-        <v>8063.6573</v>
+        <v>9981.076800000001</v>
       </c>
       <c r="H70" t="n">
-        <v>42.5977</v>
+        <v>138.2053</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7912</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>7.5026</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.1161</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>5.5535</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.1464</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>-3.9263</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>9.1602</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>14.3516</v>
+        <v>139.531</v>
       </c>
     </row>
     <row r="71">
@@ -4092,50 +4092,50 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-0.129784</v>
+        <v>0.074521</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>-3e-06</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>0.002223</v>
       </c>
       <c r="F71" t="n">
-        <v>0.189964</v>
+        <v>0.01</v>
       </c>
       <c r="G71" t="n">
-        <v>8257.291499999999</v>
+        <v>9981.858</v>
       </c>
       <c r="H71" t="n">
-        <v>41.1854</v>
+        <v>138.2716</v>
       </c>
       <c r="I71" t="n">
-        <v>0.6515</v>
+        <v>-0.0091</v>
       </c>
       <c r="J71" t="n">
-        <v>6.6065</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.0346</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>5.3292</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1.9193</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>-3.0926</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>7.7278</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>19.6004</v>
+        <v>139.5297</v>
       </c>
     </row>
     <row r="72">
@@ -4144,50 +4144,50 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.12532</v>
+        <v>0.07195799999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>0.914324</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>0.00223</v>
       </c>
       <c r="F72" t="n">
-        <v>0.191257</v>
+        <v>0.01</v>
       </c>
       <c r="G72" t="n">
-        <v>8431.562400000001</v>
+        <v>9982.5607</v>
       </c>
       <c r="H72" t="n">
-        <v>40.1062</v>
+        <v>138.3345</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5113</v>
+        <v>-0.0086</v>
       </c>
       <c r="J72" t="n">
-        <v>5.388</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.2933</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>3.6218</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1.5975</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>-2.3294</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>4.9846</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>24.4516</v>
+        <v>139.5305</v>
       </c>
     </row>
     <row r="73">
@@ -4196,50 +4196,50 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.121009</v>
+        <v>0.069483</v>
       </c>
       <c r="D73" t="n">
-        <v>0.618766</v>
+        <v>1.3e-05</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1646</v>
+        <v>0.01</v>
       </c>
       <c r="G73" t="n">
-        <v>8588.406199999999</v>
+        <v>9983.1898</v>
       </c>
       <c r="H73" t="n">
-        <v>39.3234</v>
+        <v>138.3943</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3782</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.1034</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.8812</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>2.3377</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9852</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.8069</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>2.7382</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>28.65</v>
+        <v>139.5321</v>
       </c>
     </row>
     <row r="74">
@@ -4248,50 +4248,50 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-0.116847</v>
+        <v>0.067093</v>
       </c>
       <c r="D74" t="n">
-        <v>0.429252</v>
+        <v>3e-05</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F74" t="n">
-        <v>0.126143</v>
+        <v>0.01</v>
       </c>
       <c r="G74" t="n">
-        <v>8729.565500000001</v>
+        <v>9983.759700000001</v>
       </c>
       <c r="H74" t="n">
-        <v>38.7898</v>
+        <v>138.4512</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2614</v>
+        <v>-0.0078</v>
       </c>
       <c r="J74" t="n">
-        <v>1.7077</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.1839</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>1.3621</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6004</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>-1.2703</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>1.216</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>31.7502</v>
+        <v>139.5329</v>
       </c>
     </row>
     <row r="75">
@@ -4300,29 +4300,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-0.112828</v>
+        <v>0.064785</v>
       </c>
       <c r="D75" t="n">
-        <v>0.270527</v>
+        <v>1.3e-05</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F75" t="n">
-        <v>0.08784500000000001</v>
+        <v>0.01</v>
       </c>
       <c r="G75" t="n">
-        <v>8856.609</v>
+        <v>9984.2726</v>
       </c>
       <c r="H75" t="n">
-        <v>38.4378</v>
+        <v>138.5053</v>
       </c>
       <c r="I75" t="n">
-        <v>0.174</v>
+        <v>-0.0074</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -4331,19 +4331,19 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.6991000000000001</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0.3053</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>-0.8804</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>32.3665</v>
+        <v>139.534</v>
       </c>
     </row>
     <row r="76">
@@ -4352,50 +4352,50 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-0.108948</v>
+        <v>0.062557</v>
       </c>
       <c r="D76" t="n">
-        <v>0.048524</v>
+        <v>2.1e-05</v>
       </c>
       <c r="E76" t="n">
-        <v>0.098458</v>
+        <v>0.002222</v>
       </c>
       <c r="F76" t="n">
-        <v>0.053947</v>
+        <v>0.01</v>
       </c>
       <c r="G76" t="n">
-        <v>8970.9481</v>
+        <v>9984.734200000001</v>
       </c>
       <c r="H76" t="n">
-        <v>38.1342</v>
+        <v>138.5567</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1512</v>
+        <v>-0.0071</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.4733</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1.5293</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.0948</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>-1.146</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>-2.1849</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>28.5662</v>
+        <v>139.5345</v>
       </c>
     </row>
     <row r="77">
@@ -4404,50 +4404,50 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.105201</v>
+        <v>0.060406</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.293534</v>
+        <v>9e-06</v>
       </c>
       <c r="E77" t="n">
-        <v>0.294183</v>
+        <v>0.002222</v>
       </c>
       <c r="F77" t="n">
-        <v>0.054217</v>
+        <v>0.01</v>
       </c>
       <c r="G77" t="n">
-        <v>9024.624</v>
+        <v>9985.1497</v>
       </c>
       <c r="H77" t="n">
-        <v>37.6558</v>
+        <v>138.6056</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2414</v>
+        <v>-0.0067</v>
       </c>
       <c r="J77" t="n">
-        <v>-8.0806</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>5.7527</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.3062</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.8662</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>-2.4284</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>-6.9287</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>23.6973</v>
+        <v>139.5351</v>
       </c>
     </row>
     <row r="78">
@@ -4456,50 +4456,50 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.101582</v>
+        <v>0.058328</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.426102</v>
+        <v>1.1e-05</v>
       </c>
       <c r="E78" t="n">
-        <v>0.386379</v>
+        <v>0.002222</v>
       </c>
       <c r="F78" t="n">
-        <v>0.101817</v>
+        <v>0.01</v>
       </c>
       <c r="G78" t="n">
-        <v>8975.070299999999</v>
+        <v>9985.5236</v>
       </c>
       <c r="H78" t="n">
-        <v>36.9579</v>
+        <v>138.6521</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3588</v>
+        <v>-0.0064</v>
       </c>
       <c r="J78" t="n">
-        <v>-10.6149</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>7.9973</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.1681</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.1564</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>-3.4798</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>-9.421900000000001</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>18.6126</v>
+        <v>139.5353</v>
       </c>
     </row>
     <row r="79">
@@ -4508,50 +4508,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.09808799999999999</v>
+        <v>0.056322</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.536428</v>
+        <v>3e-06</v>
       </c>
       <c r="E79" t="n">
-        <v>0.468028</v>
+        <v>0.002222</v>
       </c>
       <c r="F79" t="n">
-        <v>0.155309</v>
+        <v>0.01</v>
       </c>
       <c r="G79" t="n">
-        <v>8884.3737</v>
+        <v>9985.860199999999</v>
       </c>
       <c r="H79" t="n">
-        <v>36.0406</v>
+        <v>138.6962</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4836</v>
+        <v>-0.006</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.8193</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>10.0633</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.9636</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.3983</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>-4.5351</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>-11.653</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>13.3605</v>
+        <v>139.5334</v>
       </c>
     </row>
     <row r="80">
@@ -4560,50 +4560,50 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.09471499999999999</v>
+        <v>0.054385</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.705448</v>
+        <v>-3.3e-05</v>
       </c>
       <c r="E80" t="n">
-        <v>0.5843390000000001</v>
+        <v>0.002233</v>
       </c>
       <c r="F80" t="n">
-        <v>0.209715</v>
+        <v>0.01</v>
       </c>
       <c r="G80" t="n">
-        <v>8761.9223</v>
+        <v>9986.163</v>
       </c>
       <c r="H80" t="n">
-        <v>34.9066</v>
+        <v>138.7381</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6173</v>
+        <v>-0.0057</v>
       </c>
       <c r="J80" t="n">
-        <v>-16.0553</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>12.8202</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>-3.9134</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.7759</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>-5.7737</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>-14.6981</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>7.9158</v>
+        <v>139.5316</v>
       </c>
     </row>
     <row r="81">
@@ -4612,50 +4612,50 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-0.091457</v>
+        <v>0.052514</v>
       </c>
       <c r="D81" t="n">
-        <v>-1</v>
+        <v>-3.1e-05</v>
       </c>
       <c r="E81" t="n">
-        <v>0.777263</v>
+        <v>0.002233</v>
       </c>
       <c r="F81" t="n">
-        <v>0.272811</v>
+        <v>0.01</v>
       </c>
       <c r="G81" t="n">
-        <v>8593.5605</v>
+        <v>9986.43</v>
       </c>
       <c r="H81" t="n">
-        <v>33.5571</v>
+        <v>138.7778</v>
       </c>
       <c r="I81" t="n">
-        <v>0.7641</v>
+        <v>-0.0054</v>
       </c>
       <c r="J81" t="n">
-        <v>-21.6398</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>12.897</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>-5.2366</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.4686</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>-7.3774</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>-23.8253</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.1705</v>
+        <v>139.5309</v>
       </c>
     </row>
     <row r="82">
@@ -4664,50 +4664,50 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.088311</v>
+        <v>0.050708</v>
       </c>
       <c r="D82" t="n">
-        <v>-1</v>
+        <v>-1.4e-05</v>
       </c>
       <c r="E82" t="n">
-        <v>0.824357</v>
+        <v>0.002227</v>
       </c>
       <c r="F82" t="n">
-        <v>0.40194</v>
+        <v>0.01</v>
       </c>
       <c r="G82" t="n">
-        <v>8345.5728</v>
+        <v>9986.670700000001</v>
       </c>
       <c r="H82" t="n">
-        <v>31.9878</v>
+        <v>138.8154</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9321</v>
+        <v>-0.0052</v>
       </c>
       <c r="J82" t="n">
-        <v>-22.9769</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>12.897</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>-6.2344</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.5842</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>-8.5517</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>-27.4502</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.01</v>
+        <v>139.5293</v>
       </c>
     </row>
     <row r="83">
@@ -4716,50 +4716,50 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.085274</v>
+        <v>0.048964</v>
       </c>
       <c r="D83" t="n">
-        <v>-1</v>
+        <v>-2.8e-05</v>
       </c>
       <c r="E83" t="n">
-        <v>0.865573</v>
+        <v>0.002232</v>
       </c>
       <c r="F83" t="n">
-        <v>0.515666</v>
+        <v>0.01</v>
       </c>
       <c r="G83" t="n">
-        <v>8098.8372</v>
+        <v>9986.890100000001</v>
       </c>
       <c r="H83" t="n">
-        <v>30.3889</v>
+        <v>138.8511</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9997</v>
+        <v>-0.0049</v>
       </c>
       <c r="J83" t="n">
-        <v>-24.542</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>12.897</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>-7.2303</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>-2.7886</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>-9.098800000000001</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>-30.7627</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.01</v>
+        <v>139.5303</v>
       </c>
     </row>
     <row r="84">
@@ -4768,50 +4768,50 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-0.082341</v>
+        <v>0.04728</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="E84" t="n">
-        <v>0.319565</v>
+        <v>0.002222</v>
       </c>
       <c r="F84" t="n">
-        <v>0.617027</v>
+        <v>0.01</v>
       </c>
       <c r="G84" t="n">
-        <v>7856.1669</v>
+        <v>9987.085300000001</v>
       </c>
       <c r="H84" t="n">
-        <v>28.8699</v>
+        <v>138.8851</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9997</v>
+        <v>-0.0046</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.236599999999999</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>8.413399999999999</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>-5.9074</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>-0.588</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>-7.0402</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>-13.3589</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.01</v>
+        <v>139.5309</v>
       </c>
     </row>
     <row r="85">
@@ -4820,50 +4820,50 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-0.079509</v>
+        <v>0.045654</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="E85" t="n">
-        <v>0.272845</v>
+        <v>0.002222</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5038049999999999</v>
+        <v>0.01</v>
       </c>
       <c r="G85" t="n">
-        <v>7910.7678</v>
+        <v>9987.2657</v>
       </c>
       <c r="H85" t="n">
-        <v>27.4269</v>
+        <v>138.9174</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9996</v>
+        <v>-0.0044</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.1793</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>8.1614</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>-6.0156</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.281</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>-6.8875</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>-11.202</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.01</v>
+        <v>139.5303</v>
       </c>
     </row>
     <row r="86">
@@ -4872,50 +4872,50 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-0.076774</v>
+        <v>0.044083</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>-1e-05</v>
       </c>
       <c r="E86" t="n">
-        <v>0.235432</v>
+        <v>0.002225</v>
       </c>
       <c r="F86" t="n">
-        <v>0.414303</v>
+        <v>0.01</v>
       </c>
       <c r="G86" t="n">
-        <v>7983.2684</v>
+        <v>9987.428</v>
       </c>
       <c r="H86" t="n">
-        <v>26.0561</v>
+        <v>138.948</v>
       </c>
       <c r="I86" t="n">
-        <v>0.9996</v>
+        <v>-0.0042</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.5386</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>7.9576</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>-6.7822</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>-6.7655</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>-10.1287</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.01</v>
+        <v>139.5309</v>
       </c>
     </row>
     <row r="87">
@@ -4924,50 +4924,50 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-0.07413400000000001</v>
+        <v>0.042567</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>9e-06</v>
       </c>
       <c r="E87" t="n">
-        <v>0.207846</v>
+        <v>0.002222</v>
       </c>
       <c r="F87" t="n">
-        <v>0.349869</v>
+        <v>0.01</v>
       </c>
       <c r="G87" t="n">
-        <v>8067.2253</v>
+        <v>9987.5725</v>
       </c>
       <c r="H87" t="n">
-        <v>24.7538</v>
+        <v>138.9772</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9996</v>
+        <v>-0.004</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.3381</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>7.805</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>-7.5894</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>-6.676</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>-9.798500000000001</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.01</v>
+        <v>139.5293</v>
       </c>
     </row>
     <row r="88">
@@ -4976,50 +4976,50 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-0.07158399999999999</v>
+        <v>0.041103</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>-2.7e-05</v>
       </c>
       <c r="E88" t="n">
-        <v>0.189074</v>
+        <v>0.002231</v>
       </c>
       <c r="F88" t="n">
-        <v>0.307907</v>
+        <v>0.01</v>
       </c>
       <c r="G88" t="n">
-        <v>8156.5799</v>
+        <v>9987.704100000001</v>
       </c>
       <c r="H88" t="n">
-        <v>23.5166</v>
+        <v>139.0048</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9996</v>
+        <v>-0.0038</v>
       </c>
       <c r="J88" t="n">
-        <v>-2.5324</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>7.6981</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>-1.3685</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0.2591</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>-6.6156</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>-2.5592</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0.01</v>
+        <v>139.5275</v>
       </c>
     </row>
     <row r="89">
@@ -5028,50 +5028,50 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.069122</v>
+        <v>0.039689</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>-3.4e-05</v>
       </c>
       <c r="E89" t="n">
-        <v>0.148792</v>
+        <v>0.002233</v>
       </c>
       <c r="F89" t="n">
-        <v>0.210336</v>
+        <v>0.01</v>
       </c>
       <c r="G89" t="n">
-        <v>8246.3848</v>
+        <v>9987.817999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>22.3413</v>
+        <v>139.0309</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9996</v>
+        <v>-0.0036</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>7.4807</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.7955</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5238</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>-6.4839</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0.725</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2.526</v>
+        <v>139.5288</v>
       </c>
     </row>
     <row r="90">
@@ -5080,50 +5080,50 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-0.066744</v>
+        <v>0.038324</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2.4e-05</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F90" t="n">
-        <v>0.133452</v>
+        <v>0.01</v>
       </c>
       <c r="G90" t="n">
-        <v>8347.3501</v>
+        <v>9987.9195</v>
       </c>
       <c r="H90" t="n">
-        <v>21.3505</v>
+        <v>139.0558</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8817</v>
+        <v>-0.0034</v>
       </c>
       <c r="J90" t="n">
-        <v>8.9108</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>-1.7944</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>6.1134</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>2.4436</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>-4.4239</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>11.2495</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>7.9214</v>
+        <v>139.5298</v>
       </c>
     </row>
     <row r="91">
@@ -5132,50 +5132,50 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-0.06444900000000001</v>
+        <v>0.037006</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>1.7e-05</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F91" t="n">
-        <v>0.192566</v>
+        <v>0.01</v>
       </c>
       <c r="G91" t="n">
-        <v>8512.615100000001</v>
+        <v>9988.0165</v>
       </c>
       <c r="H91" t="n">
-        <v>20.679</v>
+        <v>139.0795</v>
       </c>
       <c r="I91" t="n">
-        <v>0.6169</v>
+        <v>-0.0032</v>
       </c>
       <c r="J91" t="n">
-        <v>7.0527</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>-3.5106</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>5.6156</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>1.9812</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>-2.8518</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>8.287100000000001</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>13.0754</v>
+        <v>139.5286</v>
       </c>
     </row>
     <row r="92">
@@ -5184,50 +5184,50 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.062232</v>
+        <v>0.035733</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>-2e-05</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.002229</v>
       </c>
       <c r="F92" t="n">
-        <v>0.19841</v>
+        <v>0.01</v>
       </c>
       <c r="G92" t="n">
-        <v>8661.3536</v>
+        <v>9988.1037</v>
       </c>
       <c r="H92" t="n">
-        <v>20.2989</v>
+        <v>139.102</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3559</v>
+        <v>-0.0031</v>
       </c>
       <c r="J92" t="n">
-        <v>5.735</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>-5.2027</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>5.3377</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1.6373</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>-1.2751</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>6.2322</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>17.9764</v>
+        <v>139.5301</v>
       </c>
     </row>
     <row r="93">
@@ -5236,50 +5236,50 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-0.060091</v>
+        <v>0.034504</v>
       </c>
       <c r="D93" t="n">
-        <v>0.937056</v>
+        <v>2.6e-05</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F93" t="n">
-        <v>0.181368</v>
+        <v>0.01</v>
       </c>
       <c r="G93" t="n">
-        <v>8795.218199999999</v>
+        <v>9988.178900000001</v>
       </c>
       <c r="H93" t="n">
-        <v>20.1827</v>
+        <v>139.1234</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1093</v>
+        <v>-0.0029</v>
       </c>
       <c r="J93" t="n">
-        <v>4.3007</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>-6.3137</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>3.7226</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1.2533</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>2.9628</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>22.1695</v>
+        <v>139.5317</v>
       </c>
     </row>
     <row r="94">
@@ -5288,50 +5288,50 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.058025</v>
+        <v>0.033317</v>
       </c>
       <c r="D94" t="n">
-        <v>0.583135</v>
+        <v>2.8e-05</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="F94" t="n">
-        <v>0.138449</v>
+        <v>0.01</v>
       </c>
       <c r="G94" t="n">
-        <v>8915.696400000001</v>
+        <v>9988.249900000001</v>
       </c>
       <c r="H94" t="n">
-        <v>20.2821</v>
+        <v>139.1438</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0931</v>
+        <v>-0.0028</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>-4.888</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>2.3035</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0.4831</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.0512</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>-1.0502</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>19.3287</v>
+        <v>139.5333</v>
       </c>
     </row>
     <row r="95">
@@ -5340,50 +5340,50 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-0.056029</v>
+        <v>0.032171</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.320349</v>
+        <v>2.9e-05</v>
       </c>
       <c r="E95" t="n">
-        <v>0.277347</v>
+        <v>0.002222</v>
       </c>
       <c r="F95" t="n">
-        <v>0.093572</v>
+        <v>0.01</v>
       </c>
       <c r="G95" t="n">
-        <v>9024.1268</v>
+        <v>9988.3138</v>
       </c>
       <c r="H95" t="n">
-        <v>20.2344</v>
+        <v>139.1633</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0448</v>
+        <v>-0.0027</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.794600000000001</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>4.4151</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.1378</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>-1.1429</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>-6.8879</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>14.4713</v>
+        <v>139.5338</v>
       </c>
     </row>
     <row r="96">
@@ -5392,50 +5392,50 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-0.054102</v>
+        <v>0.031065</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.628267</v>
+        <v>8e-06</v>
       </c>
       <c r="E96" t="n">
-        <v>0.467059</v>
+        <v>0.002222</v>
       </c>
       <c r="F96" t="n">
-        <v>0.125022</v>
+        <v>0.01</v>
       </c>
       <c r="G96" t="n">
-        <v>8983.040800000001</v>
+        <v>9988.371300000001</v>
       </c>
       <c r="H96" t="n">
-        <v>19.9462</v>
+        <v>139.1818</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2745</v>
+        <v>-0.0025</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.6988</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>9.250500000000001</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>-1.9069</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>-1.6826</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>-3.3241</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>-11.362</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>9.281700000000001</v>
+        <v>139.5354</v>
       </c>
     </row>
     <row r="97">
@@ -5444,50 +5444,50 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.052241</v>
+        <v>0.029996</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.896526</v>
+        <v>3e-05</v>
       </c>
       <c r="E97" t="n">
-        <v>0.646223</v>
+        <v>0.002222</v>
       </c>
       <c r="F97" t="n">
-        <v>0.188633</v>
+        <v>0.01</v>
       </c>
       <c r="G97" t="n">
-        <v>8851.207200000001</v>
+        <v>9988.423000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>19.413</v>
+        <v>139.1995</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5219</v>
+        <v>-0.0024</v>
       </c>
       <c r="J97" t="n">
-        <v>-18.366</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>12.897</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>-3.3954</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>-2.187</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>-5.4824</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>-16.5338</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>3.8223</v>
+        <v>139.5358</v>
       </c>
     </row>
     <row r="98">
@@ -5496,50 +5496,50 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.050444</v>
+        <v>0.028965</v>
       </c>
       <c r="D98" t="n">
-        <v>-1</v>
+        <v>7e-06</v>
       </c>
       <c r="E98" t="n">
-        <v>0.739661</v>
+        <v>0.002222</v>
       </c>
       <c r="F98" t="n">
-        <v>0.278518</v>
+        <v>0.01</v>
       </c>
       <c r="G98" t="n">
-        <v>8642.975</v>
+        <v>9988.4696</v>
       </c>
       <c r="H98" t="n">
-        <v>18.6335</v>
+        <v>139.2163</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7949000000000001</v>
+        <v>-0.0023</v>
       </c>
       <c r="J98" t="n">
-        <v>-20.4034</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>12.897</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>-4.6255</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>-2.3229</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>-7.4698</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>-21.9246</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.01</v>
+        <v>139.5356</v>
       </c>
     </row>
     <row r="99">
@@ -5548,50 +5548,50 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-0.048709</v>
+        <v>0.027969</v>
       </c>
       <c r="D99" t="n">
-        <v>-1</v>
+        <v>-4e-06</v>
       </c>
       <c r="E99" t="n">
-        <v>0.779856</v>
+        <v>0.002224</v>
       </c>
       <c r="F99" t="n">
-        <v>0.386356</v>
+        <v>0.01</v>
       </c>
       <c r="G99" t="n">
-        <v>8408.846799999999</v>
+        <v>9988.5116</v>
       </c>
       <c r="H99" t="n">
-        <v>17.7023</v>
+        <v>139.2322</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9994</v>
+        <v>-0.0022</v>
       </c>
       <c r="J99" t="n">
-        <v>-21.2304</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>12.897</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>-5.93</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>-2.3396</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>-8.841100000000001</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>-25.4441</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.01</v>
+        <v>139.5371</v>
       </c>
     </row>
     <row r="100">
@@ -5600,50 +5600,50 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.047034</v>
+        <v>0.027007</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>2.8e-05</v>
       </c>
       <c r="E100" t="n">
-        <v>0.234501</v>
+        <v>0.002222</v>
       </c>
       <c r="F100" t="n">
-        <v>0.486255</v>
+        <v>0.01</v>
       </c>
       <c r="G100" t="n">
-        <v>8178.034</v>
+        <v>9988.5486</v>
       </c>
       <c r="H100" t="n">
-        <v>16.8177</v>
+        <v>139.2475</v>
       </c>
       <c r="I100" t="n">
-        <v>0.9994</v>
+        <v>-0.0021</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.936</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>7.8364</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>-4.6652</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>-6.7836</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>-8.548400000000001</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.01</v>
+        <v>139.5357</v>
       </c>
     </row>
     <row r="101">
@@ -5652,50 +5652,50 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-0.045416</v>
+        <v>0.026078</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>-2.5e-05</v>
       </c>
       <c r="E101" t="n">
-        <v>0.190593</v>
+        <v>0.002231</v>
       </c>
       <c r="F101" t="n">
-        <v>0.377237</v>
+        <v>0.01</v>
       </c>
       <c r="G101" t="n">
-        <v>8242.9802</v>
+        <v>9988.5826</v>
       </c>
       <c r="H101" t="n">
-        <v>15.9773</v>
+        <v>139.2619</v>
       </c>
       <c r="I101" t="n">
-        <v>0.9994</v>
+        <v>-0.002</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.9871</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>7.6034</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>-4.7199</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>-6.6392</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>-6.7428</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.01</v>
+        <v>139.5375</v>
       </c>
     </row>
     <row r="102">
@@ -5704,50 +5704,50 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>crisis</t>
+          <t>strong_positive</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-0.043854</v>
+        <v>0.025181</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>3.2e-05</v>
       </c>
       <c r="E102" t="n">
-        <v>0.156662</v>
+        <v>0.002222</v>
       </c>
       <c r="F102" t="n">
-        <v>0.29377</v>
+        <v>0.01</v>
       </c>
       <c r="G102" t="n">
-        <v>8323.3855</v>
+        <v>9988.6091</v>
       </c>
       <c r="H102" t="n">
-        <v>15.1789</v>
+        <v>139.2757</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9993</v>
+        <v>-0.0019</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>7.4221</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>-5.344</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0.3781</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>-6.5278</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>-4.0715</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>0.01</v>
+        <v>139.5365</v>
       </c>
     </row>
   </sheetData>
